--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="224">
   <si>
     <t>Rank</t>
   </si>
@@ -72,19 +72,60 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>HVAC</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Official contact page is current: Mon–Fri 7:00 AM–5:30 PM, info@thermatechhvac.com, and a stated reply within 1 business hour. Current site also promotes flexible financing for new systems.</t>
+  </si>
+  <si>
+    <t>(408) 629-5400</t>
+  </si>
+  <si>
+    <t>info@thermatechhvac.com</t>
+  </si>
+  <si>
+    <t>Monday open; email reply target within 1 business hour</t>
+  </si>
+  <si>
+    <t>Turn financing and same-day HVAC decision friction into plain-English cost/option education.</t>
+  </si>
+  <si>
+    <t>Idea for Therma Tech’s financing traffic</t>
+  </si>
+  <si>
+    <t>Hi — I checked Therma Tech’s current financing and contact pages today and noticed you publish a one-business-hour email response target.
+I think there’s a strong customer question to build around:
+“Can I solve the HVAC problem now without taking the entire replacement cost at once?”
+I’d turn that into financing FAQs, Google/social posts, estimate follow-ups, objection responses and customer reactivation copy.
+Same-Day Customer Growth Pack: $150 flat, no subscription.
+Want me to send two Therma Tech-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://thermatechhvac.com/contact</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
     <t>Leader Restoration</t>
   </si>
   <si>
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>San Jose, CA</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>September 2026 FREE mold inspection is live through Sep 30; 24/7 emergency response; published 60-minute arrival target; official site publishes service@leaderestoration.com.</t>
+    <t>September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 response, 60-minute arrival target, service@leaderestoration.com, and direct insurance billing.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -93,10 +134,10 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7</t>
-  </si>
-  <si>
-    <t>Use the expiring September inspection offer as education about hidden moisture/mold rather than generic discount advertising.</t>
+    <t>24/7; direct email</t>
+  </si>
+  <si>
+    <t>Use the expiring September inspection as customer education about hidden moisture and mold risk.</t>
   </si>
   <si>
     <t>2 ideas for your September mold-inspection campaign</t>
@@ -107,25 +148,19 @@
 “You don’t need visible mold to have a moisture problem worth investigating.”
 I’d turn that into a complete September campaign: Google/social posts, homeowner FAQs, inspection reminders, customer follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat, no subscription.
-I already drafted two more Leader-specific examples. Want me to send them?</t>
+I already drafted two Leader-specific examples. Want me to send them?</t>
   </si>
   <si>
     <t>https://call.leaderestoration.com/mold-408</t>
   </si>
   <si>
-    <t>2026-09-06</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
     <t>Water / Mold Restoration</t>
   </si>
   <si>
-    <t>Official site is current today: 24/7 emergency response, free inspections, ~45-minute on-site target, direct email, and recent customer reviews posted within the last week.</t>
+    <t>Official San Jose page was crawled today and publishes 24/7 emergency response, free inspections, roughly 45-minute response in many ZIP codes, moisture mapping/documentation, and service@flooddrywdr.com. Contact page shows customer reviews from 3 and 5 days ago.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -134,7 +169,10 @@
     <t>service@flooddrywdr.com</t>
   </si>
   <si>
-    <t>Translate moisture mapping, drying logs and insurance documentation into plain-English emergency education.</t>
+    <t>24/7; direct email; recent customer activity</t>
+  </si>
+  <si>
+    <t>Translate moisture mapping, drying logs and insurance documentation into urgent plain-English education.</t>
   </si>
   <si>
     <t>Customer-education idea for FloodDry’s free inspection</t>
@@ -142,13 +180,50 @@
   <si>
     <t>Hi — I reviewed FloodDry’s current San Jose service process today and found a strong customer-education angle:
 “The floor can look dry while moisture is still inside the structure.”
-Your published process already supports that message with moisture readings, structural drying and insurance documentation.
+Your published process already supports that message with moisture readings, structural drying, drying logs and insurance documentation.
 I’d turn it into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
 Complete Same-Day Customer Growth Pack: $150 flat.
 Want me to send two FloodDry-specific samples first?</t>
   </si>
   <si>
-    <t>https://flooddrywdr.com/</t>
+    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
+  </si>
+  <si>
+    <t>ROOF EXPRESS</t>
+  </si>
+  <si>
+    <t>Roofing</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official contact page publishes sales@roof-ex.com, phone/WhatsApp responses typically within minutes during business hours, free no-obligation roof inspections, and email replies within one business day. Current San Jose page adds photo documentation, financing up to $25,000 and 24/7 emergency roofing.</t>
+  </si>
+  <si>
+    <t>(650) 666-5554</t>
+  </si>
+  <si>
+    <t>sales@roof-ex.com</t>
+  </si>
+  <si>
+    <t>Mon–Fri 7–7; phone/WhatsApp typically answered within minutes</t>
+  </si>
+  <si>
+    <t>Market the transparent inspection → photo evidence → line-item scope → financing decision path.</t>
+  </si>
+  <si>
+    <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose and contact pages today. Your inspection process gives you a stronger customer story than another generic roofing ad:
+“See what the roof needs, what it costs and what the financing options are before deciding.”
+I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
+Complete Same-Day Customer Growth Pack: $150 flat.
+Want two ROOF EXPRESS-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://quote.roof-ex.com/contact/</t>
   </si>
   <si>
     <t>IRBIS Air Plumbing Electrical</t>
@@ -157,22 +232,22 @@
     <t>HVAC / Plumbing / Electrical</t>
   </si>
   <si>
-    <t>Official site crawled today advertises same-day service across HVAC, plumbing and electrical, seven days a week; current business listing shows 24/7 operation and 942 reviews.</t>
-  </si>
-  <si>
-    <t>(669) 266-5464</t>
-  </si>
-  <si>
-    <t>Same-day / 7 days</t>
-  </si>
-  <si>
-    <t>Build one-home-one-team messaging around multiple urgent trades and same-day availability.</t>
+    <t>Official site was crawled yesterday and promotes same-day San Jose HVAC/plumbing/electrical service, 40+ trucks, free estimates, and Monday-Friday same-day dispatch with a 24/7 support line. A current official rebate page publishes (408) 317-3901.</t>
+  </si>
+  <si>
+    <t>(408) 317-3901</t>
+  </si>
+  <si>
+    <t>Monday same-day service; 24/7 support line</t>
+  </si>
+  <si>
+    <t>Build one-home-one-team messaging around problems that cross HVAC, plumbing and electrical.</t>
   </si>
   <si>
     <t>One campaign across HVAC + plumbing + electrical</t>
   </si>
   <si>
-    <t>Hi — I was reviewing IRBIS today and your biggest marketing advantage isn’t one individual service — it’s that one team can handle HVAC, plumbing and electrical with same-day availability.
+    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one individual trade — it’s that HVAC, plumbing and electrical sit under one team.
 Campaign angle:
 “One call when the problem crosses systems.”
 I’d turn that into same-day service posts, cross-service homeowner FAQs, missed-inquiry follow-ups, estimate follow-ups and genuine review-request messaging.
@@ -189,13 +264,16 @@
     <t>Water / Fire / Mold / Reconstruction</t>
   </si>
   <si>
-    <t>Official San Jose page advertises 24/7 live dispatch, local 45-minute response target, direct insurance billing, $0 upfront on covered claims, and full restoration/reconstruction.</t>
+    <t>Official San Jose page advertises 24/7 live dispatch, a 45-minute local response target, free inspection, direct insurance billing, no upfront cost on covered claims, and restoration through reconstruction.</t>
   </si>
   <si>
     <t>(408) 402-4941</t>
   </si>
   <si>
-    <t>Turn emergency response + insurance handling + rebuild capability into a clear first-call workflow.</t>
+    <t>24/7 live dispatch</t>
+  </si>
+  <si>
+    <t>Turn emergency response + insurance handling + rebuild capability into one clear first-call workflow.</t>
   </si>
   <si>
     <t>San Jose restoration campaign idea</t>
@@ -211,6 +289,40 @@
     <t>https://cawaterandfire.com/san-jose/</t>
   </si>
   <si>
+    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
+  </si>
+  <si>
+    <t>Roofing / Exterior Renovation</t>
+  </si>
+  <si>
+    <t>Sunnyvale / San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official site was crawled yesterday and publishes free inspections, same-day roof inspections, Mon–Sat 8 AM–8 PM, emergency calls 24/7, 50-year warranty availability, and roofs starting at $12,000.</t>
+  </si>
+  <si>
+    <t>(408) 685-2177</t>
+  </si>
+  <si>
+    <t>Monday 8 AM–8 PM; emergency calls 24/7</t>
+  </si>
+  <si>
+    <t>Use same-day inspections and high-ticket roof decisions to create a pre-rain inspection + estimate follow-up sequence.</t>
+  </si>
+  <si>
+    <t>Idea for Lifetime’s same-day inspection campaign</t>
+  </si>
+  <si>
+    <t>Hi — I checked Lifetime’s current San Jose roofing page today and your same-day inspection offer gives you a strong customer campaign:
+“The first rain shouldn’t be the first time you learn where the roof is vulnerable.”
+I’d turn that into roof-and-drainage education, Google/social posts, inspection reminders, estimate follow-ups and repair-vs-replacement FAQs.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Lifetime-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://lifetimeroofingrenovation.com/</t>
+  </si>
+  <si>
     <t>Infinium Solar, Roofing and Electric</t>
   </si>
   <si>
@@ -220,13 +332,13 @@
     <t>Campbell / San Jose, CA</t>
   </si>
   <si>
-    <t>Official site is current today and combines solar, roofing and electrical in-house; Campbell/San Jose phone is published; services include battery, roof replacement, panel upgrades and EV charging.</t>
+    <t>Official pages remain current and combine solar, roofing and electrical under one contractor, with free estimates and a Campbell contact number. Current business listing shows Monday hours through 7 PM.</t>
   </si>
   <si>
     <t>(408) 583-8101</t>
   </si>
   <si>
-    <t>Sunday availability shown in current business listing</t>
+    <t>Monday; official Campbell line; current listing open through 7 PM</t>
   </si>
   <si>
     <t>Use pre-solar roof/electrical readiness and bundled project coordination as the campaign.</t>
@@ -242,78 +354,38 @@
 Want two Infinium-specific samples first?</t>
   </si>
   <si>
-    <t>https://infinium.inc/</t>
-  </si>
-  <si>
-    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Exterior Renovation</t>
-  </si>
-  <si>
-    <t>Sunnyvale / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site advertises free/same-day inspections, 24/7 emergency service, San Jose coverage, and a current September storm-readiness inspection campaign ahead of rainy season.</t>
-  </si>
-  <si>
-    <t>(408) 685-2177</t>
-  </si>
-  <si>
-    <t>Emergency 24/7; regular Mon–Sat</t>
-  </si>
-  <si>
-    <t>Turn free storm-readiness inspections into a pre-rain roof + drainage education sequence.</t>
-  </si>
-  <si>
-    <t>Idea for Lifetime’s September inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked Lifetime’s current September roof-inspection messaging and there’s a strong campaign hiding inside the offer:
-“The first rain shouldn’t be the first time you learn where the roof is vulnerable.”
-I’d turn the free inspection into roof-and-drainage education, Google/social posts, inspection reminders, estimate follow-ups and repair-vs-replacement FAQs.
+    <t>https://infinium.inc/campbell-ca/</t>
+  </si>
+  <si>
+    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
+  </si>
+  <si>
+    <t>Roofing / Waterproofing</t>
+  </si>
+  <si>
+    <t>Official site was crawled within the last week and promotes free estimates, emergency leak help, financing, repair-vs-replacement education, detailed written quotes, and 100% roof-replacement financing. Monday hours are 8:30 AM–5 PM.</t>
+  </si>
+  <si>
+    <t>(408) 971-9000</t>
+  </si>
+  <si>
+    <t>Monday 8:30 AM–5 PM</t>
+  </si>
+  <si>
+    <t>Turn its explicit “we won’t sell you a roof you don’t need” positioning into a repair-vs-replacement trust campaign.</t>
+  </si>
+  <si>
+    <t>Repair-vs-replacement campaign idea for Eastman</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Eastman’s current site today and your “we won’t sell you a roof you don’t need” pledge is a strong campaign idea on its own:
+“Before replacing the roof, find out whether the problem can actually be repaired.”
+I’d turn that into repair-vs-replacement FAQs, inspection education, financing objection responses, estimate follow-ups and homeowner trust content.
 Same-Day Customer Growth Pack: $150 flat.
-Want two Lifetime-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://lifetimeroofingrenovation.com/</t>
-  </si>
-  <si>
-    <t>ROOF EXPRESS</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official site is current today: free estimates, same-day inspections Mon–Sat, photo-supported line-item scopes within 24 hours, financing up to $25,000, 24/7 emergency service, and sales@roof-ex.com.</t>
-  </si>
-  <si>
-    <t>(650) 666-5554</t>
-  </si>
-  <si>
-    <t>sales@roof-ex.com</t>
-  </si>
-  <si>
-    <t>Emergency 24/7; Sunday by appointment</t>
-  </si>
-  <si>
-    <t>Sell the transparent inspection → photo scope → financing decision process rather than generic roofing.</t>
-  </si>
-  <si>
-    <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ROOF EXPRESS today and your inspection process gives you a better customer story than a generic roofing ad:
-“See what the roof needs, what it costs and what the financing options are before deciding.”
-I’d build that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want two ROOF EXPRESS-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roof-ex.com/san-jose</t>
+Want two Eastman-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.eastmanroofing.com/</t>
   </si>
   <si>
     <t>Any Hour Water and Fire</t>
@@ -325,23 +397,22 @@
     <t>San Jose area</t>
   </si>
   <si>
-    <t>Current business listing shows Sunday hours 8 AM–5 PM, 5.0 rating with 296 reviews, and emergency mitigation/cleanup/rebuild positioning.</t>
+    <t>Current business listing shows Monday 8 AM–5 PM, a 5.0 rating with 296 reviews, and emergency mitigation, drying, cleanup and rebuild positioning.</t>
   </si>
   <si>
     <t>(669) 304-3545</t>
   </si>
   <si>
-    <t>Sunday 8:00–5:00</t>
-  </si>
-  <si>
-    <t>Lead with mitigation-first education before rebuild and insurance complexity.</t>
+    <t>Monday 8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>Lead with mitigation-first education before reconstruction and insurance complexity.</t>
   </si>
   <si>
     <t>Mitigation-first campaign idea</t>
   </si>
   <si>
-    <t>Hi — I was refreshing San Jose restoration companies today and Any Hour stood out because you’re actually reachable on Sunday.
-Campaign angle:
+    <t>Hi — I was refreshing San Jose restoration companies today and Any Hour stood out for a simple customer-education campaign:
 “Before worrying about rebuilding, stop the damage that’s still happening.”
 I’d turn that into a first-response checklist, mitigation FAQs, emergency Google/social posts, customer follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
@@ -349,68 +420,6 @@
   </si>
   <si>
     <t>https://www.google.com/search?q=Any+Hour+Water+and+Fire+San+Jose</t>
-  </si>
-  <si>
-    <t>South Bay Roofing CO</t>
-  </si>
-  <si>
-    <t>Official site updated within days: free inspection, roof/attic/flashing/gutter assessment, same-day itemized written quote, financing options and emergency roofing calls anytime.</t>
-  </si>
-  <si>
-    <t>(650) 447-1464</t>
-  </si>
-  <si>
-    <t>Emergency calls anytime; regular Mon–Sat</t>
-  </si>
-  <si>
-    <t>Use the no-pressure inspection + same-day itemized quote as a trust/decision campaign.</t>
-  </si>
-  <si>
-    <t>Turn your same-day roofing quote into a follow-up system</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed South Bay Roofing’s current San Jose process and think the best campaign is already inside the way you sell:
-“Free inspection. Same-day itemized quote. No-pressure decision.”
-I’d turn that into inspection education, estimate follow-ups, repair-vs-replacement FAQs, financing objection responses and seasonal Google/social posts.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want two South Bay Roofing-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.southbayroofingco.com/</t>
-  </si>
-  <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>HVAC</t>
-  </si>
-  <si>
-    <t>Official pages remain current: financing subject to approval, free estimates, direct email with stated one-business-hour reply, plus a current same-day-service landing page crawled today.</t>
-  </si>
-  <si>
-    <t>(408) 629-5400</t>
-  </si>
-  <si>
-    <t>info@thermatechhvac.com</t>
-  </si>
-  <si>
-    <t>Regular office closed Sunday; same-day landing page active</t>
-  </si>
-  <si>
-    <t>Combine financing and same-day repair/installation messaging into plain-English decision support.</t>
-  </si>
-  <si>
-    <t>Idea for Therma Tech’s financing + same-day traffic</t>
-  </si>
-  <si>
-    <t>Hi — I checked Therma Tech’s current financing and same-day service pages today and there’s a useful customer question connecting both:
-“Can I solve the HVAC problem now without taking the entire cost at once?”
-I’d turn that into financing FAQs, same-day service posts, estimate follow-ups, objection responses and customer reactivation copy.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want two Therma Tech-specific samples first?</t>
-  </si>
-  <si>
-    <t>https://thermatechhvac.com/financing</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -590,6 +599,9 @@
   </si>
   <si>
     <t>CostLess Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
   </si>
   <si>
     <t>Los Gatos Roofing</t>
@@ -1339,19 +1351,19 @@
         <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1365,10 +1377,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1377,26 +1389,28 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -1410,38 +1424,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="I5" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1455,38 +1471,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1500,38 +1516,38 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1545,40 +1561,38 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>80</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1592,38 +1606,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1637,10 +1651,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -1649,26 +1663,26 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1682,40 +1696,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1760,142 +1772,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1925,55 +1937,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2043,18 +2055,18 @@
         <v>27</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2078,18 +2090,18 @@
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2113,18 +2125,18 @@
         <v>27</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2148,18 +2160,18 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2183,18 +2195,18 @@
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2218,18 +2230,18 @@
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2253,18 +2265,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2288,18 +2300,18 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2323,7 +2335,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2371,30 +2383,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2408,13 +2420,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2428,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2448,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2468,13 +2480,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2488,13 +2500,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2508,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -2540,10 +2552,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2560,7 +2572,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2571,149 +2583,149 @@
         <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2747,7 +2759,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2756,17 +2768,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2778,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2787,14 +2799,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2803,14 +2815,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2819,14 +2831,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2835,7 +2847,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2844,7 +2856,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -2870,90 +2882,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2972,19 +2984,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3001,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="225">
   <si>
     <t>Rank</t>
   </si>
@@ -617,6 +617,9 @@
   </si>
   <si>
     <t>911 Restoration of San Jose</t>
+  </si>
+  <si>
+    <t>South Bay Roofing CO</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -2371,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2523,6 +2526,26 @@
         <v>175</v>
       </c>
       <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3">
+        <v>150</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2552,10 +2575,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2572,7 +2595,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2589,7 +2612,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2606,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2623,7 +2646,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2640,7 +2663,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2657,7 +2680,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2674,7 +2697,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2691,7 +2714,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2708,7 +2731,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2725,7 +2748,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2759,7 +2782,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2768,17 +2791,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2790,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2799,14 +2822,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2815,14 +2838,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2831,14 +2854,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2847,7 +2870,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2882,90 +2905,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2984,19 +3007,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3010,10 +3033,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="228">
   <si>
     <t>Rank</t>
   </si>
@@ -84,7 +84,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page is current: Mon–Fri 7:00 AM–5:30 PM, info@thermatechhvac.com, and a stated reply within 1 business hour. Current site also promotes flexible financing for new systems.</t>
+    <t>Official site is current today: Mon–Fri 7:00 AM–5:30 PM, info@thermatechhvac.com, same-day appointments, flexible financing, and a published contact expectation of a reply within one business hour.</t>
   </si>
   <si>
     <t>(408) 629-5400</t>
@@ -93,16 +93,16 @@
     <t>info@thermatechhvac.com</t>
   </si>
   <si>
-    <t>Monday open; email reply target within 1 business hour</t>
+    <t>Monday open; direct email; published reply target within 1 business hour</t>
   </si>
   <si>
     <t>Turn financing and same-day HVAC decision friction into plain-English cost/option education.</t>
   </si>
   <si>
-    <t>Idea for Therma Tech’s financing traffic</t>
-  </si>
-  <si>
-    <t>Hi — I checked Therma Tech’s current financing and contact pages today and noticed you publish a one-business-hour email response target.
+    <t>Idea for Therma Tech’s financing + same-day traffic</t>
+  </si>
+  <si>
+    <t>Hi — I checked Therma Tech’s current financing and same-day service pages today and noticed you publish a one-business-hour email response target.
 I think there’s a strong customer question to build around:
 “Can I solve the HVAC problem now without taking the entire replacement cost at once?”
 I’d turn that into financing FAQs, Google/social posts, estimate follow-ups, objection responses and customer reactivation copy.
@@ -110,7 +110,7 @@
 Want me to send two Therma Tech-specific examples first?</t>
   </si>
   <si>
-    <t>https://thermatechhvac.com/contact</t>
+    <t>https://thermatechhvac.com/</t>
   </si>
   <si>
     <t>2026-09-07</t>
@@ -125,7 +125,7 @@
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 response, 60-minute arrival target, service@leaderestoration.com, and direct insurance billing.</t>
+    <t>September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 response, a 60-minute arrival target, service@leaderestoration.com, and direct insurance billing.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -157,10 +157,10 @@
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
-    <t>Water / Mold Restoration</t>
-  </si>
-  <si>
-    <t>Official San Jose page was crawled today and publishes 24/7 emergency response, free inspections, roughly 45-minute response in many ZIP codes, moisture mapping/documentation, and service@flooddrywdr.com. Contact page shows customer reviews from 3 and 5 days ago.</t>
+    <t>Water / Mold / Fire Restoration</t>
+  </si>
+  <si>
+    <t>Official site was crawled today and publishes 24/7 emergency response, free inspections, roughly 45-minute response in many ZIP codes, service@flooddrywdr.com, claim-ready documentation, and a customer review posted within the last week.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -169,7 +169,7 @@
     <t>service@flooddrywdr.com</t>
   </si>
   <si>
-    <t>24/7; direct email; recent customer activity</t>
+    <t>24/7; direct email; fresh customer activity</t>
   </si>
   <si>
     <t>Translate moisture mapping, drying logs and insurance documentation into urgent plain-English education.</t>
@@ -178,7 +178,7 @@
     <t>Customer-education idea for FloodDry’s free inspection</t>
   </si>
   <si>
-    <t>Hi — I reviewed FloodDry’s current San Jose service process today and found a strong customer-education angle:
+    <t>Hi — I reviewed FloodDry’s current San Jose process today and found a strong customer-education angle:
 “The floor can look dry while moisture is still inside the structure.”
 Your published process already supports that message with moisture readings, structural drying, drying logs and insurance documentation.
 I’d turn it into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
@@ -189,16 +189,123 @@
     <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
   </si>
   <si>
+    <t>The Roofer Bros</t>
+  </si>
+  <si>
+    <t>Roofing / Home Improvement</t>
+  </si>
+  <si>
+    <t>Bay Area / San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official Bay Area page is current with a 5-minute response claim, same-day estimates, free roof inspections/estimates, contact@therooferbros.com, financing as low as $149/month, and a current roof-replacement special.</t>
+  </si>
+  <si>
+    <t>(669) 369-3181</t>
+  </si>
+  <si>
+    <t>contact@therooferbros.com</t>
+  </si>
+  <si>
+    <t>Direct email; published 5-minute response; same-day estimate CTA</t>
+  </si>
+  <si>
+    <t>Turn fast response + free inspection + financing into a low-friction roof-decision campaign.</t>
+  </si>
+  <si>
+    <t>Idea for your 5-minute roofing response funnel</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed The Roofer Bros’ current Bay Area page today and your strongest sales story may be the speed of the decision path itself:
+“Fast response, free inspection, real scope, then financing if the project needs it.”
+I’d turn that into inspection posts, financing FAQs, same-day estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Roofer Bros-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://bay-area.therooferbros.com/</t>
+  </si>
+  <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
+    <t>Roofing</t>
+  </si>
+  <si>
+    <t>Official site was crawled today and publishes free written estimates, same-day leak help when available, roofbytom@gmail.com, same-day callbacks on most estimate requests, and financing for up to 100% of qualifying replacement projects with same-day approvals.</t>
+  </si>
+  <si>
+    <t>(925) 488-1882</t>
+  </si>
+  <si>
+    <t>roofbytom@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day callbacks on most estimate requests</t>
+  </si>
+  <si>
+    <t>Use the inspection → written scope → financing path to reduce replacement uncertainty.</t>
+  </si>
+  <si>
+    <t>Idea for Roof By Tom’s same-day estimate flow</t>
+  </si>
+  <si>
+    <t>Hi — I checked Roof By Tom’s current estimate and financing pages today and noticed you emphasize same-day callbacks on most estimate requests.
+Campaign angle:
+“First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.”
+I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups, financing education and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Roof By Tom-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofbytom.com/</t>
+  </si>
+  <si>
+    <t>FairPrice Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>HVAC / Insulation / Indoor Air Quality</t>
+  </si>
+  <si>
+    <t>Santa Clara / San Jose area, CA</t>
+  </si>
+  <si>
+    <t>Official site is current with September specials expiring Sep 30, 24/7 availability, same-day service, financing, a $299 air-duct-cleaning offer, and direct email info@fairpriceheatingandcooling.com.</t>
+  </si>
+  <si>
+    <t>(669) 282-6453</t>
+  </si>
+  <si>
+    <t>info@fairpriceheatingandcooling.com</t>
+  </si>
+  <si>
+    <t>24/7; direct email; active September specials</t>
+  </si>
+  <si>
+    <t>Turn the expiring September specials into a cross-service HVAC + air-quality campaign.</t>
+  </si>
+  <si>
+    <t>2 ideas for FairPrice’s September specials</t>
+  </si>
+  <si>
+    <t>Hi — I checked FairPrice’s current site today and saw the September specials are live through September 30, including the air-duct-cleaning offer.
+I think there’s a stronger campaign than simply repeating the coupon:
+“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
+I’d turn that into Google/social posts, FAQs, offer reminders, follow-ups and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two FairPrice-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://fairpriceheatingandcooling.com/</t>
+  </si>
+  <si>
     <t>ROOF EXPRESS</t>
   </si>
   <si>
-    <t>Roofing</t>
-  </si>
-  <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>Official contact page publishes sales@roof-ex.com, phone/WhatsApp responses typically within minutes during business hours, free no-obligation roof inspections, and email replies within one business day. Current San Jose page adds photo documentation, financing up to $25,000 and 24/7 emergency roofing.</t>
+    <t>Current official pages publish sales@roof-ex.com, free estimates, same-day inspections Mon–Sat, photo-supported line-item scopes, financing up to $25,000, and 24/7 emergency roofing.</t>
   </si>
   <si>
     <t>(650) 666-5554</t>
@@ -207,7 +314,7 @@
     <t>sales@roof-ex.com</t>
   </si>
   <si>
-    <t>Mon–Fri 7–7; phone/WhatsApp typically answered within minutes</t>
+    <t>Direct email; Monday business hours; emergency 24/7</t>
   </si>
   <si>
     <t>Market the transparent inspection → photo evidence → line-item scope → financing decision path.</t>
@@ -216,14 +323,14 @@
     <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose and contact pages today. Your inspection process gives you a stronger customer story than another generic roofing ad:
+    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose process today. Your inspection flow gives you a stronger customer story than another generic roofing ad:
 “See what the roof needs, what it costs and what the financing options are before deciding.”
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Complete Same-Day Customer Growth Pack: $150 flat.
 Want two ROOF EXPRESS-specific examples first?</t>
   </si>
   <si>
-    <t>https://quote.roof-ex.com/contact/</t>
+    <t>https://roof-ex.com/san-jose</t>
   </si>
   <si>
     <t>IRBIS Air Plumbing Electrical</t>
@@ -232,13 +339,13 @@
     <t>HVAC / Plumbing / Electrical</t>
   </si>
   <si>
-    <t>Official site was crawled yesterday and promotes same-day San Jose HVAC/plumbing/electrical service, 40+ trucks, free estimates, and Monday-Friday same-day dispatch with a 24/7 support line. A current official rebate page publishes (408) 317-3901.</t>
-  </si>
-  <si>
-    <t>(408) 317-3901</t>
-  </si>
-  <si>
-    <t>Monday same-day service; 24/7 support line</t>
+    <t>Official site was crawled yesterday and promotes same-day HVAC, plumbing and electrical service in San Jose, with multiple trades under one license and same-day availability for breakdowns.</t>
+  </si>
+  <si>
+    <t>(669) 266-5464</t>
+  </si>
+  <si>
+    <t>Monday same-day service; phone contact</t>
   </si>
   <si>
     <t>Build one-home-one-team messaging around problems that cross HVAC, plumbing and electrical.</t>
@@ -258,37 +365,6 @@
     <t>https://www.irbishvac.com/</t>
   </si>
   <si>
-    <t>California Water and Fire</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Reconstruction</t>
-  </si>
-  <si>
-    <t>Official San Jose page advertises 24/7 live dispatch, a 45-minute local response target, free inspection, direct insurance billing, no upfront cost on covered claims, and restoration through reconstruction.</t>
-  </si>
-  <si>
-    <t>(408) 402-4941</t>
-  </si>
-  <si>
-    <t>24/7 live dispatch</t>
-  </si>
-  <si>
-    <t>Turn emergency response + insurance handling + rebuild capability into one clear first-call workflow.</t>
-  </si>
-  <si>
-    <t>San Jose restoration campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I checked your San Jose restoration page today and the strongest customer story looks bigger than “24/7 restoration”:
-“From the emergency call to the rebuild, one team keeps the loss moving.”
-I’d turn your live-dispatch, insurance-documentation and reconstruction process into emergency posts, customer FAQs, first-response follow-ups and commercial restoration messaging.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want two California Water and Fire-specific samples first?</t>
-  </si>
-  <si>
-    <t>https://cawaterandfire.com/san-jose/</t>
-  </si>
-  <si>
     <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
@@ -298,24 +374,24 @@
     <t>Sunnyvale / San Jose, CA</t>
   </si>
   <si>
-    <t>Official site was crawled yesterday and publishes free inspections, same-day roof inspections, Mon–Sat 8 AM–8 PM, emergency calls 24/7, 50-year warranty availability, and roofs starting at $12,000.</t>
+    <t>Official site was crawled yesterday and publishes free/same-day roof inspections, emergency availability, and a current September storm-readiness inspection campaign ahead of rainy season.</t>
   </si>
   <si>
     <t>(408) 685-2177</t>
   </si>
   <si>
-    <t>Monday 8 AM–8 PM; emergency calls 24/7</t>
-  </si>
-  <si>
-    <t>Use same-day inspections and high-ticket roof decisions to create a pre-rain inspection + estimate follow-up sequence.</t>
-  </si>
-  <si>
-    <t>Idea for Lifetime’s same-day inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked Lifetime’s current San Jose roofing page today and your same-day inspection offer gives you a strong customer campaign:
+    <t>Monday; same-day inspections; emergency calls</t>
+  </si>
+  <si>
+    <t>Use same-day inspections and rainy-season readiness to create a pre-rain inspection + estimate follow-up sequence.</t>
+  </si>
+  <si>
+    <t>Idea for Lifetime’s September inspection campaign</t>
+  </si>
+  <si>
+    <t>Hi — I checked Lifetime’s current September roof-inspection messaging today and there’s a strong campaign inside the offer:
 “The first rain shouldn’t be the first time you learn where the roof is vulnerable.”
-I’d turn that into roof-and-drainage education, Google/social posts, inspection reminders, estimate follow-ups and repair-vs-replacement FAQs.
+I’d turn the free inspection into roof-and-drainage education, Google/social posts, inspection reminders, estimate follow-ups and repair-vs-replacement FAQs.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Lifetime-specific examples first?</t>
   </si>
@@ -332,13 +408,13 @@
     <t>Campbell / San Jose, CA</t>
   </si>
   <si>
-    <t>Official pages remain current and combine solar, roofing and electrical under one contractor, with free estimates and a Campbell contact number. Current business listing shows Monday hours through 7 PM.</t>
+    <t>Official pages remain current and combine solar, roofing and electrical in-house, with free estimates and a published San Jose/South Bay phone line.</t>
   </si>
   <si>
     <t>(408) 583-8101</t>
   </si>
   <si>
-    <t>Monday; official Campbell line; current listing open through 7 PM</t>
+    <t>Monday; official South Bay contact line</t>
   </si>
   <si>
     <t>Use pre-solar roof/electrical readiness and bundled project coordination as the campaign.</t>
@@ -354,72 +430,7 @@
 Want two Infinium-specific samples first?</t>
   </si>
   <si>
-    <t>https://infinium.inc/campbell-ca/</t>
-  </si>
-  <si>
-    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Waterproofing</t>
-  </si>
-  <si>
-    <t>Official site was crawled within the last week and promotes free estimates, emergency leak help, financing, repair-vs-replacement education, detailed written quotes, and 100% roof-replacement financing. Monday hours are 8:30 AM–5 PM.</t>
-  </si>
-  <si>
-    <t>(408) 971-9000</t>
-  </si>
-  <si>
-    <t>Monday 8:30 AM–5 PM</t>
-  </si>
-  <si>
-    <t>Turn its explicit “we won’t sell you a roof you don’t need” positioning into a repair-vs-replacement trust campaign.</t>
-  </si>
-  <si>
-    <t>Repair-vs-replacement campaign idea for Eastman</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Eastman’s current site today and your “we won’t sell you a roof you don’t need” pledge is a strong campaign idea on its own:
-“Before replacing the roof, find out whether the problem can actually be repaired.”
-I’d turn that into repair-vs-replacement FAQs, inspection education, financing objection responses, estimate follow-ups and homeowner trust content.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Eastman-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.eastmanroofing.com/</t>
-  </si>
-  <si>
-    <t>Any Hour Water and Fire</t>
-  </si>
-  <si>
-    <t>Water / Fire Restoration</t>
-  </si>
-  <si>
-    <t>San Jose area</t>
-  </si>
-  <si>
-    <t>Current business listing shows Monday 8 AM–5 PM, a 5.0 rating with 296 reviews, and emergency mitigation, drying, cleanup and rebuild positioning.</t>
-  </si>
-  <si>
-    <t>(669) 304-3545</t>
-  </si>
-  <si>
-    <t>Monday 8 AM–5 PM</t>
-  </si>
-  <si>
-    <t>Lead with mitigation-first education before reconstruction and insurance complexity.</t>
-  </si>
-  <si>
-    <t>Mitigation-first campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I was refreshing San Jose restoration companies today and Any Hour stood out for a simple customer-education campaign:
-“Before worrying about rebuilding, stop the damage that’s still happening.”
-I’d turn that into a first-response checklist, mitigation FAQs, emergency Google/social posts, customer follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Any Hour-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.google.com/search?q=Any+Hour+Water+and+Fire+San+Jose</t>
+    <t>https://infinium.inc/solar/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -1480,7 +1491,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -1491,21 +1502,23 @@
       <c r="G6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="I6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1519,38 +1532,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1564,38 +1579,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1609,38 +1626,38 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1654,38 +1671,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1699,38 +1716,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1775,142 +1792,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1940,55 +1957,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2139,7 +2156,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2163,18 +2180,18 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2198,18 +2215,18 @@
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2233,18 +2250,18 @@
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2268,18 +2285,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2303,18 +2320,18 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2338,7 +2355,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2386,30 +2403,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2423,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2443,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2463,13 +2480,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2483,13 +2500,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2503,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2523,13 +2540,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2575,10 +2592,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2595,7 +2612,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2612,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2629,7 +2646,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2646,7 +2663,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2657,98 +2674,98 @@
         <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2782,7 +2799,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2791,17 +2808,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2813,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2822,14 +2839,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2838,14 +2855,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2854,14 +2871,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2870,7 +2887,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2879,7 +2896,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -2905,90 +2922,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3007,19 +3024,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3036,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="231">
   <si>
     <t>Rank</t>
   </si>
@@ -630,7 +630,16 @@
     <t>911 Restoration of San Jose</t>
   </si>
   <si>
+    <t>Any Hour Water and Fire</t>
+  </si>
+  <si>
+    <t>California Water and Fire</t>
+  </si>
+  <si>
     <t>South Bay Roofing CO</t>
+  </si>
+  <si>
+    <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -2391,7 +2400,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2563,6 +2572,66 @@
         <v>27</v>
       </c>
       <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3">
+        <v>150</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3">
+        <v>150</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3">
+        <v>150</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2592,10 +2661,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2612,7 +2681,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2629,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2646,7 +2715,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2663,7 +2732,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2680,7 +2749,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2697,7 +2766,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2714,7 +2783,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2731,7 +2800,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2748,7 +2817,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2765,7 +2834,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2799,7 +2868,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2808,17 +2877,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2830,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2839,14 +2908,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2855,14 +2924,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2871,14 +2940,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2887,7 +2956,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2922,90 +2991,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3024,19 +3093,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3050,10 +3119,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="234">
   <si>
     <t>Rank</t>
   </si>
@@ -116,7 +116,7 @@
     <t>2026-09-07</t>
   </si>
   <si>
-    <t>Contact Ready</t>
+    <t>Contacted</t>
   </si>
   <si>
     <t>Leader Restoration</t>
@@ -154,6 +154,9 @@
     <t>https://call.leaderestoration.com/mold-408</t>
   </si>
   <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
     <t>FloodDry Water Damage Restoration</t>
   </si>
   <si>
@@ -606,6 +609,15 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-09-07T13:34:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>Wait for a genuine reply; if none, send one respectful follow-up on 2026-09-09.</t>
+  </si>
+  <si>
     <t>Archived</t>
   </si>
   <si>
@@ -661,9 +673,6 @@
   </si>
   <si>
     <t>Revenue Metric</t>
-  </si>
-  <si>
-    <t>Contacted</t>
   </si>
   <si>
     <t>Replied</t>
@@ -1392,7 +1401,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1400,10 +1409,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -1412,34 +1421,34 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1447,46 +1456,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1494,46 +1503,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1541,46 +1550,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1588,46 +1597,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1635,10 +1644,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>17</v>
@@ -1647,32 +1656,32 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1680,44 +1689,44 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1725,44 +1734,44 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1801,142 +1810,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1966,55 +1975,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2027,8 +2036,12 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2043,7 +2056,9 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>27</v>
@@ -2069,7 +2084,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K3" s="3">
         <v>150</v>
@@ -2089,13 +2104,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2104,7 +2119,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K4" s="3">
         <v>150</v>
@@ -2119,18 +2134,18 @@
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2139,7 +2154,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K5" s="3">
         <v>150</v>
@@ -2154,18 +2169,18 @@
         <v>27</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2174,7 +2189,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K6" s="3">
         <v>150</v>
@@ -2189,18 +2204,18 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2209,7 +2224,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K7" s="3">
         <v>150</v>
@@ -2224,18 +2239,18 @@
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2244,7 +2259,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K8" s="3">
         <v>150</v>
@@ -2259,18 +2274,18 @@
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2279,7 +2294,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K9" s="3">
         <v>150</v>
@@ -2294,18 +2309,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2314,7 +2329,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K10" s="3">
         <v>150</v>
@@ -2329,18 +2344,18 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2349,7 +2364,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2364,7 +2379,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2412,33 +2427,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2449,16 +2464,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2469,16 +2484,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2489,16 +2504,16 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -2509,16 +2524,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2529,16 +2544,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -2549,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2575,10 +2590,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2595,10 +2610,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2615,10 +2630,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2661,10 +2676,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2681,7 +2696,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2698,143 +2713,143 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2868,7 +2883,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2877,29 +2892,29 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2908,14 +2923,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2924,14 +2939,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2940,14 +2955,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2956,7 +2971,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2965,7 +2980,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -2991,90 +3006,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3093,19 +3108,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3122,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="236">
   <si>
     <t>Rank</t>
   </si>
@@ -72,10 +72,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>HVAC</t>
+    <t>FloodDry Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>Water / Mold / Fire Restoration</t>
   </si>
   <si>
     <t>San Jose, CA</t>
@@ -84,39 +84,39 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official site is current today: Mon–Fri 7:00 AM–5:30 PM, info@thermatechhvac.com, same-day appointments, flexible financing, and a published contact expectation of a reply within one business hour.</t>
-  </si>
-  <si>
-    <t>(408) 629-5400</t>
-  </si>
-  <si>
-    <t>info@thermatechhvac.com</t>
-  </si>
-  <si>
-    <t>Monday open; direct email; published reply target within 1 business hour</t>
-  </si>
-  <si>
-    <t>Turn financing and same-day HVAC decision friction into plain-English cost/option education.</t>
-  </si>
-  <si>
-    <t>Idea for Therma Tech’s financing + same-day traffic</t>
-  </si>
-  <si>
-    <t>Hi — I checked Therma Tech’s current financing and same-day service pages today and noticed you publish a one-business-hour email response target.
-I think there’s a strong customer question to build around:
-“Can I solve the HVAC problem now without taking the entire replacement cost at once?”
-I’d turn that into financing FAQs, Google/social posts, estimate follow-ups, objection responses and customer reactivation copy.
+    <t>Official pages are current today: 24/7 emergency response, free inspections, roughly 45-minute response in many San Jose ZIP codes, direct email service@flooddrywdr.com, claim-ready documentation, and fresh customer reviews posted 3 and 5 days ago.</t>
+  </si>
+  <si>
+    <t>(408) 404-4000</t>
+  </si>
+  <si>
+    <t>service@flooddrywdr.com</t>
+  </si>
+  <si>
+    <t>24/7; direct email; real-person response; fresh customer activity</t>
+  </si>
+  <si>
+    <t>Translate hidden moisture, drying logs and insurance documentation into urgent plain-English education.</t>
+  </si>
+  <si>
+    <t>Customer-education idea for FloodDry’s free inspection</t>
+  </si>
+  <si>
+    <t>Hi — I checked FloodDry’s current San Jose service process today and noticed you’re still offering 24/7 response and free inspections.
+I think there’s a strong customer-education angle inside your existing process:
+“The floor can look dry while moisture is still inside the structure.”
+Your moisture readings, drying logs and insurance documentation already support that story. I’d turn it into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat, no subscription.
-Want me to send two Therma Tech-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://thermatechhvac.com/</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>Contacted</t>
+Want me to send two FloodDry-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
   </si>
   <si>
     <t>Leader Restoration</t>
@@ -125,7 +125,7 @@
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 response, a 60-minute arrival target, service@leaderestoration.com, and direct insurance billing.</t>
+    <t>The September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 emergency response, a 60-minute arrival target, direct email service@leaderestoration.com, and a San Jose office.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -134,7 +134,7 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email</t>
+    <t>24/7; direct email; active Sep 30 deadline</t>
   </si>
   <si>
     <t>Use the expiring September inspection as customer education about hidden moisture and mold risk.</t>
@@ -154,42 +154,80 @@
     <t>https://call.leaderestoration.com/mold-408</t>
   </si>
   <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>FloodDry Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>Water / Mold / Fire Restoration</t>
-  </si>
-  <si>
-    <t>Official site was crawled today and publishes 24/7 emergency response, free inspections, roughly 45-minute response in many ZIP codes, service@flooddrywdr.com, claim-ready documentation, and a customer review posted within the last week.</t>
-  </si>
-  <si>
-    <t>(408) 404-4000</t>
-  </si>
-  <si>
-    <t>service@flooddrywdr.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; fresh customer activity</t>
-  </si>
-  <si>
-    <t>Translate moisture mapping, drying logs and insurance documentation into urgent plain-English education.</t>
-  </si>
-  <si>
-    <t>Customer-education idea for FloodDry’s free inspection</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed FloodDry’s current San Jose process today and found a strong customer-education angle:
-“The floor can look dry while moisture is still inside the structure.”
-Your published process already supports that message with moisture readings, structural drying, drying logs and insurance documentation.
-I’d turn it into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want me to send two FloodDry-specific samples first?</t>
-  </si>
-  <si>
-    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
+    <t>FairPrice Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>HVAC / Insulation / Indoor Air Quality</t>
+  </si>
+  <si>
+    <t>Santa Clara / San Jose area, CA</t>
+  </si>
+  <si>
+    <t>Official pages currently publish 24/7 availability, direct email info@fairpriceheatingandcooling.com, a $299 air-duct-cleaning offer, and Hello Fall September specials expiring Sep 30, 2026.</t>
+  </si>
+  <si>
+    <t>(669) 282-6453</t>
+  </si>
+  <si>
+    <t>info@fairpriceheatingandcooling.com</t>
+  </si>
+  <si>
+    <t>24/7; direct email; active September specials</t>
+  </si>
+  <si>
+    <t>Turn the expiring September specials into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
+  </si>
+  <si>
+    <t>2 ideas for FairPrice’s September specials</t>
+  </si>
+  <si>
+    <t>Hi — I checked FairPrice’s current site today and saw the September specials are still live through September 30, including the $299 air-duct-cleaning offer.
+I think there’s a stronger campaign than simply repeating the coupon:
+“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
+I’d turn that into Google/social posts, FAQs, offer reminders, customer follow-ups and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat, no subscription.
+Want two FairPrice-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://fairpriceheatingandcooling.com/</t>
+  </si>
+  <si>
+    <t>Dansel Restoration</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Reconstruction</t>
+  </si>
+  <si>
+    <t>San Jose / Fremont, CA</t>
+  </si>
+  <si>
+    <t>New high-priority lead: official pages publish 24/7 emergency response, direct email help@danselrestoration.com, free assessments, same-day mold response, insurance assistance, in-house mitigation plus reconstruction, and a promise to reach out within the hour on its main contact flow.</t>
+  </si>
+  <si>
+    <t>(408) 564-0152</t>
+  </si>
+  <si>
+    <t>help@danselrestoration.com</t>
+  </si>
+  <si>
+    <t>24/7; direct email; published within-hour callback</t>
+  </si>
+  <si>
+    <t>Turn its mitigation-to-reconstruction continuity and free assessment into a first-hour emergency decision campaign.</t>
+  </si>
+  <si>
+    <t>First-hour restoration campaign idea for Dansel</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today and noticed you handle both emergency mitigation and reconstruction in-house, with a free assessment and 24/7 response.
+That gives you a strong customer message:
+“The first hour is about stopping the damage. The next steps should not require starting over with another contractor.”
+I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Dansel-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://danselrestoration.com/</t>
   </si>
   <si>
     <t>The Roofer Bros</t>
@@ -201,7 +239,7 @@
     <t>Bay Area / San Jose, CA</t>
   </si>
   <si>
-    <t>Official Bay Area page is current with a 5-minute response claim, same-day estimates, free roof inspections/estimates, contact@therooferbros.com, financing as low as $149/month, and a current roof-replacement special.</t>
+    <t>Official Bay Area page is current today with direct email contact@therooferbros.com, a 5-minute response claim, same-day estimate CTA, free inspections, financing from $149/month, often same-day financing approvals, and a current 10%-off roof-replacement special.</t>
   </si>
   <si>
     <t>(669) 369-3181</t>
@@ -219,7 +257,7 @@
     <t>Idea for your 5-minute roofing response funnel</t>
   </si>
   <si>
-    <t>Hi — I reviewed The Roofer Bros’ current Bay Area page today and your strongest sales story may be the speed of the decision path itself:
+    <t>Hi — I reviewed The Roofer Bros’ Bay Area page today and your strongest sales story may be the speed of the decision path itself:
 “Fast response, free inspection, real scope, then financing if the project needs it.”
 I’d turn that into inspection posts, financing FAQs, same-day estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
@@ -235,7 +273,7 @@
     <t>Roofing</t>
   </si>
   <si>
-    <t>Official site was crawled today and publishes free written estimates, same-day leak help when available, roofbytom@gmail.com, same-day callbacks on most estimate requests, and financing for up to 100% of qualifying replacement projects with same-day approvals.</t>
+    <t>Official pages remain current: free written estimates, same-day leak help when available, direct email roofbytom@gmail.com, same-day callbacks on most estimate requests, and financing up to 100% of qualifying replacement projects with same-day approvals.</t>
   </si>
   <si>
     <t>(925) 488-1882</t>
@@ -247,7 +285,7 @@
     <t>Direct email; same-day callbacks on most estimate requests</t>
   </si>
   <si>
-    <t>Use the inspection → written scope → financing path to reduce replacement uncertainty.</t>
+    <t>Use the inspection → written scope → repair/replacement/financing decision path to reduce uncertainty.</t>
   </si>
   <si>
     <t>Idea for Roof By Tom’s same-day estimate flow</t>
@@ -264,51 +302,13 @@
     <t>https://roofbytom.com/</t>
   </si>
   <si>
-    <t>FairPrice Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>HVAC / Insulation / Indoor Air Quality</t>
-  </si>
-  <si>
-    <t>Santa Clara / San Jose area, CA</t>
-  </si>
-  <si>
-    <t>Official site is current with September specials expiring Sep 30, 24/7 availability, same-day service, financing, a $299 air-duct-cleaning offer, and direct email info@fairpriceheatingandcooling.com.</t>
-  </si>
-  <si>
-    <t>(669) 282-6453</t>
-  </si>
-  <si>
-    <t>info@fairpriceheatingandcooling.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; active September specials</t>
-  </si>
-  <si>
-    <t>Turn the expiring September specials into a cross-service HVAC + air-quality campaign.</t>
-  </si>
-  <si>
-    <t>2 ideas for FairPrice’s September specials</t>
-  </si>
-  <si>
-    <t>Hi — I checked FairPrice’s current site today and saw the September specials are live through September 30, including the air-duct-cleaning offer.
-I think there’s a stronger campaign than simply repeating the coupon:
-“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
-I’d turn that into Google/social posts, FAQs, offer reminders, follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two FairPrice-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://fairpriceheatingandcooling.com/</t>
-  </si>
-  <si>
     <t>ROOF EXPRESS</t>
   </si>
   <si>
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>Current official pages publish sales@roof-ex.com, free estimates, same-day inspections Mon–Sat, photo-supported line-item scopes, financing up to $25,000, and 24/7 emergency roofing.</t>
+    <t>Official pages publish sales@roof-ex.com, phone/WhatsApp response within minutes during business hours, email response within one business day, free inspections, same-day inspections Mon–Sat, photo-supported digital scopes, and financing up to $25,000 with $0 down.</t>
   </si>
   <si>
     <t>(650) 666-5554</t>
@@ -317,7 +317,7 @@
     <t>sales@roof-ex.com</t>
   </si>
   <si>
-    <t>Direct email; Monday business hours; emergency 24/7</t>
+    <t>Direct email; phone/WhatsApp typically minutes in business hours; email within 1 business day</t>
   </si>
   <si>
     <t>Market the transparent inspection → photo evidence → line-item scope → financing decision path.</t>
@@ -326,14 +326,14 @@
     <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose process today. Your inspection flow gives you a stronger customer story than another generic roofing ad:
+    <t>Hi — I reviewed ROOF EXPRESS’s current estimate and financing process today. Your inspection flow gives you a stronger story than another generic roofing ad:
 “See what the roof needs, what it costs and what the financing options are before deciding.”
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Complete Same-Day Customer Growth Pack: $150 flat.
 Want two ROOF EXPRESS-specific examples first?</t>
   </si>
   <si>
-    <t>https://roof-ex.com/san-jose</t>
+    <t>https://quote.roof-ex.com/contact/</t>
   </si>
   <si>
     <t>IRBIS Air Plumbing Electrical</t>
@@ -342,22 +342,22 @@
     <t>HVAC / Plumbing / Electrical</t>
   </si>
   <si>
-    <t>Official site was crawled yesterday and promotes same-day HVAC, plumbing and electrical service in San Jose, with multiple trades under one license and same-day availability for breakdowns.</t>
-  </si>
-  <si>
-    <t>(669) 266-5464</t>
-  </si>
-  <si>
-    <t>Monday same-day service; phone contact</t>
-  </si>
-  <si>
-    <t>Build one-home-one-team messaging around problems that cross HVAC, plumbing and electrical.</t>
+    <t>Official site is current today: same-day HVAC/plumbing/electrical service, most calls before noon eligible for same-day visits, a 24/7 customer support line, free estimates, 10% off first service, and multi-trade home-care/rebate messaging.</t>
+  </si>
+  <si>
+    <t>+1 408-317-3919</t>
+  </si>
+  <si>
+    <t>Open 24/7 in current listing; official site advertises same-day service and 24/7 support</t>
+  </si>
+  <si>
+    <t>Build one-home-one-team messaging around same-day problems that cross HVAC, plumbing and electrical.</t>
   </si>
   <si>
     <t>One campaign across HVAC + plumbing + electrical</t>
   </si>
   <si>
-    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one individual trade — it’s that HVAC, plumbing and electrical sit under one team.
+    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one individual trade — it’s that HVAC, plumbing and electrical sit under one team, with same-day service positioned prominently.
 Campaign angle:
 “One call when the problem crosses systems.”
 I’d turn that into same-day service posts, cross-service homeowner FAQs, missed-inquiry follow-ups, estimate follow-ups and genuine review-request messaging.
@@ -368,72 +368,72 @@
     <t>https://www.irbishvac.com/</t>
   </si>
   <si>
-    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
-  </si>
-  <si>
-    <t>Roofing / Exterior Renovation</t>
-  </si>
-  <si>
-    <t>Sunnyvale / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site was crawled yesterday and publishes free/same-day roof inspections, emergency availability, and a current September storm-readiness inspection campaign ahead of rainy season.</t>
-  </si>
-  <si>
-    <t>(408) 685-2177</t>
-  </si>
-  <si>
-    <t>Monday; same-day inspections; emergency calls</t>
-  </si>
-  <si>
-    <t>Use same-day inspections and rainy-season readiness to create a pre-rain inspection + estimate follow-up sequence.</t>
-  </si>
-  <si>
-    <t>Idea for Lifetime’s September inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked Lifetime’s current September roof-inspection messaging today and there’s a strong campaign inside the offer:
-“The first rain shouldn’t be the first time you learn where the roof is vulnerable.”
-I’d turn the free inspection into roof-and-drainage education, Google/social posts, inspection reminders, estimate follow-ups and repair-vs-replacement FAQs.
+    <t>Infinium Solar, Roofing and Electric</t>
+  </si>
+  <si>
+    <t>Solar / Roofing / Electrical</t>
+  </si>
+  <si>
+    <t>Campbell / San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official site is current today and combines solar, roofing and electrical in-house with free estimates, South Bay service, battery/electrical work, and a current referral program offering a $500 Amazon gift card after a referred solar/battery project is completed and paid.</t>
+  </si>
+  <si>
+    <t>(408) 583-8101</t>
+  </si>
+  <si>
+    <t>Tuesday business hours; official South Bay contact line; free estimates</t>
+  </si>
+  <si>
+    <t>Use pre-solar roof/electrical readiness plus the active referral program as two customer-acquisition angles.</t>
+  </si>
+  <si>
+    <t>Solar + roof + referral campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Infinium’s current service and referral pages today and think you have two unusually strong campaign stories: coordinating solar, roofing and electrical under one team, and the current referral reward.
+The customer-facing angle I’d lead with is:
+“Before installing a long-term solar and battery system, make sure the roof and electrical system underneath it are ready for the same project.”
+I’d turn that into consultation FAQs, readiness posts, estimate follow-ups, referral reminders and cross-service CTAs.
 Same-Day Customer Growth Pack: $150 flat.
-Want two Lifetime-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://lifetimeroofingrenovation.com/</t>
-  </si>
-  <si>
-    <t>Infinium Solar, Roofing and Electric</t>
-  </si>
-  <si>
-    <t>Solar / Roofing / Electrical</t>
-  </si>
-  <si>
-    <t>Campbell / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official pages remain current and combine solar, roofing and electrical in-house, with free estimates and a published San Jose/South Bay phone line.</t>
-  </si>
-  <si>
-    <t>(408) 583-8101</t>
-  </si>
-  <si>
-    <t>Monday; official South Bay contact line</t>
-  </si>
-  <si>
-    <t>Use pre-solar roof/electrical readiness and bundled project coordination as the campaign.</t>
-  </si>
-  <si>
-    <t>Solar + roof + electrical campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Infinium’s current service mix today and think the best campaign is about what has to be ready before solar goes on the roof:
-“Before installing a long-term solar and battery system, make sure the roof and electrical system underneath it are ready for the same project.”
-I’d turn that into consultation FAQs, roof-readiness posts, solar/battery education, estimate follow-ups and cross-service CTAs.
-Complete Same-Day Customer Growth Pack: $150 flat.
-Want two Infinium-specific samples first?</t>
-  </si>
-  <si>
-    <t>https://infinium.inc/solar/</t>
+Want two Infinium-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://infinium.inc/</t>
+  </si>
+  <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>HVAC</t>
+  </si>
+  <si>
+    <t>Already contacted by email on Sep 7; no genuine reply found as of this refresh. Official site remains current with flexible financing, same-day HVAC messaging, free estimates, info@thermatechhvac.com, and Tuesday business hours. First respectful follow-up is due Sep 9 if no reply arrives.</t>
+  </si>
+  <si>
+    <t>(408) 629-5400</t>
+  </si>
+  <si>
+    <t>info@thermatechhvac.com</t>
+  </si>
+  <si>
+    <t>Already contacted Sep 7; follow-up due Sep 9 if no genuine reply</t>
+  </si>
+  <si>
+    <t>Preserve the financing + same-day decision angle; do not resend a new cold opener today.</t>
+  </si>
+  <si>
+    <t>Idea for Therma Tech’s financing + same-day traffic</t>
+  </si>
+  <si>
+    <t>Hi — following up on the financing-content idea I sent. Your site already has the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up. I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
+  </si>
+  <si>
+    <t>https://thermatechhvac.com/</t>
+  </si>
+  <si>
+    <t>Contacted</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t>Any Hour Water and Fire</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>California Water and Fire</t>
@@ -1401,7 +1404,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1409,13 +1412,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
@@ -1448,7 +1451,7 @@
         <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1495,7 +1498,7 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1509,40 +1512,40 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1550,13 +1553,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
@@ -1589,7 +1592,7 @@
         <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1600,7 +1603,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>83</v>
@@ -1636,7 +1639,7 @@
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1681,7 +1684,7 @@
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1726,7 +1729,7 @@
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1740,18 +1743,20 @@
         <v>112</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
         <v>116</v>
       </c>
@@ -1771,7 +1776,7 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1810,142 +1815,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1975,55 +1980,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2036,12 +2041,8 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2056,9 +2057,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>27</v>
@@ -2084,7 +2083,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K3" s="3">
         <v>150</v>
@@ -2104,7 +2103,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -2119,7 +2118,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K4" s="3">
         <v>150</v>
@@ -2154,7 +2153,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K5" s="3">
         <v>150</v>
@@ -2180,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2189,7 +2188,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K6" s="3">
         <v>150</v>
@@ -2204,12 +2203,12 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -2224,7 +2223,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K7" s="3">
         <v>150</v>
@@ -2259,7 +2258,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K8" s="3">
         <v>150</v>
@@ -2294,7 +2293,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K9" s="3">
         <v>150</v>
@@ -2329,7 +2328,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K10" s="3">
         <v>150</v>
@@ -2357,14 +2356,18 @@
       <c r="C11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2373,7 +2376,9 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
@@ -2427,33 +2432,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2464,16 +2469,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2484,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2504,16 +2509,16 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -2524,16 +2529,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2544,16 +2549,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -2564,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2584,16 +2589,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2604,16 +2609,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2624,16 +2629,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2644,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -2676,10 +2681,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2696,7 +2701,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2713,12 +2718,12 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>42</v>
@@ -2730,7 +2735,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2747,7 +2752,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2755,21 +2760,21 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>74</v>
@@ -2781,7 +2786,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2798,7 +2803,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2815,7 +2820,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2832,7 +2837,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2840,7 +2845,7 @@
         <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>120</v>
@@ -2849,7 +2854,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2883,7 +2888,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2892,29 +2897,29 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2923,14 +2928,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2939,14 +2944,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2955,14 +2960,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2971,7 +2976,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -2980,7 +2985,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3006,90 +3011,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -3108,19 +3113,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3137,7 +3142,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="237">
   <si>
     <t>Rank</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>California Water and Fire</t>
+  </si>
+  <si>
+    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
     <t>South Bay Roofing CO</t>
@@ -2420,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2629,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -2652,6 +2655,26 @@
         <v>190</v>
       </c>
       <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3">
+        <v>150</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2681,10 +2704,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2701,7 +2724,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2718,7 +2741,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2735,7 +2758,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2752,7 +2775,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2769,7 +2792,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2786,7 +2809,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2803,7 +2826,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2820,7 +2843,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2837,7 +2860,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2854,7 +2877,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2911,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2897,17 +2920,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2919,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2935,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2944,14 +2967,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2960,14 +2983,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2976,7 +2999,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3011,90 +3034,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3113,19 +3136,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3139,10 +3162,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="238">
   <si>
     <t>Rank</t>
   </si>
@@ -84,7 +84,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official pages are current today: 24/7 emergency response, free inspections, roughly 45-minute response in many San Jose ZIP codes, direct email service@flooddrywdr.com, claim-ready documentation, and fresh customer reviews posted 3 and 5 days ago.</t>
+    <t>Official contact page remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, and fresh customer reviews posted within the past week.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -96,24 +96,24 @@
     <t>24/7; direct email; real-person response; fresh customer activity</t>
   </si>
   <si>
-    <t>Translate hidden moisture, drying logs and insurance documentation into urgent plain-English education.</t>
+    <t>Translate hidden moisture, drying documentation and insurance coordination into urgent plain-English homeowner education.</t>
   </si>
   <si>
     <t>Customer-education idea for FloodDry’s free inspection</t>
   </si>
   <si>
-    <t>Hi — I checked FloodDry’s current San Jose service process today and noticed you’re still offering 24/7 response and free inspections.
-I think there’s a strong customer-education angle inside your existing process:
-“The floor can look dry while moisture is still inside the structure.”
-Your moisture readings, drying logs and insurance documentation already support that story. I’d turn it into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat, no subscription.
+    <t>Hi — I checked FloodDry’s current San Jose contact and restoration messaging today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
+I think there’s a strong customer-education angle inside that process:
+‘The surface can look dry while moisture is still inside the structure.’
+I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
 Want me to send two FloodDry-specific examples first?</t>
   </si>
   <si>
-    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
+    <t>https://flooddrywdr.com/contact/</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>Contact Ready</t>
@@ -125,7 +125,7 @@
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>The September 2026 FREE mold inspection remains live through Sep 30. The official campaign publishes 24/7 emergency response, a 60-minute arrival target, direct email service@leaderestoration.com, and a San Jose office.</t>
+    <t>Official San Jose mold page remains current with a free inspection CTA, 24/7 emergency response, a published 60-minute on-site target, direct email service@leaderestoration.com, and California contractor license information.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -134,20 +134,20 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; active Sep 30 deadline</t>
-  </si>
-  <si>
-    <t>Use the expiring September inspection as customer education about hidden moisture and mold risk.</t>
-  </si>
-  <si>
-    <t>2 ideas for your September mold-inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked your September mold campaign again today and saw the free inspection is still live through September 30.
+    <t>24/7; direct email; 60-minute response positioning</t>
+  </si>
+  <si>
+    <t>Use hidden-moisture education to make the free mold inspection feel useful before visible growth appears.</t>
+  </si>
+  <si>
+    <t>2 ideas for Leader’s free mold-inspection campaign</t>
+  </si>
+  <si>
+    <t>Hi — I checked Leader Restoration’s San Jose mold page today and saw the free inspection, 24/7 response and 60-minute arrival positioning are still prominent.
 I think the strongest customer-facing angle is:
-“You don’t need visible mold to have a moisture problem worth investigating.”
-I’d turn that into a complete September campaign: Google/social posts, homeowner FAQs, inspection reminders, customer follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat, no subscription.
+‘You don’t need visible mold to have a moisture problem worth investigating.’
+I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, customer follow-ups and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
 I already drafted two Leader-specific examples. Want me to send them?</t>
   </si>
   <si>
@@ -163,7 +163,7 @@
     <t>Santa Clara / San Jose area, CA</t>
   </si>
   <si>
-    <t>Official pages currently publish 24/7 availability, direct email info@fairpriceheatingandcooling.com, a $299 air-duct-cleaning offer, and Hello Fall September specials expiring Sep 30, 2026.</t>
+    <t>Official site currently publishes Hello Fall September specials expiring Sep 30, 2026, a $299 air-duct-cleaning offer, 24/7 availability, same-day service and financing.</t>
   </si>
   <si>
     <t>(669) 282-6453</t>
@@ -175,17 +175,17 @@
     <t>24/7; direct email; active September specials</t>
   </si>
   <si>
-    <t>Turn the expiring September specials into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
+    <t>Turn the expiring September offers into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
   </si>
   <si>
     <t>2 ideas for FairPrice’s September specials</t>
   </si>
   <si>
-    <t>Hi — I checked FairPrice’s current site today and saw the September specials are still live through September 30, including the $299 air-duct-cleaning offer.
+    <t>Hi — I checked FairPrice’s site today and the September specials are still live through September 30, including the $299 air-duct-cleaning offer.
 I think there’s a stronger campaign than simply repeating the coupon:
-“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
+‘Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.’
 I’d turn that into Google/social posts, FAQs, offer reminders, customer follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat, no subscription.
+Same-Day Customer Growth Pack: $150 flat.
 Want two FairPrice-specific examples first?</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t>San Jose / Fremont, CA</t>
   </si>
   <si>
-    <t>New high-priority lead: official pages publish 24/7 emergency response, direct email help@danselrestoration.com, free assessments, same-day mold response, insurance assistance, in-house mitigation plus reconstruction, and a promise to reach out within the hour on its main contact flow.</t>
+    <t>Official site remains current with 24/7 emergency service, free assessments, direct email help@danselrestoration.com, insurance assistance, mitigation plus reconstruction in-house, and a published within-the-hour callback promise.</t>
   </si>
   <si>
     <t>(408) 564-0152</t>
@@ -213,15 +213,14 @@
     <t>24/7; direct email; published within-hour callback</t>
   </si>
   <si>
-    <t>Turn its mitigation-to-reconstruction continuity and free assessment into a first-hour emergency decision campaign.</t>
+    <t>Turn mitigation-to-reconstruction continuity into a first-hour emergency decision campaign.</t>
   </si>
   <si>
     <t>First-hour restoration campaign idea for Dansel</t>
   </si>
   <si>
-    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today and noticed you handle both emergency mitigation and reconstruction in-house, with a free assessment and 24/7 response.
-That gives you a strong customer message:
-“The first hour is about stopping the damage. The next steps should not require starting over with another contractor.”
+    <t>Hi — I reviewed Dansel’s current restoration page today. The combination of 24/7 response, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
+‘The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.’
 I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Dansel-specific examples first?</t>
@@ -230,50 +229,92 @@
     <t>https://danselrestoration.com/</t>
   </si>
   <si>
-    <t>The Roofer Bros</t>
-  </si>
-  <si>
-    <t>Roofing / Home Improvement</t>
+    <t>Galaxy Heating &amp; Air Conditioning</t>
+  </si>
+  <si>
+    <t>HVAC / Heat Pumps / Indoor Air Quality</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>New high-priority lead: current San Jose page advertises same-day service for most calls, 24/7 emergency availability, free HVAC replacement estimates, flexible financing and a $59 diagnostic applied toward repair. Direct email info@galaxyservices.com is published.</t>
+  </si>
+  <si>
+    <t>(925) 578-3379</t>
+  </si>
+  <si>
+    <t>info@galaxyservices.com</t>
+  </si>
+  <si>
+    <t>24/7 phone support; direct email; same-day appointments; free replacement estimates</t>
+  </si>
+  <si>
+    <t>Build a repair-versus-replacement decision campaign around the $59 diagnostic, same-day response, free replacement estimate and financing options.</t>
+  </si>
+  <si>
+    <t>Idea for Galaxy’s $59 diagnostic → replacement-estimate flow</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Galaxy’s current San Jose page today and noticed a useful customer decision path already exists in your offer: a $59 diagnostic that applies toward repair, same-day service for most calls, and free replacement estimates with financing available.
+Campaign angle:
+‘Diagnose first. Then decide whether repairing or replacing actually makes sense.’
+I’d turn that into symptom-based posts, repair-vs-replace FAQs, estimate follow-ups, financing education and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Galaxy-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://galaxyservices.com/san-jose/</t>
+  </si>
+  <si>
+    <t>Air &amp; Plumbing Systems</t>
+  </si>
+  <si>
+    <t>HVAC / Water Heating</t>
+  </si>
+  <si>
+    <t>Campbell / San Jose, CA</t>
+  </si>
+  <si>
+    <t>New high-priority lead: current official pages publish same-day AC/heating repair, Monday-Saturday 8AM-6PM availability, free consultation/estimate positioning, direct email info@airandplumbing.com, and a same-day service page focused on completing common repairs in one visit.</t>
+  </si>
+  <si>
+    <t>(408) 733-2000</t>
+  </si>
+  <si>
+    <t>info@airandplumbing.com</t>
+  </si>
+  <si>
+    <t>Direct email; Mon-Sat; same-day repair positioning</t>
+  </si>
+  <si>
+    <t>Market the stocked-truck, same-day first-visit resolution story instead of generic HVAC availability.</t>
+  </si>
+  <si>
+    <t>Same-day first-visit campaign idea for Air &amp; Plumbing Systems</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Air &amp; Plumbing Systems’ current same-day San Jose page today. The strongest story isn’t simply ‘same-day HVAC’; it’s that common repairs are intended to be diagnosed and completed on the first visit.
+Campaign angle:
+‘A same-day appointment should solve the problem, not just schedule the next appointment.’
+I’d turn that into symptom-based posts, first-visit FAQs, missed-inquiry follow-ups, repair-vs-replacement education and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Air &amp; Plumbing-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://airandplumbing.com/same-day-hvac-service-in-san-jose-book-your-appointment-now/</t>
+  </si>
+  <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
+    <t>Roofing</t>
   </si>
   <si>
     <t>Bay Area / San Jose, CA</t>
   </si>
   <si>
-    <t>Official Bay Area page is current today with direct email contact@therooferbros.com, a 5-minute response claim, same-day estimate CTA, free inspections, financing from $149/month, often same-day financing approvals, and a current 10%-off roof-replacement special.</t>
-  </si>
-  <si>
-    <t>(669) 369-3181</t>
-  </si>
-  <si>
-    <t>contact@therooferbros.com</t>
-  </si>
-  <si>
-    <t>Direct email; published 5-minute response; same-day estimate CTA</t>
-  </si>
-  <si>
-    <t>Turn fast response + free inspection + financing into a low-friction roof-decision campaign.</t>
-  </si>
-  <si>
-    <t>Idea for your 5-minute roofing response funnel</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed The Roofer Bros’ Bay Area page today and your strongest sales story may be the speed of the decision path itself:
-“Fast response, free inspection, real scope, then financing if the project needs it.”
-I’d turn that into inspection posts, financing FAQs, same-day estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Roofer Bros-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://bay-area.therooferbros.com/</t>
-  </si>
-  <si>
-    <t>Roof By Tom</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>Official pages remain current: free written estimates, same-day leak help when available, direct email roofbytom@gmail.com, same-day callbacks on most estimate requests, and financing up to 100% of qualifying replacement projects with same-day approvals.</t>
+    <t>Official pages remain current with free written estimates, same-day leak help when available, direct email roofbytom@gmail.com, same-day callbacks on most requests, inspection photos and financing for qualifying replacement work.</t>
   </si>
   <si>
     <t>(925) 488-1882</t>
@@ -285,15 +326,15 @@
     <t>Direct email; same-day callbacks on most estimate requests</t>
   </si>
   <si>
-    <t>Use the inspection → written scope → repair/replacement/financing decision path to reduce uncertainty.</t>
+    <t>Use inspection → photos → written scope → repair/replacement/financing as a low-pressure decision path.</t>
   </si>
   <si>
     <t>Idea for Roof By Tom’s same-day estimate flow</t>
   </si>
   <si>
-    <t>Hi — I checked Roof By Tom’s current estimate and financing pages today and noticed you emphasize same-day callbacks on most estimate requests.
+    <t>Hi — I checked Roof By Tom’s current estimate and financing pages today and noticed you still emphasize same-day callbacks on most estimate requests.
 Campaign angle:
-“First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.”
+‘First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.’
 I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups, financing education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Roof By Tom-specific examples first?</t>
@@ -305,10 +346,7 @@
     <t>ROOF EXPRESS</t>
   </si>
   <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official pages publish sales@roof-ex.com, phone/WhatsApp response within minutes during business hours, email response within one business day, free inspections, same-day inspections Mon–Sat, photo-supported digital scopes, and financing up to $25,000 with $0 down.</t>
+    <t>Current official San Jose page publishes free estimates, same-day inspections Monday-Saturday, detailed photo-supported line-item digital scopes within 24 hours, financing up to $25,000 with $0 down, and emergency roofing service.</t>
   </si>
   <si>
     <t>(650) 666-5554</t>
@@ -317,23 +355,23 @@
     <t>sales@roof-ex.com</t>
   </si>
   <si>
-    <t>Direct email; phone/WhatsApp typically minutes in business hours; email within 1 business day</t>
-  </si>
-  <si>
-    <t>Market the transparent inspection → photo evidence → line-item scope → financing decision path.</t>
+    <t>Direct email; same-day inspections Mon-Sat</t>
+  </si>
+  <si>
+    <t>Market transparent photo evidence and line-item scope as proof-before-purchase.</t>
   </si>
   <si>
     <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed ROOF EXPRESS’s current estimate and financing process today. Your inspection flow gives you a stronger story than another generic roofing ad:
-“See what the roof needs, what it costs and what the financing options are before deciding.”
+    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose page today. Your photo-supported digital scope gives you a stronger story than another generic roofing ad:
+‘See the roof. See the scope. Then decide.’
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Complete Same-Day Customer Growth Pack: $150 flat.
+Same-Day Customer Growth Pack: $150 flat.
 Want two ROOF EXPRESS-specific examples first?</t>
   </si>
   <si>
-    <t>https://quote.roof-ex.com/contact/</t>
+    <t>https://roof-ex.com/san-jose</t>
   </si>
   <si>
     <t>IRBIS Air Plumbing Electrical</t>
@@ -342,24 +380,24 @@
     <t>HVAC / Plumbing / Electrical</t>
   </si>
   <si>
-    <t>Official site is current today: same-day HVAC/plumbing/electrical service, most calls before noon eligible for same-day visits, a 24/7 customer support line, free estimates, 10% off first service, and multi-trade home-care/rebate messaging.</t>
+    <t>Current local listing shows 24/7 availability, 40+ trucks and HVAC, plumbing and electrical under one in-house team, with financing and photo-report/project-management positioning. No direct public email was re-verified today, so use the official web route or phone rather than guessing an address.</t>
   </si>
   <si>
     <t>+1 408-317-3919</t>
   </si>
   <si>
-    <t>Open 24/7 in current listing; official site advertises same-day service and 24/7 support</t>
-  </si>
-  <si>
-    <t>Build one-home-one-team messaging around same-day problems that cross HVAC, plumbing and electrical.</t>
+    <t>24/7 listing; phone/web route; no direct email asserted</t>
+  </si>
+  <si>
+    <t>Build one-home-one-team messaging around problems that cross HVAC, plumbing and electrical.</t>
   </si>
   <si>
     <t>One campaign across HVAC + plumbing + electrical</t>
   </si>
   <si>
-    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one individual trade — it’s that HVAC, plumbing and electrical sit under one team, with same-day service positioned prominently.
+    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one trade — it’s that HVAC, plumbing and electrical sit under one in-house team.
 Campaign angle:
-“One call when the problem crosses systems.”
+‘One home. Three systems. One accountable team.’
 I’d turn that into same-day service posts, cross-service homeowner FAQs, missed-inquiry follow-ups, estimate follow-ups and genuine review-request messaging.
 Same-Day Customer Growth Pack: $150 flat.
 Want two IRBIS-specific examples first?</t>
@@ -368,48 +406,13 @@
     <t>https://www.irbishvac.com/</t>
   </si>
   <si>
-    <t>Infinium Solar, Roofing and Electric</t>
-  </si>
-  <si>
-    <t>Solar / Roofing / Electrical</t>
-  </si>
-  <si>
-    <t>Campbell / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site is current today and combines solar, roofing and electrical in-house with free estimates, South Bay service, battery/electrical work, and a current referral program offering a $500 Amazon gift card after a referred solar/battery project is completed and paid.</t>
-  </si>
-  <si>
-    <t>(408) 583-8101</t>
-  </si>
-  <si>
-    <t>Tuesday business hours; official South Bay contact line; free estimates</t>
-  </si>
-  <si>
-    <t>Use pre-solar roof/electrical readiness plus the active referral program as two customer-acquisition angles.</t>
-  </si>
-  <si>
-    <t>Solar + roof + referral campaign idea</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Infinium’s current service and referral pages today and think you have two unusually strong campaign stories: coordinating solar, roofing and electrical under one team, and the current referral reward.
-The customer-facing angle I’d lead with is:
-“Before installing a long-term solar and battery system, make sure the roof and electrical system underneath it are ready for the same project.”
-I’d turn that into consultation FAQs, readiness posts, estimate follow-ups, referral reminders and cross-service CTAs.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Infinium-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://infinium.inc/</t>
-  </si>
-  <si>
     <t>Therma Tech</t>
   </si>
   <si>
     <t>HVAC</t>
   </si>
   <si>
-    <t>Already contacted by email on Sep 7; no genuine reply found as of this refresh. Official site remains current with flexible financing, same-day HVAC messaging, free estimates, info@thermatechhvac.com, and Tuesday business hours. First respectful follow-up is due Sep 9 if no reply arrives.</t>
+    <t>Already contacted by email on Sep 7. Gmail was checked again on Sep 9 and no genuine reply was found. Current local listing shows the business open today with strong review volume and financing positioning. The first respectful follow-up is due today, but it has not been marked sent.</t>
   </si>
   <si>
     <t>(408) 629-5400</t>
@@ -418,16 +421,16 @@
     <t>info@thermatechhvac.com</t>
   </si>
   <si>
-    <t>Already contacted Sep 7; follow-up due Sep 9 if no genuine reply</t>
-  </si>
-  <si>
-    <t>Preserve the financing + same-day decision angle; do not resend a new cold opener today.</t>
-  </si>
-  <si>
-    <t>Idea for Therma Tech’s financing + same-day traffic</t>
-  </si>
-  <si>
-    <t>Hi — following up on the financing-content idea I sent. Your site already has the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up. I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
+    <t>Already contacted Sep 7; no reply found; FU1 due Sep 9</t>
+  </si>
+  <si>
+    <t>Preserve the financing + same-day decision angle; next action is one respectful follow-up, not a new cold opener.</t>
+  </si>
+  <si>
+    <t>Follow-up: Therma Tech financing + same-day traffic idea</t>
+  </si>
+  <si>
+    <t>Hi — following up once on the financing-content idea I sent. Your existing positioning already gives customers the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up. I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
   </si>
   <si>
     <t>https://thermatechhvac.com/</t>
@@ -612,9 +615,6 @@
     <t>2026-09-07T13:34:00-07:00</t>
   </si>
   <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
     <t>Wait for a genuine reply; if none, send one respectful follow-up on 2026-09-09.</t>
   </si>
   <si>
@@ -652,6 +652,9 @@
   </si>
   <si>
     <t>Lifetime Roofing &amp; Renovation, Inc.</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>South Bay Roofing CO</t>
@@ -1562,34 +1565,34 @@
         <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1603,40 +1606,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1650,38 +1653,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="I9" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1695,38 +1700,38 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1740,10 +1745,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1752,34 +1757,34 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1818,142 +1823,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1983,55 +1988,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2217,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2241,18 +2246,18 @@
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2276,18 +2281,18 @@
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2311,18 +2316,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2346,31 +2351,31 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2387,7 +2392,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2435,25 +2440,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>181</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2632,13 +2637,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2658,7 +2663,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2704,10 +2709,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2724,7 +2729,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2741,7 +2746,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2758,7 +2763,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2775,7 +2780,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2792,7 +2797,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2800,84 +2805,84 @@
         <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +2916,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2920,17 +2925,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2942,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2951,14 +2956,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2967,14 +2972,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2983,14 +2988,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2999,7 +3004,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3008,7 +3013,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3034,90 +3039,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3136,19 +3141,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3165,7 +3170,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="242">
   <si>
     <t>Rank</t>
   </si>
@@ -612,10 +612,16 @@
     <t>Source</t>
   </si>
   <si>
+    <t>New verified lead added 2026-09-09; direct email available.</t>
+  </si>
+  <si>
+    <t>Use official web/phone route; no direct email re-verified 2026-09-09.</t>
+  </si>
+  <si>
     <t>2026-09-07T13:34:00-07:00</t>
   </si>
   <si>
-    <t>Wait for a genuine reply; if none, send one respectful follow-up on 2026-09-09.</t>
+    <t>No genuine reply found as of 2026-09-09 08:38 PT. One respectful follow-up is due today; do not mark it sent until actually sent.</t>
   </si>
   <si>
     <t>Archived</t>
@@ -651,6 +657,9 @@
     <t>California Water and Fire</t>
   </si>
   <si>
+    <t>Infinium Solar, Roofing and Electric</t>
+  </si>
+  <si>
     <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
@@ -661,6 +670,9 @@
   </si>
   <si>
     <t>Eastman Roofing &amp; Waterproofing, Inc.</t>
+  </si>
+  <si>
+    <t>The Roofer Bros</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -2205,7 +2217,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
@@ -2240,7 +2254,9 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
@@ -2345,7 +2361,9 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
@@ -2365,7 +2383,7 @@
         <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>27</v>
@@ -2385,7 +2403,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
@@ -2428,7 +2446,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2455,7 +2473,7 @@
         <v>173</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>176</v>
@@ -2463,7 +2481,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2477,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2497,13 +2515,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2517,13 +2535,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2537,13 +2555,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2557,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2577,13 +2595,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2597,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -2617,13 +2635,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -2637,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2657,13 +2675,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2677,9 +2695,49 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3">
+        <v>150</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3">
+        <v>150</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2709,10 +2767,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2729,7 +2787,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2746,7 +2804,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2763,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2780,7 +2838,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2797,7 +2855,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2814,7 +2872,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2831,7 +2889,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2848,7 +2906,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2865,7 +2923,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2882,7 +2940,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2916,7 +2974,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2925,17 +2983,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2947,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -2963,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -2972,14 +3030,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -2988,14 +3046,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3004,7 +3062,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3039,90 +3097,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3141,19 +3199,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3167,10 +3225,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="243">
   <si>
     <t>Rank</t>
   </si>
@@ -84,7 +84,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official contact page remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, and fresh customer reviews posted within the past week.</t>
+    <t>Official site remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, insurance-claim guidance, and customer reviews posted within the past week.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -96,15 +96,15 @@
     <t>24/7; direct email; real-person response; fresh customer activity</t>
   </si>
   <si>
-    <t>Translate hidden moisture, drying documentation and insurance coordination into urgent plain-English homeowner education.</t>
+    <t>Turn hidden moisture, drying documentation and insurance coordination into urgent plain-English homeowner education.</t>
   </si>
   <si>
     <t>Customer-education idea for FloodDry’s free inspection</t>
   </si>
   <si>
-    <t>Hi — I checked FloodDry’s current San Jose contact and restoration messaging today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
+    <t>Hi — I checked FloodDry’s current San Jose restoration messaging today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
 I think there’s a strong customer-education angle inside that process:
-‘The surface can look dry while moisture is still inside the structure.’
+“The surface can look dry while moisture is still inside the structure.”
 I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want me to send two FloodDry-specific examples first?</t>
@@ -113,7 +113,7 @@
     <t>https://flooddrywdr.com/contact/</t>
   </si>
   <si>
-    <t>2026-09-09</t>
+    <t>2026-09-10</t>
   </si>
   <si>
     <t>Contact Ready</t>
@@ -125,7 +125,7 @@
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>Official San Jose mold page remains current with a free inspection CTA, 24/7 emergency response, a published 60-minute on-site target, direct email service@leaderestoration.com, and California contractor license information.</t>
+    <t>September 2026 free mold inspection remains live through Sep 30, with 24/7 availability, a published 60-minute arrival target, direct email service@leaderestoration.com, and current San Jose service coverage.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -134,19 +134,19 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; 60-minute response positioning</t>
-  </si>
-  <si>
-    <t>Use hidden-moisture education to make the free mold inspection feel useful before visible growth appears.</t>
-  </si>
-  <si>
-    <t>2 ideas for Leader’s free mold-inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked Leader Restoration’s San Jose mold page today and saw the free inspection, 24/7 response and 60-minute arrival positioning are still prominent.
+    <t>24/7; direct email; active Sep 30 deadline</t>
+  </si>
+  <si>
+    <t>Use hidden-moisture education to make the expiring free inspection useful before visible mold appears.</t>
+  </si>
+  <si>
+    <t>2 ideas for Leader’s September mold-inspection campaign</t>
+  </si>
+  <si>
+    <t>Hi — I checked Leader Restoration’s September mold campaign today and the free inspection is still live through September 30.
 I think the strongest customer-facing angle is:
-‘You don’t need visible mold to have a moisture problem worth investigating.’
-I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, customer follow-ups and genuine review-request copy.
+“You don’t need visible mold to have a moisture problem worth investigating.”
+I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 I already drafted two Leader-specific examples. Want me to send them?</t>
   </si>
@@ -163,7 +163,7 @@
     <t>Santa Clara / San Jose area, CA</t>
   </si>
   <si>
-    <t>Official site currently publishes Hello Fall September specials expiring Sep 30, 2026, a $299 air-duct-cleaning offer, 24/7 availability, same-day service and financing.</t>
+    <t>Official site is current today with Hello Fall September specials expiring Sep 30, a $299 air-duct-cleaning offer, 24/7 availability, same-day service, direct email, and financing.</t>
   </si>
   <si>
     <t>(669) 282-6453</t>
@@ -175,7 +175,7 @@
     <t>24/7; direct email; active September specials</t>
   </si>
   <si>
-    <t>Turn the expiring September offers into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
+    <t>Turn expiring September offers into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
   </si>
   <si>
     <t>2 ideas for FairPrice’s September specials</t>
@@ -183,7 +183,7 @@
   <si>
     <t>Hi — I checked FairPrice’s site today and the September specials are still live through September 30, including the $299 air-duct-cleaning offer.
 I think there’s a stronger campaign than simply repeating the coupon:
-‘Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.’
+“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
 I’d turn that into Google/social posts, FAQs, offer reminders, customer follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two FairPrice-specific examples first?</t>
@@ -201,7 +201,7 @@
     <t>San Jose / Fremont, CA</t>
   </si>
   <si>
-    <t>Official site remains current with 24/7 emergency service, free assessments, direct email help@danselrestoration.com, insurance assistance, mitigation plus reconstruction in-house, and a published within-the-hour callback promise.</t>
+    <t>Official site remains current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance, same-day mold response, and mitigation plus reconstruction in-house.</t>
   </si>
   <si>
     <t>(408) 564-0152</t>
@@ -210,7 +210,7 @@
     <t>help@danselrestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; published within-hour callback</t>
+    <t>24/7; direct email; same-day response positioning</t>
   </si>
   <si>
     <t>Turn mitigation-to-reconstruction continuity into a first-hour emergency decision campaign.</t>
@@ -219,8 +219,8 @@
     <t>First-hour restoration campaign idea for Dansel</t>
   </si>
   <si>
-    <t>Hi — I reviewed Dansel’s current restoration page today. The combination of 24/7 response, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
-‘The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.’
+    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today. The combination of 24/7 response, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
+“The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.”
 I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Dansel-specific examples first?</t>
@@ -229,6 +229,41 @@
     <t>https://danselrestoration.com/</t>
   </si>
   <si>
+    <t>California First Roofing</t>
+  </si>
+  <si>
+    <t>Roofing / Commercial Roofing</t>
+  </si>
+  <si>
+    <t>New high-priority lead: official site is current today, publishes sales@californiafirstroofing.com, says estimate requests receive a response within 15 minutes during business hours, offers free 22-point inspections, same-day financing decisions for qualified homeowners, and cites typical San Jose re-roofs at $12,000–$45,000+.</t>
+  </si>
+  <si>
+    <t>(424) 777-1619</t>
+  </si>
+  <si>
+    <t>sales@californiafirstroofing.com</t>
+  </si>
+  <si>
+    <t>Direct sales email; published 15-minute business-hours response; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Market the fast estimate + drone/inspection documentation + financing decision path for high-ticket roofing projects.</t>
+  </si>
+  <si>
+    <t>15-minute roofing estimate funnel idea for California First</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed California First Roofing’s San Jose site today and noticed you already have the pieces of a strong high-ticket decision funnel: a fast sales response, free inspection, documented scope, and financing options.
+Campaign angle:
+“Know the condition, the fixed scope and the payment options before you decide on a $12k–$45k+ roof.”
+I’d turn that into inspection posts, financing FAQs, estimate follow-ups, commercial/property-manager content and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two California First-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://californiafirstroofingsanjose.com/</t>
+  </si>
+  <si>
     <t>Galaxy Heating &amp; Air Conditioning</t>
   </si>
   <si>
@@ -238,7 +273,7 @@
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>New high-priority lead: current San Jose page advertises same-day service for most calls, 24/7 emergency availability, free HVAC replacement estimates, flexible financing and a $59 diagnostic applied toward repair. Direct email info@galaxyservices.com is published.</t>
+    <t>Official San Jose page remains current with same-day service, 24/7 emergency availability, direct email info@galaxyservices.com, a $59 diagnostic applied toward repair, free HVAC replacement estimates, and financing. The Labor Day discount has expired and is excluded from outreach.</t>
   </si>
   <si>
     <t>(925) 578-3379</t>
@@ -247,18 +282,18 @@
     <t>info@galaxyservices.com</t>
   </si>
   <si>
-    <t>24/7 phone support; direct email; same-day appointments; free replacement estimates</t>
-  </si>
-  <si>
-    <t>Build a repair-versus-replacement decision campaign around the $59 diagnostic, same-day response, free replacement estimate and financing options.</t>
+    <t>24/7 phone support; direct email; same-day appointments</t>
+  </si>
+  <si>
+    <t>Build a repair-versus-replacement decision campaign around the $59 diagnostic, free replacement estimate and financing, without using the expired Labor Day offer.</t>
   </si>
   <si>
     <t>Idea for Galaxy’s $59 diagnostic → replacement-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed Galaxy’s current San Jose page today and noticed a useful customer decision path already exists in your offer: a $59 diagnostic that applies toward repair, same-day service for most calls, and free replacement estimates with financing available.
+    <t>Hi — I reviewed Galaxy’s current San Jose page today and there’s a useful customer decision path already in the offer: a $59 diagnostic that applies toward repair, same-day service, and free replacement estimates with financing available.
 Campaign angle:
-‘Diagnose first. Then decide whether repairing or replacing actually makes sense.’
+“Diagnose first. Then decide whether repairing or replacing actually makes sense.”
 I’d turn that into symptom-based posts, repair-vs-replace FAQs, estimate follow-ups, financing education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Galaxy-specific examples first?</t>
@@ -276,7 +311,7 @@
     <t>Campbell / San Jose, CA</t>
   </si>
   <si>
-    <t>New high-priority lead: current official pages publish same-day AC/heating repair, Monday-Saturday 8AM-6PM availability, free consultation/estimate positioning, direct email info@airandplumbing.com, and a same-day service page focused on completing common repairs in one visit.</t>
+    <t>Official same-day San Jose page remains current with direct email info@airandplumbing.com, Monday-Saturday 8AM-6PM availability, same-day AC/heating/heat-pump repair, and a first-visit completion angle for common repairs.</t>
   </si>
   <si>
     <t>(408) 733-2000</t>
@@ -288,15 +323,15 @@
     <t>Direct email; Mon-Sat; same-day repair positioning</t>
   </si>
   <si>
-    <t>Market the stocked-truck, same-day first-visit resolution story instead of generic HVAC availability.</t>
+    <t>Market first-visit resolution and stocked-truck convenience instead of generic same-day availability.</t>
   </si>
   <si>
     <t>Same-day first-visit campaign idea for Air &amp; Plumbing Systems</t>
   </si>
   <si>
-    <t>Hi — I reviewed Air &amp; Plumbing Systems’ current same-day San Jose page today. The strongest story isn’t simply ‘same-day HVAC’; it’s that common repairs are intended to be diagnosed and completed on the first visit.
+    <t>Hi — I reviewed Air &amp; Plumbing Systems’ current same-day San Jose page today. The strongest story isn’t simply “same-day HVAC”; it’s that common repairs are intended to be diagnosed and completed on the first visit.
 Campaign angle:
-‘A same-day appointment should solve the problem, not just schedule the next appointment.’
+“A same-day appointment should solve the problem, not just schedule the next appointment.”
 I’d turn that into symptom-based posts, first-visit FAQs, missed-inquiry follow-ups, repair-vs-replacement education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Air &amp; Plumbing-specific examples first?</t>
@@ -314,7 +349,7 @@
     <t>Bay Area / San Jose, CA</t>
   </si>
   <si>
-    <t>Official pages remain current with free written estimates, same-day leak help when available, direct email roofbytom@gmail.com, same-day callbacks on most requests, inspection photos and financing for qualifying replacement work.</t>
+    <t>Official site remains current with free written estimates, same-day leak help when available, same-day callbacks on most estimate requests, inspection photos, and a low-pressure repair-versus-replacement process.</t>
   </si>
   <si>
     <t>(925) 488-1882</t>
@@ -326,16 +361,16 @@
     <t>Direct email; same-day callbacks on most estimate requests</t>
   </si>
   <si>
-    <t>Use inspection → photos → written scope → repair/replacement/financing as a low-pressure decision path.</t>
+    <t>Use inspection → photos → written scope → repair/replacement decision as a trust-building funnel.</t>
   </si>
   <si>
     <t>Idea for Roof By Tom’s same-day estimate flow</t>
   </si>
   <si>
-    <t>Hi — I checked Roof By Tom’s current estimate and financing pages today and noticed you still emphasize same-day callbacks on most estimate requests.
+    <t>Hi — I checked Roof By Tom’s current estimate process today and noticed you still emphasize same-day callbacks on most requests.
 Campaign angle:
-‘First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.’
-I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups, financing education and genuine review-request copy.
+“First find out exactly what the roof needs. Then decide whether repair or replacement makes sense.”
+I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Roof By Tom-specific examples first?</t>
   </si>
@@ -346,7 +381,7 @@
     <t>ROOF EXPRESS</t>
   </si>
   <si>
-    <t>Current official San Jose page publishes free estimates, same-day inspections Monday-Saturday, detailed photo-supported line-item digital scopes within 24 hours, financing up to $25,000 with $0 down, and emergency roofing service.</t>
+    <t>Official pages are current today with free estimates, same-day inspections Monday-Saturday, photo-supported line-item digital scopes within 24 hours, financing up to $25,000 with $0 down, and emergency roof service.</t>
   </si>
   <si>
     <t>(650) 666-5554</t>
@@ -355,7 +390,7 @@
     <t>sales@roof-ex.com</t>
   </si>
   <si>
-    <t>Direct email; same-day inspections Mon-Sat</t>
+    <t>Direct email; same-day inspections Mon-Sat; 24-hour digital quotes</t>
   </si>
   <si>
     <t>Market transparent photo evidence and line-item scope as proof-before-purchase.</t>
@@ -365,7 +400,7 @@
   </si>
   <si>
     <t>Hi — I reviewed ROOF EXPRESS’s current San Jose page today. Your photo-supported digital scope gives you a stronger story than another generic roofing ad:
-‘See the roof. See the scope. Then decide.’
+“See the roof. See the scope. Then decide.”
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two ROOF EXPRESS-specific examples first?</t>
@@ -374,45 +409,13 @@
     <t>https://roof-ex.com/san-jose</t>
   </si>
   <si>
-    <t>IRBIS Air Plumbing Electrical</t>
-  </si>
-  <si>
-    <t>HVAC / Plumbing / Electrical</t>
-  </si>
-  <si>
-    <t>Current local listing shows 24/7 availability, 40+ trucks and HVAC, plumbing and electrical under one in-house team, with financing and photo-report/project-management positioning. No direct public email was re-verified today, so use the official web route or phone rather than guessing an address.</t>
-  </si>
-  <si>
-    <t>+1 408-317-3919</t>
-  </si>
-  <si>
-    <t>24/7 listing; phone/web route; no direct email asserted</t>
-  </si>
-  <si>
-    <t>Build one-home-one-team messaging around problems that cross HVAC, plumbing and electrical.</t>
-  </si>
-  <si>
-    <t>One campaign across HVAC + plumbing + electrical</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed IRBIS today and your strongest marketing advantage isn’t one trade — it’s that HVAC, plumbing and electrical sit under one in-house team.
-Campaign angle:
-‘One home. Three systems. One accountable team.’
-I’d turn that into same-day service posts, cross-service homeowner FAQs, missed-inquiry follow-ups, estimate follow-ups and genuine review-request messaging.
-Same-Day Customer Growth Pack: $150 flat.
-Want two IRBIS-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.irbishvac.com/</t>
-  </si>
-  <si>
     <t>Therma Tech</t>
   </si>
   <si>
     <t>HVAC</t>
   </si>
   <si>
-    <t>Already contacted by email on Sep 7. Gmail was checked again on Sep 9 and no genuine reply was found. Current local listing shows the business open today with strong review volume and financing positioning. The first respectful follow-up is due today, but it has not been marked sent.</t>
+    <t>Already contacted by email on Sep 7. Gmail checked again Sep 10: no reply and no follow-up email found. Official site is current today with financing, free estimates and direct email. The Sep 9 follow-up is now overdue but remains unsent in the CRM.</t>
   </si>
   <si>
     <t>(408) 629-5400</t>
@@ -421,10 +424,10 @@
     <t>info@thermatechhvac.com</t>
   </si>
   <si>
-    <t>Already contacted Sep 7; no reply found; FU1 due Sep 9</t>
-  </si>
-  <si>
-    <t>Preserve the financing + same-day decision angle; next action is one respectful follow-up, not a new cold opener.</t>
+    <t>Already contacted Sep 7; no reply; FU1 overdue since Sep 9</t>
+  </si>
+  <si>
+    <t>Do not cold-open again. Next action is one respectful follow-up on the financing + same-day decision angle.</t>
   </si>
   <si>
     <t>Follow-up: Therma Tech financing + same-day traffic idea</t>
@@ -615,10 +618,10 @@
     <t>New verified lead added 2026-09-09; direct email available.</t>
   </si>
   <si>
-    <t>Use official web/phone route; no direct email re-verified 2026-09-09.</t>
-  </si>
-  <si>
     <t>2026-09-07T13:34:00-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>No genuine reply found as of 2026-09-09 08:38 PT. One respectful follow-up is due today; do not mark it sent until actually sent.</t>
@@ -1530,34 +1533,34 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1571,40 +1574,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1618,40 +1621,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1665,40 +1668,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1712,13 +1715,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -1729,21 +1732,23 @@
       <c r="G10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1757,10 +1762,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1769,34 +1774,34 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1835,142 +1840,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2000,55 +2005,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2199,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2217,26 +2222,24 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2255,25 +2258,25 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2291,24 +2294,26 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2332,18 +2337,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2361,39 +2366,37 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>181</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2403,14 +2406,14 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2458,30 +2461,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2495,13 +2498,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2515,13 +2518,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2535,13 +2538,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2555,13 +2558,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2575,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2595,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2615,13 +2618,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -2635,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -2655,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2675,13 +2678,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2695,13 +2698,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -2715,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -2735,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -2767,10 +2770,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2787,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2804,7 +2807,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2821,7 +2824,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2838,7 +2841,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2846,101 +2849,101 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2974,7 +2977,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2983,17 +2986,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3005,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3014,14 +3017,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3030,14 +3033,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3046,14 +3049,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3062,7 +3065,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3071,7 +3074,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3097,90 +3100,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3199,19 +3202,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3228,7 +3231,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="246">
   <si>
     <t>Rank</t>
   </si>
@@ -615,7 +615,13 @@
     <t>Source</t>
   </si>
   <si>
-    <t>New verified lead added 2026-09-09; direct email available.</t>
+    <t>New verified lead added 2026-09-10; direct sales email and published 15-minute business-hours response.</t>
+  </si>
+  <si>
+    <t>Verified 2026-09-10; direct email and same-day service remain current. Expired Labor Day discount excluded from outreach.</t>
+  </si>
+  <si>
+    <t>Verified 2026-09-10; direct email and same-day first-visit positioning remain current.</t>
   </si>
   <si>
     <t>2026-09-07T13:34:00-07:00</t>
@@ -624,7 +630,7 @@
     <t>2026-09-09</t>
   </si>
   <si>
-    <t>No genuine reply found as of 2026-09-09 08:38 PT. One respectful follow-up is due today; do not mark it sent until actually sent.</t>
+    <t>Gmail checked 2026-09-10 08:52 PT: no genuine reply and no follow-up sent. One respectful follow-up is overdue; do not mark it sent until actually sent.</t>
   </si>
   <si>
     <t>Archived</t>
@@ -655,6 +661,9 @@
   </si>
   <si>
     <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>IRBIS Air Plumbing Electrical</t>
   </si>
   <si>
     <t>California Water and Fire</t>
@@ -2222,7 +2231,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
@@ -2258,7 +2269,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
@@ -2295,7 +2306,7 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
@@ -2386,10 +2397,10 @@
         <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -2406,7 +2417,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
@@ -2449,7 +2460,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2476,7 +2487,7 @@
         <v>174</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>177</v>
@@ -2484,7 +2495,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2498,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2518,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2538,13 +2549,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2558,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2578,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2598,13 +2609,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2618,13 +2629,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -2638,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -2658,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2678,13 +2689,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2698,13 +2709,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -2718,13 +2729,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -2738,9 +2749,29 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3">
+        <v>150</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2770,10 +2801,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2790,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2807,7 +2838,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2824,7 +2855,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2841,7 +2872,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2858,7 +2889,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2875,7 +2906,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2892,7 +2923,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2909,7 +2940,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2926,7 +2957,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2943,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +3008,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2986,17 +3017,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3008,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3024,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3033,14 +3064,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3049,14 +3080,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3065,7 +3096,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3100,90 +3131,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3202,19 +3233,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3228,10 +3259,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="247">
   <si>
     <t>Rank</t>
   </si>
@@ -84,7 +84,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official site remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, insurance-claim guidance, and customer reviews posted within the past week.</t>
+    <t>Official site remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, ~45-minute response in many San Jose ZIP codes, insurance documentation, and customer reviews posted 3 and 5 days ago.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -102,7 +102,7 @@
     <t>Customer-education idea for FloodDry’s free inspection</t>
   </si>
   <si>
-    <t>Hi — I checked FloodDry’s current San Jose restoration messaging today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
+    <t>Hi — I checked FloodDry’s current San Jose restoration pages today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
 I think there’s a strong customer-education angle inside that process:
 “The surface can look dry while moisture is still inside the structure.”
 I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
@@ -110,10 +110,10 @@
 Want me to send two FloodDry-specific examples first?</t>
   </si>
   <si>
-    <t>https://flooddrywdr.com/contact/</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
+    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>Contact Ready</t>
@@ -125,7 +125,7 @@
     <t>Mold / Water / Fire Restoration</t>
   </si>
   <si>
-    <t>September 2026 free mold inspection remains live through Sep 30, with 24/7 availability, a published 60-minute arrival target, direct email service@leaderestoration.com, and current San Jose service coverage.</t>
+    <t>September 2026 free mold inspection remains live through Sep 30, with 24/7 availability, a published 60-minute arrival target, direct email service@leaderestoration.com, same-day scheduling, and 15% off remediation over $500.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -134,10 +134,10 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; active Sep 30 deadline</t>
-  </si>
-  <si>
-    <t>Use hidden-moisture education to make the expiring free inspection useful before visible mold appears.</t>
+    <t>24/7; direct email; active Sep 30 deadline; same-day scheduling</t>
+  </si>
+  <si>
+    <t>Use hidden-moisture education to make the expiring free inspection and remediation offer useful before visible mold appears.</t>
   </si>
   <si>
     <t>2 ideas for Leader’s September mold-inspection campaign</t>
@@ -146,7 +146,7 @@
     <t>Hi — I checked Leader Restoration’s September mold campaign today and the free inspection is still live through September 30.
 I think the strongest customer-facing angle is:
 “You don’t need visible mold to have a moisture problem worth investigating.”
-I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy.
+I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy, with the September offer used as the reason to act rather than the whole message.
 Same-Day Customer Growth Pack: $150 flat.
 I already drafted two Leader-specific examples. Want me to send them?</t>
   </si>
@@ -163,7 +163,7 @@
     <t>Santa Clara / San Jose area, CA</t>
   </si>
   <si>
-    <t>Official site is current today with Hello Fall September specials expiring Sep 30, a $299 air-duct-cleaning offer, 24/7 availability, same-day service, direct email, and financing.</t>
+    <t>Official site was current today with Hello Fall September specials expiring Sep 30, a $299 air-duct-cleaning offer, 24/7 emergency service, flexible financing, direct email, and a new Sep 7 article on attic radiant barriers.</t>
   </si>
   <si>
     <t>(669) 282-6453</t>
@@ -172,19 +172,19 @@
     <t>info@fairpriceheatingandcooling.com</t>
   </si>
   <si>
-    <t>24/7; direct email; active September specials</t>
-  </si>
-  <si>
-    <t>Turn expiring September offers into a cross-service comfort + airflow + indoor-air-quality campaign.</t>
+    <t>24/7; direct email; active September specials; fresh Sep 7 content</t>
+  </si>
+  <si>
+    <t>Turn the September offers and fresh attic-efficiency content into a fall comfort + airflow + insulation campaign.</t>
   </si>
   <si>
     <t>2 ideas for FairPrice’s September specials</t>
   </si>
   <si>
-    <t>Hi — I checked FairPrice’s site today and the September specials are still live through September 30, including the $299 air-duct-cleaning offer.
-I think there’s a stronger campaign than simply repeating the coupon:
-“Use the fall service visit to solve comfort, airflow and indoor-air-quality problems together.”
-I’d turn that into Google/social posts, FAQs, offer reminders, customer follow-ups and genuine review-request copy.
+    <t>Hi — I checked FairPrice’s site today and the September specials are still live through September 30, including the $299 air-duct-cleaning offer. I also noticed the fresh September content around attic heat gain and radiant barriers.
+I think there’s a stronger campaign than simply repeating a coupon:
+“Fall comfort starts with the air you move — and the heat your attic lets in.”
+I’d turn that into Google/social posts, FAQs, offer reminders, insulation/airflow education, customer follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two FairPrice-specific examples first?</t>
   </si>
@@ -201,7 +201,7 @@
     <t>San Jose / Fremont, CA</t>
   </si>
   <si>
-    <t>Official site remains current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance, same-day mold response, and mitigation plus reconstruction in-house.</t>
+    <t>Official site remains current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance, same-day mold response, a within-hour callback promise, and mitigation plus reconstruction in-house.</t>
   </si>
   <si>
     <t>(408) 564-0152</t>
@@ -210,7 +210,7 @@
     <t>help@danselrestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; same-day response positioning</t>
+    <t>24/7; direct email; within-hour callback; same-day mold response</t>
   </si>
   <si>
     <t>Turn mitigation-to-reconstruction continuity into a first-hour emergency decision campaign.</t>
@@ -219,7 +219,7 @@
     <t>First-hour restoration campaign idea for Dansel</t>
   </si>
   <si>
-    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today. The combination of 24/7 response, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
+    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today. The combination of a within-hour callback, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
 “The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.”
 I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
@@ -235,7 +235,7 @@
     <t>Roofing / Commercial Roofing</t>
   </si>
   <si>
-    <t>New high-priority lead: official site is current today, publishes sales@californiafirstroofing.com, says estimate requests receive a response within 15 minutes during business hours, offers free 22-point inspections, same-day financing decisions for qualified homeowners, and cites typical San Jose re-roofs at $12,000–$45,000+.</t>
+    <t>Official San Jose site remains current with direct sales email, a published 15-minute business-hours response, free estimates, drone/inspection documentation, same-day financing decisions for qualified homeowners, 24/7 emergency service, and residential plus large commercial work.</t>
   </si>
   <si>
     <t>(424) 777-1619</t>
@@ -247,15 +247,15 @@
     <t>Direct sales email; published 15-minute business-hours response; 24/7 emergency service</t>
   </si>
   <si>
-    <t>Market the fast estimate + drone/inspection documentation + financing decision path for high-ticket roofing projects.</t>
+    <t>Market fast response + documented scope + financing as a high-ticket decision funnel for residential and commercial roofing.</t>
   </si>
   <si>
     <t>15-minute roofing estimate funnel idea for California First</t>
   </si>
   <si>
-    <t>Hi — I reviewed California First Roofing’s San Jose site today and noticed you already have the pieces of a strong high-ticket decision funnel: a fast sales response, free inspection, documented scope, and financing options.
+    <t>Hi — I reviewed California First Roofing’s San Jose site again today. You already have the pieces of a strong high-ticket decision funnel: a fast sales response, inspection/drone documentation, a fixed scope and financing options.
 Campaign angle:
-“Know the condition, the fixed scope and the payment options before you decide on a $12k–$45k+ roof.”
+“Before committing to a major roof project, know the condition, the scope and the payment options.”
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, commercial/property-manager content and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two California First-specific examples first?</t>
@@ -273,7 +273,7 @@
     <t>San Jose / Bay Area, CA</t>
   </si>
   <si>
-    <t>Official San Jose page remains current with same-day service, 24/7 emergency availability, direct email info@galaxyservices.com, a $59 diagnostic applied toward repair, free HVAC replacement estimates, and financing. The Labor Day discount has expired and is excluded from outreach.</t>
+    <t>Official San Jose page remains current with same-day service, 24/7 emergency availability, direct email info@galaxyservices.com, a $59 diagnostic applied toward repair, free replacement estimates, 10% off repairs, and financing. Expired Labor Day system discount is excluded.</t>
   </si>
   <si>
     <t>(925) 578-3379</t>
@@ -285,13 +285,13 @@
     <t>24/7 phone support; direct email; same-day appointments</t>
   </si>
   <si>
-    <t>Build a repair-versus-replacement decision campaign around the $59 diagnostic, free replacement estimate and financing, without using the expired Labor Day offer.</t>
+    <t>Build a repair-versus-replacement decision campaign around the diagnostic, repair discount, free replacement estimate and financing without using the expired system offer.</t>
   </si>
   <si>
     <t>Idea for Galaxy’s $59 diagnostic → replacement-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed Galaxy’s current San Jose page today and there’s a useful customer decision path already in the offer: a $59 diagnostic that applies toward repair, same-day service, and free replacement estimates with financing available.
+    <t>Hi — I reviewed Galaxy’s current San Jose page today and there’s a useful customer decision path already in the offer: a $59 diagnostic that applies toward repair, same-day service, repair savings, and free replacement estimates with financing available.
 Campaign angle:
 “Diagnose first. Then decide whether repairing or replacing actually makes sense.”
 I’d turn that into symptom-based posts, repair-vs-replace FAQs, estimate follow-ups, financing education and genuine review-request copy.
@@ -302,42 +302,39 @@
     <t>https://galaxyservices.com/san-jose/</t>
   </si>
   <si>
-    <t>Air &amp; Plumbing Systems</t>
-  </si>
-  <si>
-    <t>HVAC / Water Heating</t>
-  </si>
-  <si>
-    <t>Campbell / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official same-day San Jose page remains current with direct email info@airandplumbing.com, Monday-Saturday 8AM-6PM availability, same-day AC/heating/heat-pump repair, and a first-visit completion angle for common repairs.</t>
-  </si>
-  <si>
-    <t>(408) 733-2000</t>
-  </si>
-  <si>
-    <t>info@airandplumbing.com</t>
-  </si>
-  <si>
-    <t>Direct email; Mon-Sat; same-day repair positioning</t>
-  </si>
-  <si>
-    <t>Market first-visit resolution and stocked-truck convenience instead of generic same-day availability.</t>
-  </si>
-  <si>
-    <t>Same-day first-visit campaign idea for Air &amp; Plumbing Systems</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Air &amp; Plumbing Systems’ current same-day San Jose page today. The strongest story isn’t simply “same-day HVAC”; it’s that common repairs are intended to be diagnosed and completed on the first visit.
+    <t>Top Tier Roofing</t>
+  </si>
+  <si>
+    <t>Premium Roofing / Roof Replacement</t>
+  </si>
+  <si>
+    <t>New higher-ticket lead: official San Jose homepage was current today with free 16-point inspections, direct email david@toptierroofing.com, nearly two decades in business, 500+ Bay Area projects, CertainTeed credentialing, and a lifetime workmanship warranty.</t>
+  </si>
+  <si>
+    <t>(408) 337-6985</t>
+  </si>
+  <si>
+    <t>david@toptierroofing.com</t>
+  </si>
+  <si>
+    <t>Direct email; Mon-Fri business hours; free 16-point inspection</t>
+  </si>
+  <si>
+    <t>Turn premium inspection + material/warranty expertise into a proof-before-purchase campaign for homeowners comparing major roof investments.</t>
+  </si>
+  <si>
+    <t>Premium roof-decision campaign idea for Top Tier</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Top Tier Roofing’s San Jose site today and noticed your strongest marketing advantage isn’t simply that you install roofs — it’s the inspection, credentialing and long-term workmanship warranty behind the decision.
 Campaign angle:
-“A same-day appointment should solve the problem, not just schedule the next appointment.”
-I’d turn that into symptom-based posts, first-visit FAQs, missed-inquiry follow-ups, repair-vs-replacement education and genuine review-request copy.
+“A premium roof should come with proof before the purchase — not just a price.”
+I’d turn that into 16-point inspection content, material/warranty FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
-Want two Air &amp; Plumbing-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://airandplumbing.com/same-day-hvac-service-in-san-jose-book-your-appointment-now/</t>
+Want two Top Tier-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.toptierroofing.com/</t>
   </si>
   <si>
     <t>Roof By Tom</t>
@@ -381,7 +378,7 @@
     <t>ROOF EXPRESS</t>
   </si>
   <si>
-    <t>Official pages are current today with free estimates, same-day inspections Monday-Saturday, photo-supported line-item digital scopes within 24 hours, financing up to $25,000 with $0 down, and emergency roof service.</t>
+    <t>Official pages remain current with free estimates, same-day inspections Monday-Saturday, photo-supported line-item digital scopes within 24 hours, financing, and emergency roof service.</t>
   </si>
   <si>
     <t>(650) 666-5554</t>
@@ -399,14 +396,14 @@
     <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
   </si>
   <si>
-    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose page today. Your photo-supported digital scope gives you a stronger story than another generic roofing ad:
+    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose estimate process today. Your photo-supported digital scope gives you a stronger story than another generic roofing ad:
 “See the roof. See the scope. Then decide.”
 I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two ROOF EXPRESS-specific examples first?</t>
   </si>
   <si>
-    <t>https://roof-ex.com/san-jose</t>
+    <t>https://roof-ex.com/contact</t>
   </si>
   <si>
     <t>Therma Tech</t>
@@ -415,7 +412,7 @@
     <t>HVAC</t>
   </si>
   <si>
-    <t>Already contacted by email on Sep 7. Gmail checked again Sep 10: no reply and no follow-up email found. Official site is current today with financing, free estimates and direct email. The Sep 9 follow-up is now overdue but remains unsent in the CRM.</t>
+    <t>Already contacted by email on Sep 7. Gmail checked again Sep 11: no genuine reply and no follow-up email found. Official site was current today with same-day service, flexible financing, free estimates and direct email. The Sep 9 follow-up remains overdue and unsent.</t>
   </si>
   <si>
     <t>(408) 629-5400</t>
@@ -433,7 +430,8 @@
     <t>Follow-up: Therma Tech financing + same-day traffic idea</t>
   </si>
   <si>
-    <t>Hi — following up once on the financing-content idea I sent. Your existing positioning already gives customers the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up. I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
+    <t>Hi — following up once on the financing-content idea I sent. Your existing positioning already gives customers the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up.
+I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
   </si>
   <si>
     <t>https://thermatechhvac.com/</t>
@@ -621,7 +619,7 @@
     <t>Verified 2026-09-10; direct email and same-day service remain current. Expired Labor Day discount excluded from outreach.</t>
   </si>
   <si>
-    <t>Verified 2026-09-10; direct email and same-day first-visit positioning remain current.</t>
+    <t>New verified higher-ticket lead added 2026-09-11; direct email, free 16-point inspection, lifetime workmanship warranty, and premium roofing positioning.</t>
   </si>
   <si>
     <t>2026-09-07T13:34:00-07:00</t>
@@ -630,7 +628,7 @@
     <t>2026-09-09</t>
   </si>
   <si>
-    <t>Gmail checked 2026-09-10 08:52 PT: no genuine reply and no follow-up sent. One respectful follow-up is overdue; do not mark it sent until actually sent.</t>
+    <t>Gmail checked 2026-09-11 08:42 PT: no genuine reply and no follow-up sent. One respectful follow-up has been overdue since 2026-09-09; do not mark it sent until actually sent.</t>
   </si>
   <si>
     <t>Archived</t>
@@ -666,6 +664,9 @@
     <t>IRBIS Air Plumbing Electrical</t>
   </si>
   <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
     <t>California Water and Fire</t>
   </si>
   <si>
@@ -685,6 +686,9 @@
   </si>
   <si>
     <t>The Roofer Bros</t>
+  </si>
+  <si>
+    <t>Air &amp; Plumbing Systems</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -1636,34 +1640,34 @@
         <v>83</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1677,40 +1681,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1724,10 +1728,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>73</v>
@@ -1736,28 +1740,28 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1771,10 +1775,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1783,34 +1787,34 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1849,142 +1853,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2014,55 +2018,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2232,7 +2236,7 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
@@ -2287,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2306,25 +2310,25 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2348,18 +2352,18 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2383,31 +2387,31 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2417,14 +2421,14 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2460,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2472,30 +2476,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2509,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2529,13 +2533,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2549,13 +2553,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2569,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2589,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2609,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2629,13 +2633,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -2649,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -2669,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -2689,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -2729,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -2749,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -2769,9 +2773,29 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3">
+        <v>150</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2801,10 +2825,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2821,7 +2845,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2838,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2855,7 +2879,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2872,7 +2896,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2889,7 +2913,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2906,7 +2930,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2914,67 +2938,67 @@
         <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3032,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3017,17 +3041,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3039,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3048,14 +3072,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3064,14 +3088,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3080,14 +3104,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3096,7 +3120,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3105,7 +3129,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3131,90 +3155,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3233,19 +3257,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3259,10 +3283,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="246">
   <si>
     <t>Rank</t>
   </si>
@@ -84,7 +84,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>Official site remains current with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, ~45-minute response in many San Jose ZIP codes, insurance documentation, and customer reviews posted 3 and 5 days ago.</t>
+    <t>Official site was current Sep 12 with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, an ~45-minute on-site target, mitigation/drying, and insurance-claim documentation.</t>
   </si>
   <si>
     <t>(408) 404-4000</t>
@@ -93,7 +93,7 @@
     <t>service@flooddrywdr.com</t>
   </si>
   <si>
-    <t>24/7; direct email; real-person response; fresh customer activity</t>
+    <t>24/7; direct email; emergency-response business</t>
   </si>
   <si>
     <t>Turn hidden moisture, drying documentation and insurance coordination into urgent plain-English homeowner education.</t>
@@ -102,18 +102,18 @@
     <t>Customer-education idea for FloodDry’s free inspection</t>
   </si>
   <si>
-    <t>Hi — I checked FloodDry’s current San Jose restoration pages today. You’re still offering 24/7 response and free inspections, and your recent customer feedback reinforces the speed-and-guidance story.
+    <t>Hi — I checked FloodDry’s current Bay Area restoration page today. You’re still offering 24/7 response, free inspections and clear insurance documentation.
 I think there’s a strong customer-education angle inside that process:
 “The surface can look dry while moisture is still inside the structure.”
-I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, insurance-documentation reminders and genuine review-request copy.
+I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, drying-documentation reminders and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want me to send two FloodDry-specific examples first?</t>
   </si>
   <si>
-    <t>https://flooddrywdr.com/water-damage-restoration-san-jose/</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
+    <t>https://flooddrywdr.com/</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
   <si>
     <t>Contact Ready</t>
@@ -122,10 +122,10 @@
     <t>Leader Restoration</t>
   </si>
   <si>
-    <t>Mold / Water / Fire Restoration</t>
-  </si>
-  <si>
-    <t>September 2026 free mold inspection remains live through Sep 30, with 24/7 availability, a published 60-minute arrival target, direct email service@leaderestoration.com, same-day scheduling, and 15% off remediation over $500.</t>
+    <t>Mold / Water / Fire / Attic Restoration</t>
+  </si>
+  <si>
+    <t>September offers remain live through Sep 30: free mold inspection and free attic inspection, with 24/7 availability, same-day inspection positioning, a published 60-minute arrival target and direct email service@leaderestoration.com.</t>
   </si>
   <si>
     <t>(408) 868-2433</t>
@@ -134,21 +134,21 @@
     <t>service@leaderestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; active Sep 30 deadline; same-day scheduling</t>
-  </si>
-  <si>
-    <t>Use hidden-moisture education to make the expiring free inspection and remediation offer useful before visible mold appears.</t>
-  </si>
-  <si>
-    <t>2 ideas for Leader’s September mold-inspection campaign</t>
-  </si>
-  <si>
-    <t>Hi — I checked Leader Restoration’s September mold campaign today and the free inspection is still live through September 30.
-I think the strongest customer-facing angle is:
-“You don’t need visible mold to have a moisture problem worth investigating.”
-I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy, with the September offer used as the reason to act rather than the whole message.
+    <t>24/7; direct email; active Sep 30 deadline</t>
+  </si>
+  <si>
+    <t>Use hidden-moisture and attic-efficiency education to make the expiring inspection offers useful rather than coupon-only.</t>
+  </si>
+  <si>
+    <t>2 ideas for Leader’s September inspection campaigns</t>
+  </si>
+  <si>
+    <t>Hi — I checked Leader Restoration’s September campaigns today and saw both the free mold inspection and free attic inspection are still live through September 30.
+A stronger customer message than simply repeating “free inspection” is:
+“You don’t need visible mold — or a visible attic problem — to have moisture, contamination or efficiency issues worth investigating.”
+I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
-I already drafted two Leader-specific examples. Want me to send them?</t>
+Want me to send two Leader-specific examples first?</t>
   </si>
   <si>
     <t>https://call.leaderestoration.com/mold-408</t>
@@ -163,7 +163,7 @@
     <t>Santa Clara / San Jose area, CA</t>
   </si>
   <si>
-    <t>Official site was current today with Hello Fall September specials expiring Sep 30, a $299 air-duct-cleaning offer, 24/7 emergency service, flexible financing, direct email, and a new Sep 7 article on attic radiant barriers.</t>
+    <t>Official site remains current with Hello Fall September specials, 24/7 emergency service including weekends/holidays, flexible financing and direct email info@fairpriceheatingandcooling.com.</t>
   </si>
   <si>
     <t>(669) 282-6453</t>
@@ -172,19 +172,19 @@
     <t>info@fairpriceheatingandcooling.com</t>
   </si>
   <si>
-    <t>24/7; direct email; active September specials; fresh Sep 7 content</t>
-  </si>
-  <si>
-    <t>Turn the September offers and fresh attic-efficiency content into a fall comfort + airflow + insulation campaign.</t>
+    <t>24/7; direct email; active September campaign</t>
+  </si>
+  <si>
+    <t>Turn the September offers into a fall comfort + airflow + attic-efficiency campaign rather than coupon repetition.</t>
   </si>
   <si>
     <t>2 ideas for FairPrice’s September specials</t>
   </si>
   <si>
-    <t>Hi — I checked FairPrice’s site today and the September specials are still live through September 30, including the $299 air-duct-cleaning offer. I also noticed the fresh September content around attic heat gain and radiant barriers.
+    <t>Hi — I checked FairPrice’s current site today and your September specials are still prominent alongside 24/7 service and financing.
 I think there’s a stronger campaign than simply repeating a coupon:
 “Fall comfort starts with the air you move — and the heat your attic lets in.”
-I’d turn that into Google/social posts, FAQs, offer reminders, insulation/airflow education, customer follow-ups and genuine review-request copy.
+I’d turn that into Google/social posts, FAQs, offer reminders, airflow/insulation education, customer follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two FairPrice-specific examples first?</t>
   </si>
@@ -201,7 +201,7 @@
     <t>San Jose / Fremont, CA</t>
   </si>
   <si>
-    <t>Official site remains current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance, same-day mold response, a within-hour callback promise, and mitigation plus reconstruction in-house.</t>
+    <t>Official pages remain current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance and mitigation plus reconstruction in-house.</t>
   </si>
   <si>
     <t>(408) 564-0152</t>
@@ -210,23 +210,55 @@
     <t>help@danselrestoration.com</t>
   </si>
   <si>
-    <t>24/7; direct email; within-hour callback; same-day mold response</t>
-  </si>
-  <si>
     <t>Turn mitigation-to-reconstruction continuity into a first-hour emergency decision campaign.</t>
   </si>
   <si>
     <t>First-hour restoration campaign idea for Dansel</t>
   </si>
   <si>
-    <t>Hi — I reviewed Dansel’s current San Jose restoration pages today. The combination of a within-hour callback, free assessment, insurance assistance and in-house reconstruction gives you a strong customer message:
+    <t>Hi — I reviewed Dansel’s current restoration pages today. Handling emergency mitigation and reconstruction in-house gives you a strong customer message:
 “The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.”
 I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Dansel-specific examples first?</t>
   </si>
   <si>
-    <t>https://danselrestoration.com/</t>
+    <t>https://danselrestoration.com/about-us/</t>
+  </si>
+  <si>
+    <t>Newhaus Roofing &amp; Construction</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Roofing</t>
+  </si>
+  <si>
+    <t>New Saturday-priority lead: official San Jose page publishes info@newhausroofing.com, free estimates/inspections, residential and commercial roofing, 24/7 availability, emergency repair and flexible 0% financing for qualified homeowners. Current business data shows the San Jose location open Saturday.</t>
+  </si>
+  <si>
+    <t>(669) 287-8895</t>
+  </si>
+  <si>
+    <t>info@newhausroofing.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7 availability; Saturday service; free inspection</t>
+  </si>
+  <si>
+    <t>Market inspection-first scope + financing as a lower-friction path into a high-ticket roof replacement or commercial project.</t>
+  </si>
+  <si>
+    <t>Saturday roof-inspection + financing campaign idea for Newhaus</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Newhaus Roofing’s San Jose page today and noticed you already combine free inspections, residential/commercial roofing, emergency response and financing.
+Campaign angle:
+“Inspect the roof first. Then decide what needs fixing, what it costs and how the project should be financed.”
+I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and commercial/property-owner content.
+Same-Day Customer Growth Pack: $150 flat.
+Want two Newhaus-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://newhausroofing.com/locations/san-jose-ca</t>
   </si>
   <si>
     <t>California First Roofing</t>
@@ -235,7 +267,7 @@
     <t>Roofing / Commercial Roofing</t>
   </si>
   <si>
-    <t>Official San Jose site remains current with direct sales email, a published 15-minute business-hours response, free estimates, drone/inspection documentation, same-day financing decisions for qualified homeowners, 24/7 emergency service, and residential plus large commercial work.</t>
+    <t>Official San Jose site was current Sep 12 with direct sales email, 24/7 emergency service, free estimates, drone/ground documentation, fixed-price proposals, residential/commercial work and typical San Jose re-roofs published at roughly $12,000–$45,000+.</t>
   </si>
   <si>
     <t>(424) 777-1619</t>
@@ -244,19 +276,19 @@
     <t>sales@californiafirstroofing.com</t>
   </si>
   <si>
-    <t>Direct sales email; published 15-minute business-hours response; 24/7 emergency service</t>
-  </si>
-  <si>
-    <t>Market fast response + documented scope + financing as a high-ticket decision funnel for residential and commercial roofing.</t>
-  </si>
-  <si>
-    <t>15-minute roofing estimate funnel idea for California First</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed California First Roofing’s San Jose site again today. You already have the pieces of a strong high-ticket decision funnel: a fast sales response, inspection/drone documentation, a fixed scope and financing options.
+    <t>Direct sales email; 24/7 emergency service; high-ticket roofing</t>
+  </si>
+  <si>
+    <t>Market documented scope + fixed-price estimate + consultation as a proof-before-purchase funnel for major roof projects.</t>
+  </si>
+  <si>
+    <t>High-ticket roof decision funnel idea for California First</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed California First Roofing’s San Jose site again today. Your published process already has the pieces of a strong high-ticket decision funnel: documentation, a fixed-price proposal and premium residential/commercial roofing.
 Campaign angle:
-“Before committing to a major roof project, know the condition, the scope and the payment options.”
-I’d turn that into inspection posts, financing FAQs, estimate follow-ups, commercial/property-manager content and genuine review-request copy.
+“Before committing to a major roof project, know the condition, the scope and the price.”
+I’d turn that into inspection posts, estimate follow-ups, material/warranty FAQs, property-manager content and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two California First-specific examples first?</t>
   </si>
@@ -264,16 +296,51 @@
     <t>https://californiafirstroofingsanjose.com/</t>
   </si>
   <si>
+    <t>ROOF EXPRESS</t>
+  </si>
+  <si>
+    <t>Roofing</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Especially strong today: official contact page says same-day inspections Monday-Saturday 8 AM–5 PM, direct email sales@roof-ex.com, detailed photo-supported digital quotes within 24 hours and financing up to $25,000 with $0 down.</t>
+  </si>
+  <si>
+    <t>(650) 666-5554</t>
+  </si>
+  <si>
+    <t>sales@roof-ex.com</t>
+  </si>
+  <si>
+    <t>Direct email; Saturday same-day inspections; 24-hour digital quotes</t>
+  </si>
+  <si>
+    <t>Use Saturday same-day inspection → photo evidence → line-item scope → financing as a proof-before-purchase sequence.</t>
+  </si>
+  <si>
+    <t>Saturday inspection-to-estimate campaign idea for ROOF EXPRESS</t>
+  </si>
+  <si>
+    <t>Hi — I checked ROOF EXPRESS’s current contact and San Jose pages today and noticed you’re offering same-day inspections on Saturdays, followed by detailed photo-supported digital estimates within 24 hours.
+Campaign angle:
+“See the roof today. See the documented scope next. Then decide.”
+I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
+Same-Day Customer Growth Pack: $150 flat.
+Want two ROOF EXPRESS-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roof-ex.com/contact</t>
+  </si>
+  <si>
     <t>Galaxy Heating &amp; Air Conditioning</t>
   </si>
   <si>
     <t>HVAC / Heat Pumps / Indoor Air Quality</t>
   </si>
   <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Official San Jose page remains current with same-day service, 24/7 emergency availability, direct email info@galaxyservices.com, a $59 diagnostic applied toward repair, free replacement estimates, 10% off repairs, and financing. Expired Labor Day system discount is excluded.</t>
+    <t>Official pages remain current with direct email info@galaxyservices.com, 24/7 phone support, same-day service, a $59 diagnostic applied toward repair, free replacement estimates and a published call-before-noon same-afternoon service path with no added weekend fee.</t>
   </si>
   <si>
     <t>(925) 578-3379</t>
@@ -282,16 +349,16 @@
     <t>info@galaxyservices.com</t>
   </si>
   <si>
-    <t>24/7 phone support; direct email; same-day appointments</t>
-  </si>
-  <si>
-    <t>Build a repair-versus-replacement decision campaign around the diagnostic, repair discount, free replacement estimate and financing without using the expired system offer.</t>
-  </si>
-  <si>
-    <t>Idea for Galaxy’s $59 diagnostic → replacement-estimate flow</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Galaxy’s current San Jose page today and there’s a useful customer decision path already in the offer: a $59 diagnostic that applies toward repair, same-day service, repair savings, and free replacement estimates with financing available.
+    <t>24/7; direct email; same-day/weekend service</t>
+  </si>
+  <si>
+    <t>Build a diagnose-first repair-versus-replacement campaign around same-day weekend service and transparent decision points.</t>
+  </si>
+  <si>
+    <t>Same-day weekend HVAC decision-flow idea for Galaxy</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Galaxy’s current same-day service pages today and noticed a very usable customer decision path: call before noon for typical same-afternoon service, diagnose the system, then choose repair or a replacement estimate without an added weekend service fee.
 Campaign angle:
 “Diagnose first. Then decide whether repairing or replacing actually makes sense.”
 I’d turn that into symptom-based posts, repair-vs-replace FAQs, estimate follow-ups, financing education and genuine review-request copy.
@@ -299,75 +366,37 @@
 Want two Galaxy-specific examples first?</t>
   </si>
   <si>
-    <t>https://galaxyservices.com/san-jose/</t>
-  </si>
-  <si>
-    <t>Top Tier Roofing</t>
-  </si>
-  <si>
-    <t>Premium Roofing / Roof Replacement</t>
-  </si>
-  <si>
-    <t>New higher-ticket lead: official San Jose homepage was current today with free 16-point inspections, direct email david@toptierroofing.com, nearly two decades in business, 500+ Bay Area projects, CertainTeed credentialing, and a lifetime workmanship warranty.</t>
-  </si>
-  <si>
-    <t>(408) 337-6985</t>
-  </si>
-  <si>
-    <t>david@toptierroofing.com</t>
-  </si>
-  <si>
-    <t>Direct email; Mon-Fri business hours; free 16-point inspection</t>
-  </si>
-  <si>
-    <t>Turn premium inspection + material/warranty expertise into a proof-before-purchase campaign for homeowners comparing major roof investments.</t>
-  </si>
-  <si>
-    <t>Premium roof-decision campaign idea for Top Tier</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Top Tier Roofing’s San Jose site today and noticed your strongest marketing advantage isn’t simply that you install roofs — it’s the inspection, credentialing and long-term workmanship warranty behind the decision.
+    <t>https://galaxyservices.com/same-day-ac-repair/</t>
+  </si>
+  <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
+    <t>Bay Area / San Jose, CA</t>
+  </si>
+  <si>
+    <t>Official site was current Sep 12 with direct email roofbytom@gmail.com, free written estimates, same-day callbacks on most requests, same-day leak help when available, photo documentation, and financing up to 100% for qualifying replacement projects with same-day approvals.</t>
+  </si>
+  <si>
+    <t>(925) 488-1882</t>
+  </si>
+  <si>
+    <t>roofbytom@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day callbacks on most estimate requests</t>
+  </si>
+  <si>
+    <t>Use inspection → photos → written scope → repair/replacement/financing decision as a trust-building funnel.</t>
+  </si>
+  <si>
+    <t>Idea for Roof By Tom’s same-day estimate flow</t>
+  </si>
+  <si>
+    <t>Hi — I checked Roof By Tom’s current estimate and financing process today and noticed you still emphasize same-day callbacks on most requests.
 Campaign angle:
-“A premium roof should come with proof before the purchase — not just a price.”
-I’d turn that into 16-point inspection content, material/warranty FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Top Tier-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://www.toptierroofing.com/</t>
-  </si>
-  <si>
-    <t>Roof By Tom</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>Bay Area / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site remains current with free written estimates, same-day leak help when available, same-day callbacks on most estimate requests, inspection photos, and a low-pressure repair-versus-replacement process.</t>
-  </si>
-  <si>
-    <t>(925) 488-1882</t>
-  </si>
-  <si>
-    <t>roofbytom@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day callbacks on most estimate requests</t>
-  </si>
-  <si>
-    <t>Use inspection → photos → written scope → repair/replacement decision as a trust-building funnel.</t>
-  </si>
-  <si>
-    <t>Idea for Roof By Tom’s same-day estimate flow</t>
-  </si>
-  <si>
-    <t>Hi — I checked Roof By Tom’s current estimate process today and noticed you still emphasize same-day callbacks on most requests.
-Campaign angle:
-“First find out exactly what the roof needs. Then decide whether repair or replacement makes sense.”
-I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups and genuine review-request copy.
+“First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.”
+I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups, financing education and genuine review-request copy.
 Same-Day Customer Growth Pack: $150 flat.
 Want two Roof By Tom-specific examples first?</t>
   </si>
@@ -375,44 +404,13 @@
     <t>https://roofbytom.com/</t>
   </si>
   <si>
-    <t>ROOF EXPRESS</t>
-  </si>
-  <si>
-    <t>Official pages remain current with free estimates, same-day inspections Monday-Saturday, photo-supported line-item digital scopes within 24 hours, financing, and emergency roof service.</t>
-  </si>
-  <si>
-    <t>(650) 666-5554</t>
-  </si>
-  <si>
-    <t>sales@roof-ex.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day inspections Mon-Sat; 24-hour digital quotes</t>
-  </si>
-  <si>
-    <t>Market transparent photo evidence and line-item scope as proof-before-purchase.</t>
-  </si>
-  <si>
-    <t>Idea for ROOF EXPRESS’s inspection-to-estimate flow</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed ROOF EXPRESS’s current San Jose estimate process today. Your photo-supported digital scope gives you a stronger story than another generic roofing ad:
-“See the roof. See the scope. Then decide.”
-I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two ROOF EXPRESS-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roof-ex.com/contact</t>
-  </si>
-  <si>
     <t>Therma Tech</t>
   </si>
   <si>
     <t>HVAC</t>
   </si>
   <si>
-    <t>Already contacted by email on Sep 7. Gmail checked again Sep 11: no genuine reply and no follow-up email found. Official site was current today with same-day service, flexible financing, free estimates and direct email. The Sep 9 follow-up remains overdue and unsent.</t>
+    <t>Already contacted by email Sep 7. Gmail checked Sep 12: only the original sent email exists; no genuine reply and no follow-up email found. Official site is current today, open Saturday 8 AM–2:30 PM, with same-day service, a free diagnostic, financing and fast callback positioning.</t>
   </si>
   <si>
     <t>(408) 629-5400</t>
@@ -421,7 +419,7 @@
     <t>info@thermatechhvac.com</t>
   </si>
   <si>
-    <t>Already contacted Sep 7; no reply; FU1 overdue since Sep 9</t>
+    <t>Already contacted Sep 7; no reply; Saturday 8 AM–2:30 PM; FU1 overdue</t>
   </si>
   <si>
     <t>Do not cold-open again. Next action is one respectful follow-up on the financing + same-day decision angle.</t>
@@ -430,7 +428,7 @@
     <t>Follow-up: Therma Tech financing + same-day traffic idea</t>
   </si>
   <si>
-    <t>Hi — following up once on the financing-content idea I sent. Your existing positioning already gives customers the offer; my thought is to make the decision easier to understand across posts, FAQs and estimate follow-up.
+    <t>Hi — following up once on the financing-content idea I sent. Your current site already has the offer; my thought is to make the repair/replace/finance decision easier to understand across posts, FAQs and estimate follow-up.
 I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
   </si>
   <si>
@@ -619,9 +617,6 @@
     <t>Verified 2026-09-10; direct email and same-day service remain current. Expired Labor Day discount excluded from outreach.</t>
   </si>
   <si>
-    <t>New verified higher-ticket lead added 2026-09-11; direct email, free 16-point inspection, lifetime workmanship warranty, and premium roofing positioning.</t>
-  </si>
-  <si>
     <t>2026-09-07T13:34:00-07:00</t>
   </si>
   <si>
@@ -689,6 +684,9 @@
   </si>
   <si>
     <t>Air &amp; Plumbing Systems</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -1514,19 +1512,19 @@
         <v>55</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1540,10 +1538,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -1552,28 +1550,28 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1587,40 +1585,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1634,40 +1632,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1681,40 +1679,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1728,40 +1726,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1775,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1787,34 +1785,34 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1853,142 +1851,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2018,55 +2016,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2206,18 +2204,18 @@
         <v>27</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2235,26 +2233,24 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2273,25 +2269,25 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2309,26 +2305,24 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>181</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2346,24 +2340,26 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2387,31 +2383,31 @@
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K11" s="3">
         <v>150</v>
@@ -2421,14 +2417,14 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2476,30 +2472,30 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -2513,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -2533,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -2553,13 +2549,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
@@ -2573,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2593,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2613,13 +2609,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -2633,13 +2629,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -2653,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -2673,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2693,13 +2689,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2713,13 +2709,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
@@ -2733,13 +2729,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -2753,13 +2749,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
@@ -2773,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -2793,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -2825,10 +2821,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2845,7 +2841,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2862,7 +2858,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2879,7 +2875,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2890,115 +2886,115 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3032,7 +3028,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3041,17 +3037,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3063,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3072,14 +3068,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3088,14 +3084,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3104,14 +3100,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3120,7 +3116,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3129,7 +3125,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3155,90 +3151,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3257,19 +3253,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3286,7 +3282,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="255">
   <si>
     <t>Rank</t>
   </si>
@@ -116,7 +116,7 @@
     <t>2026-09-12</t>
   </si>
   <si>
-    <t>Contact Ready</t>
+    <t>Contacted</t>
   </si>
   <si>
     <t>Leader Restoration</t>
@@ -154,6 +154,9 @@
     <t>https://call.leaderestoration.com/mold-408</t>
   </si>
   <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
     <t>FairPrice Heating &amp; Cooling</t>
   </si>
   <si>
@@ -435,9 +438,6 @@
     <t>https://thermatechhvac.com/</t>
   </si>
   <si>
-    <t>Contacted</t>
-  </si>
-  <si>
     <t>Script ID</t>
   </si>
   <si>
@@ -611,19 +611,46 @@
     <t>Source</t>
   </si>
   <si>
-    <t>New verified lead added 2026-09-10; direct sales email and published 15-minute business-hours response.</t>
-  </si>
-  <si>
-    <t>Verified 2026-09-10; direct email and same-day service remain current. Expired Labor Day discount excluded from outreach.</t>
-  </si>
-  <si>
-    <t>2026-09-07T13:34:00-07:00</t>
+    <t>2026-09-05T22:50:24-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-08T16:45:47-07:00</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:49:58-07:00</t>
   </si>
   <si>
     <t>2026-09-09</t>
   </si>
   <si>
-    <t>Gmail checked 2026-09-11 08:42 PT: no genuine reply and no follow-up sent. One respectful follow-up has been overdue since 2026-09-09; do not mark it sent until actually sent.</t>
+    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:21-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-05T20:01:38-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-07T13:35:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:19:35-07:00</t>
+  </si>
+  <si>
+    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
   </si>
   <si>
     <t>Archived</t>
@@ -641,6 +668,9 @@
     <t>Precision Heating &amp; Cooling</t>
   </si>
   <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
     <t>Roofs By Reveille, Inc</t>
   </si>
   <si>
@@ -653,9 +683,6 @@
     <t>Any Hour Water and Fire</t>
   </si>
   <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
     <t>IRBIS Air Plumbing Electrical</t>
   </si>
   <si>
@@ -671,9 +698,6 @@
     <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
     <t>South Bay Roofing CO</t>
   </si>
   <si>
@@ -687,6 +711,9 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Top Tier Roofing</t>
   </si>
   <si>
     <t>Verified Date</t>
@@ -1436,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1444,46 +1471,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1491,40 +1518,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1538,10 +1565,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -1550,34 +1577,34 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1585,10 +1612,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -1597,28 +1624,28 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1632,46 +1659,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1679,46 +1706,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1726,46 +1753,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1773,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1785,34 +1812,34 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2077,9 +2104,15 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2087,13 +2120,15 @@
         <v>28</v>
       </c>
       <c r="K2" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
         <v>27</v>
@@ -2119,16 +2154,18 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K3" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>27</v>
@@ -2139,13 +2176,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2154,36 +2191,42 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K4" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2192,30 +2235,32 @@
         <v>28</v>
       </c>
       <c r="K5" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2224,7 +2269,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K6" s="3">
         <v>150</v>
@@ -2239,21 +2284,25 @@
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2262,32 +2311,32 @@
         <v>28</v>
       </c>
       <c r="K7" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2296,33 +2345,35 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K8" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2331,35 +2382,35 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K9" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2368,63 +2419,71 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K10" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="K11" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2460,7 +2519,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -2487,7 +2546,7 @@
         <v>172</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>175</v>
@@ -2495,303 +2554,425 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2821,10 +3002,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2841,7 +3022,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2858,143 +3039,143 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3209,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3037,29 +3218,29 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3068,14 +3249,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3084,14 +3265,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3100,14 +3281,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3116,7 +3297,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3151,90 +3332,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3253,19 +3434,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3279,10 +3460,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -17,15 +17,15 @@
     <sheet name="Refresh Log" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priority Leads'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priority Leads'!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="345">
   <si>
     <t>Rank</t>
   </si>
@@ -72,370 +72,607 @@
     <t>Status</t>
   </si>
   <si>
-    <t>FloodDry Water Damage Restoration</t>
-  </si>
-  <si>
-    <t>Water / Mold / Fire Restoration</t>
+    <t>Hertz Electric Inc</t>
+  </si>
+  <si>
+    <t>Electrical / EV / Panel / Battery</t>
+  </si>
+  <si>
+    <t>San Jose / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Current official site advertises same-day and emergency electrical service, EV chargers, panel upgrades, Tesla Powerwall work, free estimates and typically responding within a few hours.</t>
+  </si>
+  <si>
+    <t>(415) 676-0598</t>
+  </si>
+  <si>
+    <t>arash@thehertzelectric.com</t>
+  </si>
+  <si>
+    <t>Direct email; same-day/emergency service</t>
+  </si>
+  <si>
+    <t>Turn panel, EV and battery work into an electrical-readiness decision funnel.</t>
+  </si>
+  <si>
+    <t>Same-day electrical decision-flow idea for Hertz Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Hertz Electric’s current services and noticed you combine same-day work with panel upgrades, EV chargers and Powerwall projects. Campaign angle: ‘Before adding an EV charger or battery, make sure the electrical system underneath it is ready.’ I’d turn that into FAQs, upgrade-readiness posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Hertz-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://thehertzelectric.com/</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>Contact Ready</t>
+  </si>
+  <si>
+    <t>1-800 WATER DAMAGE of West San Jose &amp; Sunnyvale</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Sewage Restoration</t>
+  </si>
+  <si>
+    <t>West San Jose / Sunnyvale, CA</t>
+  </si>
+  <si>
+    <t>Current local franchise pages publish a direct owner email, 24/7 emergency restoration, residential/commercial service, water/fire/mold/sewage work and insurance assistance.</t>
+  </si>
+  <si>
+    <t>(408) 834-7773</t>
+  </si>
+  <si>
+    <t>Murali.Sridharane@1800waterdamage.com</t>
+  </si>
+  <si>
+    <t>Direct owner email; 24/7 emergency business</t>
+  </si>
+  <si>
+    <t>Market first-hour mitigation plus insurance documentation as a calm local decision path.</t>
+  </si>
+  <si>
+    <t>First-hour restoration campaign idea for 1-800 WATER DAMAGE</t>
+  </si>
+  <si>
+    <t>Hi Murali — I reviewed the West San Jose / Sunnyvale pages and saw your local team handles water, fire, mold and sewage emergencies 24/7. Campaign angle: ‘The first hour is about stopping the damage and documenting what happens next.’ I’d turn that into emergency checklists, FAQs and insurance-documentation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two location-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.1800waterdamage.com/west-san-jose-sunnyvale/</t>
+  </si>
+  <si>
+    <t>Ozone Service</t>
+  </si>
+  <si>
+    <t>Electrical / Panel Upgrades</t>
+  </si>
+  <si>
+    <t>Current site advertises 24/7 Bay Area electrical service, free panel-upgrade estimates, no trip/diagnostic fee positioning and written scope/price before work.</t>
+  </si>
+  <si>
+    <t>(669) 323-7077</t>
+  </si>
+  <si>
+    <t>go@serviceozone.com</t>
+  </si>
+  <si>
+    <t>Direct email; 24/7 service; free estimate</t>
+  </si>
+  <si>
+    <t>Make written scope and pricing the trust campaign for upgrades.</t>
+  </si>
+  <si>
+    <t>Panel-upgrade trust campaign idea for Ozone Service</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Ozone Service’s current electrical pages. You already reduce several homeowner objections with 24/7 availability, free panel-upgrade estimates and written scope before work. I’d turn that into panel-readiness posts, EV/upgrade FAQs and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two Ozone-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://serviceozone.com/</t>
+  </si>
+  <si>
+    <t>Silicon Valley Building Service and Repair</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Additions</t>
+  </si>
+  <si>
+    <t>San Jose / Silicon Valley, CA</t>
+  </si>
+  <si>
+    <t>Official site is current with kitchen/bath/whole-home remodeling, ADUs, additions and garage conversions, free estimates, written fixed-price proposals and a same-day reply expectation.</t>
+  </si>
+  <si>
+    <t>(408) 667-4946</t>
+  </si>
+  <si>
+    <t>info@siliconvalleybuilding.com</t>
+  </si>
+  <si>
+    <t>Direct email; usually same-day reply; free estimate</t>
+  </si>
+  <si>
+    <t>Turn scope-first, fixed-price proposals into a high-ticket remodeling decision campaign.</t>
+  </si>
+  <si>
+    <t>Fixed-price remodeling decision-flow idea for SVBSR</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed SVBSR’s current process and noticed a strong trust angle: free estimate, written scope and fixed-price proposal. Campaign idea: ‘Before committing to a remodel or ADU, make the scope and price understandable.’ I’d build project-planning FAQs, ADU/remodel posts and estimate follow-ups. $150 flat. Want two SVBSR-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://siliconvalleybuilding.com/</t>
+  </si>
+  <si>
+    <t>South San Jose Electric</t>
+  </si>
+  <si>
+    <t>Residential / Commercial Electrical</t>
   </si>
   <si>
     <t>San Jose, CA</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Official site was current Sep 12 with 24/7 emergency response, free inspections, direct email service@flooddrywdr.com, an ~45-minute on-site target, mitigation/drying, and insurance-claim documentation.</t>
-  </si>
-  <si>
-    <t>(408) 404-4000</t>
-  </si>
-  <si>
-    <t>service@flooddrywdr.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; emergency-response business</t>
-  </si>
-  <si>
-    <t>Turn hidden moisture, drying documentation and insurance coordination into urgent plain-English homeowner education.</t>
-  </si>
-  <si>
-    <t>Customer-education idea for FloodDry’s free inspection</t>
-  </si>
-  <si>
-    <t>Hi — I checked FloodDry’s current Bay Area restoration page today. You’re still offering 24/7 response, free inspections and clear insurance documentation.
-I think there’s a strong customer-education angle inside that process:
-“The surface can look dry while moisture is still inside the structure.”
-I’d turn that into emergency Google/social posts, homeowner FAQs, inspection follow-ups, drying-documentation reminders and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want me to send two FloodDry-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://flooddrywdr.com/</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>Leader Restoration</t>
-  </si>
-  <si>
-    <t>Mold / Water / Fire / Attic Restoration</t>
-  </si>
-  <si>
-    <t>September offers remain live through Sep 30: free mold inspection and free attic inspection, with 24/7 availability, same-day inspection positioning, a published 60-minute arrival target and direct email service@leaderestoration.com.</t>
-  </si>
-  <si>
-    <t>(408) 868-2433</t>
-  </si>
-  <si>
-    <t>service@leaderestoration.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; active Sep 30 deadline</t>
-  </si>
-  <si>
-    <t>Use hidden-moisture and attic-efficiency education to make the expiring inspection offers useful rather than coupon-only.</t>
-  </si>
-  <si>
-    <t>2 ideas for Leader’s September inspection campaigns</t>
-  </si>
-  <si>
-    <t>Hi — I checked Leader Restoration’s September campaigns today and saw both the free mold inspection and free attic inspection are still live through September 30.
-A stronger customer message than simply repeating “free inspection” is:
-“You don’t need visible mold — or a visible attic problem — to have moisture, contamination or efficiency issues worth investigating.”
-I’d turn that into Google/social posts, homeowner FAQs, inspection reminders, follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want me to send two Leader-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://call.leaderestoration.com/mold-408</t>
-  </si>
-  <si>
-    <t>Contact Ready</t>
-  </si>
-  <si>
-    <t>FairPrice Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>HVAC / Insulation / Indoor Air Quality</t>
-  </si>
-  <si>
-    <t>Santa Clara / San Jose area, CA</t>
-  </si>
-  <si>
-    <t>Official site remains current with Hello Fall September specials, 24/7 emergency service including weekends/holidays, flexible financing and direct email info@fairpriceheatingandcooling.com.</t>
-  </si>
-  <si>
-    <t>(669) 282-6453</t>
-  </si>
-  <si>
-    <t>info@fairpriceheatingandcooling.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; active September campaign</t>
-  </si>
-  <si>
-    <t>Turn the September offers into a fall comfort + airflow + attic-efficiency campaign rather than coupon repetition.</t>
-  </si>
-  <si>
-    <t>2 ideas for FairPrice’s September specials</t>
-  </si>
-  <si>
-    <t>Hi — I checked FairPrice’s current site today and your September specials are still prominent alongside 24/7 service and financing.
-I think there’s a stronger campaign than simply repeating a coupon:
-“Fall comfort starts with the air you move — and the heat your attic lets in.”
-I’d turn that into Google/social posts, FAQs, offer reminders, airflow/insulation education, customer follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two FairPrice-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://fairpriceheatingandcooling.com/</t>
-  </si>
-  <si>
-    <t>Dansel Restoration</t>
-  </si>
-  <si>
-    <t>Water / Fire / Mold / Reconstruction</t>
-  </si>
-  <si>
-    <t>San Jose / Fremont, CA</t>
-  </si>
-  <si>
-    <t>Official pages remain current with 24/7 emergency restoration, free assessments, direct email help@danselrestoration.com, insurance assistance and mitigation plus reconstruction in-house.</t>
-  </si>
-  <si>
-    <t>(408) 564-0152</t>
-  </si>
-  <si>
-    <t>help@danselrestoration.com</t>
-  </si>
-  <si>
-    <t>Turn mitigation-to-reconstruction continuity into a first-hour emergency decision campaign.</t>
-  </si>
-  <si>
-    <t>First-hour restoration campaign idea for Dansel</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Dansel’s current restoration pages today. Handling emergency mitigation and reconstruction in-house gives you a strong customer message:
-“The first hour is about stopping the damage. The next steps shouldn’t require starting over with another contractor.”
-I’d turn that into a first-hour emergency checklist, water/mold FAQs, insurance-assistance messaging, follow-ups and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Dansel-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://danselrestoration.com/about-us/</t>
-  </si>
-  <si>
-    <t>Newhaus Roofing &amp; Construction</t>
+    <t>Current official site publishes a direct email, free estimates and residential/commercial work including panel upgrades, full rewiring and EV chargers, with seven-day availability.</t>
+  </si>
+  <si>
+    <t>(669) 371-5273</t>
+  </si>
+  <si>
+    <t>contact@southsanjoseelectric.com</t>
+  </si>
+  <si>
+    <t>Direct email; seven-day availability; free estimate</t>
+  </si>
+  <si>
+    <t>Build an electrical-capacity readiness campaign around panels, rewiring and EV additions.</t>
+  </si>
+  <si>
+    <t>Electrical-capacity campaign idea for South San Jose Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed South San Jose Electric’s current services. Panel upgrades, rewiring and EV chargers all answer the same question: ‘Is the electrical system ready for what I want to add next?’ I’d turn that into capacity-readiness posts, FAQs and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://southsanjoseelectric.com/</t>
+  </si>
+  <si>
+    <t>RoofCraft Inc</t>
+  </si>
+  <si>
+    <t>Roofing</t>
+  </si>
+  <si>
+    <t>Sunnyvale / Bay Area, CA</t>
+  </si>
+  <si>
+    <t>Official pages are current with free estimates/inspections, financing from $1,000 to $100,000, published Bay Area replacement ranges around $12,000–$40,000 and payment after project completion.</t>
+  </si>
+  <si>
+    <t>(408) 904-8900</t>
+  </si>
+  <si>
+    <t>info@roofcraftcompany.com</t>
+  </si>
+  <si>
+    <t>Direct email; high-ticket roofing; financing</t>
+  </si>
+  <si>
+    <t>Use inspection, realistic project ranges and financing education to reduce replacement uncertainty.</t>
+  </si>
+  <si>
+    <t>High-ticket roof decision campaign idea for RoofCraft</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed RoofCraft’s current estimate and financing pages. Publishing inspection guidance and realistic project ranges creates a strong trust angle: ‘Understand the roof condition, project range and financing options before committing.’ I’d build inspection posts, repair-vs-replacement FAQs and estimate follow-ups. $150 flat. Want two RoofCraft-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://roofcraftcompany.com/</t>
+  </si>
+  <si>
+    <t>SERVPRO of Mountain View, Los Altos</t>
+  </si>
+  <si>
+    <t>Water / Fire / Mold / Storm / Construction</t>
+  </si>
+  <si>
+    <t>Sunnyvale / Mountain View / Los Altos, CA</t>
+  </si>
+  <si>
+    <t>Current local SERVPRO pages publish 24/7 emergency service, fire/water/mold/storm restoration, construction and commercial services, a Sunnyvale office and direct office email.</t>
+  </si>
+  <si>
+    <t>(650) 770-2992</t>
+  </si>
+  <si>
+    <t>office@SERVPROmtview.com</t>
+  </si>
+  <si>
+    <t>Direct office email; 24/7 emergency service</t>
+  </si>
+  <si>
+    <t>Explain mitigation-to-reconstruction continuity and commercial response in plain language.</t>
+  </si>
+  <si>
+    <t>Mitigation-to-rebuild campaign idea for SERVPRO Mountain View</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed your local SERVPRO pages and noticed the team handles both emergency mitigation and reconstruction, plus commercial losses. Campaign angle: ‘Stop the damage first, then keep recovery moving without making the customer restart the process.’ I’d build first-hour checklists, commercial-response posts and reconstruction FAQs. $150 flat. Want two local examples first?</t>
+  </si>
+  <si>
+    <t>https://www.servpromountainviewlosaltos.com/</t>
+  </si>
+  <si>
+    <t>Courtesy Electric</t>
+  </si>
+  <si>
+    <t>Electrical / Remodel / Service Upgrades</t>
+  </si>
+  <si>
+    <t>Sunnyvale / South Bay, CA</t>
+  </si>
+  <si>
+    <t>Official site publishes owner-operated electrical service, free estimates, new construction, remodeling, service upgrades and lighting, plus a direct business email.</t>
+  </si>
+  <si>
+    <t>(408) 509-1017</t>
+  </si>
+  <si>
+    <t>mike@courtesyelectric.us</t>
+  </si>
+  <si>
+    <t>Direct owner/business email; free estimate</t>
+  </si>
+  <si>
+    <t>Use owner-operated accountability plus upgrade/remodel scope clarity.</t>
+  </si>
+  <si>
+    <t>Service-upgrade campaign idea for Courtesy Electric</t>
+  </si>
+  <si>
+    <t>Hi Mike — I reviewed Courtesy Electric’s current services and think the owner-operated positioning can do more work in the marketing. Campaign angle: ‘For a remodel or service upgrade, know who is responsible for the electrical scope from estimate through completion.’ I’d build upgrade FAQs, remodel posts and estimate follow-ups. $150 flat. Want two Courtesy-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://courtesyelectric.us/</t>
+  </si>
+  <si>
+    <t>408 Builders Inc</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / New Construction</t>
+  </si>
+  <si>
+    <t>Official pages publish kitchen/bath remodeling, ADUs and new-home construction, free on-site estimates, detailed proposals and a stated reply within one business day.</t>
+  </si>
+  <si>
+    <t>(408) 609-1643</t>
+  </si>
+  <si>
+    <t>info@408buildersinc.com</t>
+  </si>
+  <si>
+    <t>Direct email; reply within one business day; free estimate</t>
+  </si>
+  <si>
+    <t>Build a consultation-to-detailed-proposal funnel for high-ticket ADU/remodel leads.</t>
+  </si>
+  <si>
+    <t>ADU + remodeling proposal-funnel idea for 408 Builders</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed 408 Builders’ current process and noticed you already give prospects a useful path: free on-site estimate followed by a detailed proposal. I’d turn that into ADU FAQs, project-planning posts and consultation follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two 408 Builders-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://408buildersinc.com/</t>
+  </si>
+  <si>
+    <t>AYH Remodeling &amp; Construction Inc</t>
+  </si>
+  <si>
+    <t>Current site publishes free estimates, remodeling, ADUs/additions, structural and permit services, a direct email and Monday–Saturday 7 AM–7 PM hours.</t>
+  </si>
+  <si>
+    <t>833-408-5179</t>
+  </si>
+  <si>
+    <t>ayhremodelingandconstruction@gmail.com</t>
+  </si>
+  <si>
+    <t>Direct email; Mon–Sat; free estimate</t>
+  </si>
+  <si>
+    <t>Use permit, structural and build coordination to simplify the ADU/addition decision.</t>
+  </si>
+  <si>
+    <t>ADU permit-to-build campaign idea for AYH</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed AYH’s current services and noticed you cover the parts homeowners often find most confusing on an ADU or addition: structural work, permits and construction. I’d turn that into ADU FAQs, permit/process posts and estimate follow-ups. Same-Day Customer Growth Pack: $150 flat. Want two AYH-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://ayhremodeling.com/</t>
+  </si>
+  <si>
+    <t>Pylon Builders</t>
+  </si>
+  <si>
+    <t>Remodeling / ADU / Design-Build</t>
+  </si>
+  <si>
+    <t>Current site publishes premium remodeling/ADU services, free in-home consultations, a current 2026 ADU cost guide and direct business email.</t>
+  </si>
+  <si>
+    <t>(650) 800-9755</t>
+  </si>
+  <si>
+    <t>info@pylonbuilders.com</t>
+  </si>
+  <si>
+    <t>Direct email; free in-home consultation</t>
+  </si>
+  <si>
+    <t>Turn the current 2026 ADU cost guide into consultation-driving education.</t>
+  </si>
+  <si>
+    <t>2026 ADU cost-guide campaign idea for Pylon Builders</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Pylon Builders’ current ADU content and saw the 2026 cost guide alongside your free in-home consultation. Campaign angle: ‘Use real planning ranges to decide whether an ADU is worth designing before you commit.’ I’d build cost/feasibility posts, ADU FAQs and consultation follow-ups. $150 flat. Want two Pylon-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://pylonbuilders.com/</t>
+  </si>
+  <si>
+    <t>Home Pro Roofing and Solar</t>
+  </si>
+  <si>
+    <t>Roofing / Solar / Battery / EV</t>
+  </si>
+  <si>
+    <t>Current contact page advertises free estimates within 24 hours and offers through Sep 15, 2026: $250 off a full roof replacement and $1,500 off a roof + solar combo.</t>
+  </si>
+  <si>
+    <t>(800) 650-3134</t>
+  </si>
+  <si>
+    <t>Phone/web form; seven-day availability; Sep 15 deadline</t>
+  </si>
+  <si>
+    <t>Use the Sep 15 roof+solar deadline to explain bundling readiness rather than repeating a discount.</t>
+  </si>
+  <si>
+    <t>Sep 15 roof + solar campaign idea for Home Pro</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Home Pro’s current page and saw the roof and roof-plus-solar offers run through September 15. Campaign angle: ‘If the roof and solar system will live together for years, plan them as one project before installation.’ I’d build roof-readiness posts, solar/battery FAQs and offer follow-ups. $150 flat. Want two Home Pro-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://homeproroofingandsolar.com/contact/</t>
+  </si>
+  <si>
+    <t>Foundation Repair of California</t>
+  </si>
+  <si>
+    <t>Foundation / Concrete / Crawl Space</t>
+  </si>
+  <si>
+    <t>Current San Jose pages advertise free expert inspections, financing, concrete/foundation services and current qualifying-project savings; financing pages describe large-project lender options.</t>
+  </si>
+  <si>
+    <t>(925) 961-9012</t>
+  </si>
+  <si>
+    <t>Phone/web form; free inspection; financing</t>
+  </si>
+  <si>
+    <t>Build inspection-first education around cracks, settlement and financing without fear-based claims.</t>
+  </si>
+  <si>
+    <t>Foundation inspection decision-flow idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed your current San Jose pages and think the free inspection can support a stronger campaign than generic foundation-problem advertising. Angle: ‘Start with evidence of what is moving, why, and what actually needs repair.’ I’d build symptom FAQs, inspection-prep posts and estimate follow-ups. $150 flat. Want two business-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://www.foundationrepairofca.com/service-areas/san-jose-ca/</t>
+  </si>
+  <si>
+    <t>Bentson Window &amp; Door</t>
+  </si>
+  <si>
+    <t>Windows / Doors</t>
+  </si>
+  <si>
+    <t>San Jose / Campbell / Sunnyvale, CA</t>
+  </si>
+  <si>
+    <t>Current official pages publish free in-home estimates, itemized estimates typically within 24 hours, flexible financing including qualified 0% APR promotions and limited savings for 5+ windows.</t>
+  </si>
+  <si>
+    <t>(408) 479-7960</t>
+  </si>
+  <si>
+    <t>Phone/web form; 24-hour estimate target; financing</t>
+  </si>
+  <si>
+    <t>Use the itemized 24-hour estimate as the trust hook for multi-window replacement.</t>
+  </si>
+  <si>
+    <t>24-hour window-estimate campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Bentson’s current estimate process and noticed you typically provide an itemized estimate within 24 hours. Campaign angle: ‘Before replacing several windows, know the itemized scope, efficiency choices and financing options.’ I’d build comparison FAQs, estimate follow-ups and financing education. $150 flat. Want two Bentson-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://bentsonwindows.com/</t>
+  </si>
+  <si>
+    <t>Trio Roofers</t>
   </si>
   <si>
     <t>Residential / Commercial Roofing</t>
   </si>
   <si>
-    <t>New Saturday-priority lead: official San Jose page publishes info@newhausroofing.com, free estimates/inspections, residential and commercial roofing, 24/7 availability, emergency repair and flexible 0% financing for qualified homeowners. Current business data shows the San Jose location open Saturday.</t>
-  </si>
-  <si>
-    <t>(669) 287-8895</t>
-  </si>
-  <si>
-    <t>info@newhausroofing.com</t>
-  </si>
-  <si>
-    <t>Direct email; 24/7 availability; Saturday service; free inspection</t>
-  </si>
-  <si>
-    <t>Market inspection-first scope + financing as a lower-friction path into a high-ticket roof replacement or commercial project.</t>
-  </si>
-  <si>
-    <t>Saturday roof-inspection + financing campaign idea for Newhaus</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Newhaus Roofing’s San Jose page today and noticed you already combine free inspections, residential/commercial roofing, emergency response and financing.
-Campaign angle:
-“Inspect the roof first. Then decide what needs fixing, what it costs and how the project should be financed.”
-I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and commercial/property-owner content.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Newhaus-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://newhausroofing.com/locations/san-jose-ca</t>
-  </si>
-  <si>
-    <t>California First Roofing</t>
-  </si>
-  <si>
-    <t>Roofing / Commercial Roofing</t>
-  </si>
-  <si>
-    <t>Official San Jose site was current Sep 12 with direct sales email, 24/7 emergency service, free estimates, drone/ground documentation, fixed-price proposals, residential/commercial work and typical San Jose re-roofs published at roughly $12,000–$45,000+.</t>
-  </si>
-  <si>
-    <t>(424) 777-1619</t>
-  </si>
-  <si>
-    <t>sales@californiafirstroofing.com</t>
-  </si>
-  <si>
-    <t>Direct sales email; 24/7 emergency service; high-ticket roofing</t>
-  </si>
-  <si>
-    <t>Market documented scope + fixed-price estimate + consultation as a proof-before-purchase funnel for major roof projects.</t>
-  </si>
-  <si>
-    <t>High-ticket roof decision funnel idea for California First</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed California First Roofing’s San Jose site again today. Your published process already has the pieces of a strong high-ticket decision funnel: documentation, a fixed-price proposal and premium residential/commercial roofing.
-Campaign angle:
-“Before committing to a major roof project, know the condition, the scope and the price.”
-I’d turn that into inspection posts, estimate follow-ups, material/warranty FAQs, property-manager content and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two California First-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://californiafirstroofingsanjose.com/</t>
-  </si>
-  <si>
-    <t>ROOF EXPRESS</t>
-  </si>
-  <si>
-    <t>Roofing</t>
-  </si>
-  <si>
-    <t>San Jose / Bay Area, CA</t>
-  </si>
-  <si>
-    <t>Especially strong today: official contact page says same-day inspections Monday-Saturday 8 AM–5 PM, direct email sales@roof-ex.com, detailed photo-supported digital quotes within 24 hours and financing up to $25,000 with $0 down.</t>
-  </si>
-  <si>
-    <t>(650) 666-5554</t>
-  </si>
-  <si>
-    <t>sales@roof-ex.com</t>
-  </si>
-  <si>
-    <t>Direct email; Saturday same-day inspections; 24-hour digital quotes</t>
-  </si>
-  <si>
-    <t>Use Saturday same-day inspection → photo evidence → line-item scope → financing as a proof-before-purchase sequence.</t>
-  </si>
-  <si>
-    <t>Saturday inspection-to-estimate campaign idea for ROOF EXPRESS</t>
-  </si>
-  <si>
-    <t>Hi — I checked ROOF EXPRESS’s current contact and San Jose pages today and noticed you’re offering same-day inspections on Saturdays, followed by detailed photo-supported digital estimates within 24 hours.
-Campaign angle:
-“See the roof today. See the documented scope next. Then decide.”
-I’d turn that into inspection posts, financing FAQs, estimate follow-ups, repair-vs-replacement education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two ROOF EXPRESS-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roof-ex.com/contact</t>
-  </si>
-  <si>
-    <t>Galaxy Heating &amp; Air Conditioning</t>
-  </si>
-  <si>
-    <t>HVAC / Heat Pumps / Indoor Air Quality</t>
-  </si>
-  <si>
-    <t>Official pages remain current with direct email info@galaxyservices.com, 24/7 phone support, same-day service, a $59 diagnostic applied toward repair, free replacement estimates and a published call-before-noon same-afternoon service path with no added weekend fee.</t>
-  </si>
-  <si>
-    <t>(925) 578-3379</t>
-  </si>
-  <si>
-    <t>info@galaxyservices.com</t>
-  </si>
-  <si>
-    <t>24/7; direct email; same-day/weekend service</t>
-  </si>
-  <si>
-    <t>Build a diagnose-first repair-versus-replacement campaign around same-day weekend service and transparent decision points.</t>
-  </si>
-  <si>
-    <t>Same-day weekend HVAC decision-flow idea for Galaxy</t>
-  </si>
-  <si>
-    <t>Hi — I reviewed Galaxy’s current same-day service pages today and noticed a very usable customer decision path: call before noon for typical same-afternoon service, diagnose the system, then choose repair or a replacement estimate without an added weekend service fee.
-Campaign angle:
-“Diagnose first. Then decide whether repairing or replacing actually makes sense.”
-I’d turn that into symptom-based posts, repair-vs-replace FAQs, estimate follow-ups, financing education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Galaxy-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://galaxyservices.com/same-day-ac-repair/</t>
-  </si>
-  <si>
-    <t>Roof By Tom</t>
-  </si>
-  <si>
-    <t>Bay Area / San Jose, CA</t>
-  </si>
-  <si>
-    <t>Official site was current Sep 12 with direct email roofbytom@gmail.com, free written estimates, same-day callbacks on most requests, same-day leak help when available, photo documentation, and financing up to 100% for qualifying replacement projects with same-day approvals.</t>
-  </si>
-  <si>
-    <t>(925) 488-1882</t>
-  </si>
-  <si>
-    <t>roofbytom@gmail.com</t>
-  </si>
-  <si>
-    <t>Direct email; same-day callbacks on most estimate requests</t>
-  </si>
-  <si>
-    <t>Use inspection → photos → written scope → repair/replacement/financing decision as a trust-building funnel.</t>
-  </si>
-  <si>
-    <t>Idea for Roof By Tom’s same-day estimate flow</t>
-  </si>
-  <si>
-    <t>Hi — I checked Roof By Tom’s current estimate and financing process today and noticed you still emphasize same-day callbacks on most requests.
-Campaign angle:
-“First find out exactly what the roof needs. Then decide whether repair, replacement or financing makes sense.”
-I’d turn that into leak-response posts, repair-vs-replacement FAQs, estimate follow-ups, financing education and genuine review-request copy.
-Same-Day Customer Growth Pack: $150 flat.
-Want two Roof By Tom-specific examples first?</t>
-  </si>
-  <si>
-    <t>https://roofbytom.com/</t>
-  </si>
-  <si>
-    <t>Therma Tech</t>
-  </si>
-  <si>
-    <t>HVAC</t>
-  </si>
-  <si>
-    <t>Already contacted by email Sep 7. Gmail checked Sep 12: only the original sent email exists; no genuine reply and no follow-up email found. Official site is current today, open Saturday 8 AM–2:30 PM, with same-day service, a free diagnostic, financing and fast callback positioning.</t>
-  </si>
-  <si>
-    <t>(408) 629-5400</t>
-  </si>
-  <si>
-    <t>info@thermatechhvac.com</t>
-  </si>
-  <si>
-    <t>Already contacted Sep 7; no reply; Saturday 8 AM–2:30 PM; FU1 overdue</t>
-  </si>
-  <si>
-    <t>Do not cold-open again. Next action is one respectful follow-up on the financing + same-day decision angle.</t>
-  </si>
-  <si>
-    <t>Follow-up: Therma Tech financing + same-day traffic idea</t>
-  </si>
-  <si>
-    <t>Hi — following up once on the financing-content idea I sent. Your current site already has the offer; my thought is to make the repair/replace/finance decision easier to understand across posts, FAQs and estimate follow-up.
-I can send the two Therma Tech-specific examples first so you can judge the direction before deciding. No obligation.</t>
-  </si>
-  <si>
-    <t>https://thermatechhvac.com/</t>
+    <t>Current San Jose pages advertise free inspections, residential/commercial/emergency roofing, 24/7 emergency availability and $0-upfront financing positioning. No tax-credit claim is used.</t>
+  </si>
+  <si>
+    <t>(408) 886-9287</t>
+  </si>
+  <si>
+    <t>Phone/web form; 24/7 emergency; free inspection</t>
+  </si>
+  <si>
+    <t>Use free inspection plus financing as a proof-before-purchase sequence.</t>
+  </si>
+  <si>
+    <t>Free-inspection roofing funnel idea for Trio</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Trio Roofers’ current San Jose pages. The strongest customer story is the decision sequence: ‘Inspect first. See the scope. Then decide how to fund the project.’ I’d build inspection posts, repair-vs-replacement FAQs and financing follow-ups. $150 flat. Want two Trio-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://trioroofers.com/san-jose/</t>
+  </si>
+  <si>
+    <t>Foundation Strategies &amp; Construction</t>
+  </si>
+  <si>
+    <t>Foundation / Waterproofing / Structural</t>
+  </si>
+  <si>
+    <t>San Jose / Sunnyvale, CA</t>
+  </si>
+  <si>
+    <t>Current pages publish free no-pressure inspections/estimates, foundation and waterproofing services, financing options and structural/new-foundation work in the South Bay.</t>
+  </si>
+  <si>
+    <t>(408) 320-7433</t>
+  </si>
+  <si>
+    <t>Turn no-pressure inspection plus structural explanation into trust-focused content.</t>
+  </si>
+  <si>
+    <t>No-pressure foundation inspection campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Foundation Strategies’ current South Bay pages and noticed you emphasize free, no-pressure inspections alongside structural and waterproofing work. Campaign angle: ‘Understand the cause and repair options before deciding whether a foundation project is actually necessary.’ I’d build crack/settlement FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
+  </si>
+  <si>
+    <t>https://foundationstrategies.com/</t>
+  </si>
+  <si>
+    <t>Jackson Electric</t>
+  </si>
+  <si>
+    <t>Electrical / Panel / EV</t>
+  </si>
+  <si>
+    <t>Current site says emergency calls are prioritized, panel-upgrade and EV-charger quotes are usually returned within one business day, and the company has operated locally since 1989.</t>
+  </si>
+  <si>
+    <t>(408) 266-5351</t>
+  </si>
+  <si>
+    <t>Phone/web form; one-business-day quote target</t>
+  </si>
+  <si>
+    <t>Use long local history plus fast quotes to clarify panel/EV upgrades.</t>
+  </si>
+  <si>
+    <t>One-day electrical quote campaign idea for Jackson Electric</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Jackson Electric’s current services and noticed you pair long local history with a practical advantage: panel-upgrade and EV-charger quotes are usually turned around within one business day. I’d build panel/EV FAQs, quote follow-ups and capacity-readiness posts. $150 flat. Want two Jackson-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://jacksonelectric.com/</t>
+  </si>
+  <si>
+    <t>Atlas Trillo</t>
+  </si>
+  <si>
+    <t>HVAC / Plumbing</t>
+  </si>
+  <si>
+    <t>Current site has September residential offers through Sep 30, including a $59 seasonal HVAC tune-up and $50 off qualifying service repair, alongside HVAC and plumbing services.</t>
+  </si>
+  <si>
+    <t>(408) 444-9511</t>
+  </si>
+  <si>
+    <t>Phone/web form; active Sep 30 offers</t>
+  </si>
+  <si>
+    <t>Use the tune-up as a diagnostic/decision campaign rather than coupon-only advertising.</t>
+  </si>
+  <si>
+    <t>September HVAC tune-up campaign idea for Atlas Trillo</t>
+  </si>
+  <si>
+    <t>Hi — I checked Atlas Trillo’s current September offers and saw the seasonal HVAC tune-up and repair savings are live through September 30. Campaign angle: ‘Use the tune-up to learn what actually needs attention before peak heating season.’ I’d build symptom posts, tune-up FAQs and repair follow-ups. $150 flat. Want two examples first?</t>
+  </si>
+  <si>
+    <t>https://www.atlastrillo.com/specials/</t>
+  </si>
+  <si>
+    <t>Rooter Hero Plumbing &amp; Air of San Jose</t>
+  </si>
+  <si>
+    <t>Plumbing / Drain / HVAC</t>
+  </si>
+  <si>
+    <t>Current San Jose pages publish 24/7 service and active Sep 1–30 residential promotions including drain/camera-inspection and qualifying repair savings. Expired commercial promotions are excluded.</t>
+  </si>
+  <si>
+    <t>(408) 703-6715</t>
+  </si>
+  <si>
+    <t>24/7 phone/web; active Sep 30 residential offers</t>
+  </si>
+  <si>
+    <t>Turn drain-camera and repair offers into see-the-problem-before-choosing-the-repair education.</t>
+  </si>
+  <si>
+    <t>Drain-camera decision campaign idea for Rooter Hero</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Rooter Hero San Jose’s current September residential offers and think the camera-inspection angle supports a better campaign than discount-only messaging: ‘See what is causing the drain problem before choosing the repair.’ I’d build diagnosis posts, FAQs and service follow-ups. $150 flat. Want two San Jose-specific examples first?</t>
+  </si>
+  <si>
+    <t>https://rooterhero.com/san-jose/</t>
+  </si>
+  <si>
+    <t>Home Additions San Jose</t>
+  </si>
+  <si>
+    <t>Home Additions / ADU / Remodeling</t>
+  </si>
+  <si>
+    <t>Current site publishes free estimates, home additions, ADUs and second-story work, a direct email, Monday–Saturday service and Sunday appointments.</t>
+  </si>
+  <si>
+    <t>info@homeadditionssanjose.com</t>
+  </si>
+  <si>
+    <t>Direct email; free estimate; Mon–Sat + Sunday by appointment</t>
+  </si>
+  <si>
+    <t>Use feasibility-to-estimate planning as a high-ticket addition/ADU funnel.</t>
+  </si>
+  <si>
+    <t>Addition + ADU feasibility campaign idea</t>
+  </si>
+  <si>
+    <t>Hi — I reviewed Home Additions San Jose’s current services and saw you cover additions, ADUs and second-story projects with free estimates. Campaign angle: ‘Before designing a major addition, establish what is feasible, what needs permitting and what the project scope should include.’ I’d build feasibility FAQs and estimate follow-ups. $150 flat. Want two examples first?</t>
+  </si>
+  <si>
+    <t>https://homeadditionssanjose.com/</t>
   </si>
   <si>
     <t>Script ID</t>
@@ -611,91 +848,70 @@
     <t>Source</t>
   </si>
   <si>
-    <t>2026-09-05T22:50:24-07:00</t>
+    <t>New verified lead added 2026-09-12; no outreach recorded. Use individualized initial pitch.</t>
+  </si>
+  <si>
+    <t>Archived</t>
+  </si>
+  <si>
+    <t>Leader Restoration</t>
+  </si>
+  <si>
+    <t>CostLess Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>Los Gatos Roofing</t>
+  </si>
+  <si>
+    <t>Precision Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
+    <t>Roofs By Reveille, Inc</t>
+  </si>
+  <si>
+    <t>A1 Restoration</t>
+  </si>
+  <si>
+    <t>911 Restoration of San Jose</t>
+  </si>
+  <si>
+    <t>Any Hour Water and Fire</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>IRBIS Air Plumbing Electrical</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>California Water and Fire</t>
+  </si>
+  <si>
+    <t>Infinium Solar, Roofing and Electric</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
     <t>2026-09-08</t>
   </si>
   <si>
-    <t>2026-09-08T16:45:47-07:00</t>
-  </si>
-  <si>
-    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
-  </si>
-  <si>
-    <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:49:58-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
-  </si>
-  <si>
-    <t>2026-09-05T22:39:21-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-05T20:01:38-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-09-07T13:35:02-07:00</t>
-  </si>
-  <si>
-    <t>2026-09-07T14:19:35-07:00</t>
-  </si>
-  <si>
-    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
-  </si>
-  <si>
-    <t>Archived</t>
-  </si>
-  <si>
-    <t>CostLess Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>2026-09-06</t>
-  </si>
-  <si>
-    <t>Los Gatos Roofing</t>
-  </si>
-  <si>
-    <t>Precision Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>2026-09-06T01:37:52-07:00</t>
-  </si>
-  <si>
-    <t>Roofs By Reveille, Inc</t>
-  </si>
-  <si>
-    <t>A1 Restoration</t>
-  </si>
-  <si>
-    <t>911 Restoration of San Jose</t>
-  </si>
-  <si>
-    <t>Any Hour Water and Fire</t>
-  </si>
-  <si>
-    <t>IRBIS Air Plumbing Electrical</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>California Water and Fire</t>
-  </si>
-  <si>
-    <t>Infinium Solar, Roofing and Electric</t>
-  </si>
-  <si>
-    <t>Lifetime Roofing &amp; Renovation, Inc.</t>
+    <t>ROOF EXPRESS</t>
   </si>
   <si>
     <t>South Bay Roofing CO</t>
@@ -705,6 +921,15 @@
   </si>
   <si>
     <t>The Roofer Bros</t>
+  </si>
+  <si>
+    <t>Roof By Tom</t>
+  </si>
+  <si>
+    <t>FairPrice Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>Galaxy Heating &amp; Air Conditioning</t>
   </si>
   <si>
     <t>Air &amp; Plumbing Systems</t>
@@ -1305,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -1430,40 +1655,40 @@
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1477,40 +1702,40 @@
         <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1518,28 +1743,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>57</v>
@@ -1571,40 +1796,40 @@
         <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1612,40 +1837,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1659,46 +1884,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1706,46 +1931,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1753,46 +1978,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1800,10 +2025,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1812,28 +2037,28 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1842,9 +2067,461 @@
         <v>28</v>
       </c>
     </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
-  <conditionalFormatting sqref="E2:E11">
+  <autoFilter ref="A1:O21"/>
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E2)))</formula>
     </cfRule>
@@ -1860,6 +2537,16 @@
     <hyperlink ref="M9" r:id="rId8"/>
     <hyperlink ref="M10" r:id="rId9"/>
     <hyperlink ref="M11" r:id="rId10"/>
+    <hyperlink ref="M12" r:id="rId11"/>
+    <hyperlink ref="M13" r:id="rId12"/>
+    <hyperlink ref="M14" r:id="rId13"/>
+    <hyperlink ref="M15" r:id="rId14"/>
+    <hyperlink ref="M16" r:id="rId15"/>
+    <hyperlink ref="M17" r:id="rId16"/>
+    <hyperlink ref="M18" r:id="rId17"/>
+    <hyperlink ref="M19" r:id="rId18"/>
+    <hyperlink ref="M20" r:id="rId19"/>
+    <hyperlink ref="M21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1878,142 +2565,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>222</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>137</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>234</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>161</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2023,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2043,55 +2730,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>262</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
+        <v>263</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>177</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2104,15 +2791,9 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2127,7 +2808,7 @@
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
@@ -2145,7 +2826,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2154,7 +2835,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -2164,14 +2845,14 @@
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2182,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2191,7 +2872,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -2201,32 +2882,28 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>184</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -2242,7 +2919,7 @@
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>185</v>
+        <v>272</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
@@ -2260,7 +2937,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2269,40 +2946,38 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K6" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>184</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2318,25 +2993,25 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>185</v>
+        <v>272</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -2345,7 +3020,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -2355,25 +3030,25 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2382,7 +3057,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -2392,25 +3067,25 @@
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2419,7 +3094,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -2429,41 +3104,31 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>190</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
         <v>28</v>
@@ -2476,18 +3141,388 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="2">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q21"/>
   <conditionalFormatting sqref="J2:J501">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Won/Paid">
       <formula>NOT(ISERROR(SEARCH("Won/Paid",J2)))</formula>
@@ -2512,6 +3547,16 @@
     <hyperlink ref="Q9" r:id="rId8"/>
     <hyperlink ref="Q10" r:id="rId9"/>
     <hyperlink ref="Q11" r:id="rId10"/>
+    <hyperlink ref="Q12" r:id="rId11"/>
+    <hyperlink ref="Q13" r:id="rId12"/>
+    <hyperlink ref="Q14" r:id="rId13"/>
+    <hyperlink ref="Q15" r:id="rId14"/>
+    <hyperlink ref="Q16" r:id="rId15"/>
+    <hyperlink ref="Q17" r:id="rId16"/>
+    <hyperlink ref="Q18" r:id="rId17"/>
+    <hyperlink ref="Q19" r:id="rId18"/>
+    <hyperlink ref="Q20" r:id="rId19"/>
+    <hyperlink ref="Q21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2531,33 +3576,33 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>274</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2574,10 +3619,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2588,16 +3633,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2608,19 +3653,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>197</v>
+        <v>280</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -2630,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2650,16 +3695,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -2670,16 +3715,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2690,16 +3735,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2710,16 +3755,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2730,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2750,16 +3795,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -2770,16 +3815,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2790,16 +3835,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -2816,10 +3861,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -2830,16 +3875,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -2850,16 +3895,16 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -2870,16 +3915,16 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>297</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2896,10 +3941,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -2916,10 +3961,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>299</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2936,10 +3981,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -2950,16 +3995,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -2981,7 +4026,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -3002,10 +4047,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3022,7 +4067,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3030,16 +4075,16 @@
         <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3047,24 +4092,24 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>60</v>
@@ -3073,7 +4118,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3081,101 +4126,271 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>215</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -3190,6 +4405,16 @@
     <hyperlink ref="C9" r:id="rId8"/>
     <hyperlink ref="C10" r:id="rId9"/>
     <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
+    <hyperlink ref="C17" r:id="rId16"/>
+    <hyperlink ref="C18" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId18"/>
+    <hyperlink ref="C20" r:id="rId19"/>
+    <hyperlink ref="C21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3209,7 +4434,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>216</v>
+        <v>306</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3218,29 +4443,29 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>307</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>219</v>
+        <v>309</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contact Ready")</f>
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="E4" s="3">
         <f>SUM(Pipeline!K:K)</f>
@@ -3249,14 +4474,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>279</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="E5" s="3">
         <f>SUM(Pipeline!L:L)</f>
@@ -3265,14 +4490,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="E6" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3281,14 +4506,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>316</v>
       </c>
       <c r="E7" s="6">
         <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
@@ -3297,7 +4522,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>222</v>
+        <v>312</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
@@ -3306,7 +4531,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Pipeline!J:J,"Fulfilled")</f>
@@ -3332,90 +4557,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>231</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>232</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>233</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>234</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>325</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>236</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>239</v>
+        <v>329</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>241</v>
+        <v>331</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>242</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>243</v>
+        <v>333</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>244</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>246</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>247</v>
+        <v>337</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>248</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -3434,19 +4659,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>341</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>342</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>253</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3457,13 +4682,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>254</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
+++ b/sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx
@@ -7,25 +7,26 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Priority Leads" sheetId="1" r:id="rId1"/>
+    <sheet name="New Lead Queue" sheetId="1" r:id="rId1"/>
     <sheet name="Scripts" sheetId="2" r:id="rId2"/>
     <sheet name="Pipeline" sheetId="3" r:id="rId3"/>
-    <sheet name="Archived Leads" sheetId="4" r:id="rId4"/>
-    <sheet name="Sources" sheetId="5" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
-    <sheet name="Update Rules" sheetId="7" r:id="rId7"/>
-    <sheet name="Refresh Log" sheetId="8" r:id="rId8"/>
+    <sheet name="Actual Outreach History" sheetId="4" r:id="rId4"/>
+    <sheet name="Archived Leads" sheetId="5" r:id="rId5"/>
+    <sheet name="Sources" sheetId="6" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="7" r:id="rId7"/>
+    <sheet name="Update Rules" sheetId="8" r:id="rId8"/>
+    <sheet name="Refresh Log" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$Q$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priority Leads'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'New Lead Queue'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pipeline!$A$1:$R$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="423">
   <si>
     <t>Rank</t>
   </si>
@@ -848,15 +849,237 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Offer Value $</t>
+  </si>
+  <si>
     <t>New verified lead added 2026-09-12; no outreach recorded. Use individualized initial pitch.</t>
   </si>
   <si>
+    <t>FloodDry Water Damage Restoration</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:50:24-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-08T16:45:47-07:00</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails, no inbound reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>Therma Tech</t>
+  </si>
+  <si>
+    <t>2026-09-05T20:01:38-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-07T13:35:02-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:19:35-07:00</t>
+  </si>
+  <si>
+    <t>Three verified outbound emails across two connected Gmail accounts; no inbound reply found through 2026-09-12. Stop cold follow-up unless they reply.</t>
+  </si>
+  <si>
+    <t>Dansel Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:49:58-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no inbound reply found through 2026-09-12. One final respectful follow-up is permissible, then stop unless they reply.</t>
+  </si>
+  <si>
+    <t>California First Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:21-07:00</t>
+  </si>
+  <si>
+    <t>US Creative Restoration</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:53:01-07:00</t>
+  </si>
+  <si>
+    <t>One verified outbound email; no reply found through 2026-09-12. Eligible for at most one respectful follow-up.</t>
+  </si>
+  <si>
+    <t>WJM Builders</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:30:53-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Clean Roofing</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:42:04-07:00</t>
+  </si>
+  <si>
+    <t>Solar Energy Consultants</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:25:44-07:00</t>
+  </si>
+  <si>
+    <t>Mayer's Construction</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:31:58-07:00</t>
+  </si>
+  <si>
+    <t>EVS Mechanical</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:32:27-07:00</t>
+  </si>
+  <si>
+    <t>Dueling Trowels Concrete Solutions</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:39:44-07:00</t>
+  </si>
+  <si>
+    <t>2026-09-06T03:20:39-07:00</t>
+  </si>
+  <si>
+    <t>Two verified outbound emails; no reply found through 2026-09-12. Do not send another cold touch now.</t>
+  </si>
+  <si>
+    <t>GBD Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:54:30-07:00</t>
+  </si>
+  <si>
+    <t>John Molina Concrete</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:46:13-07:00</t>
+  </si>
+  <si>
+    <t>Precision Concrete Inc</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:40:53-07:00</t>
+  </si>
+  <si>
+    <t>One Day Complete Repipe</t>
+  </si>
+  <si>
+    <t>2026-09-05T22:35:59-07:00</t>
+  </si>
+  <si>
+    <t>First Touch Evidence</t>
+  </si>
+  <si>
+    <t>FU1 Evidence</t>
+  </si>
+  <si>
+    <t>FU2 Evidence</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a074aa18c4a15e5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07d94dc355abc7</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07dbda8027b039</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07537695be159d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753a7d53e5a5c</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753ad793984cf</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0763c06f9e9dc5</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0753be59b49989</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07540c8b9fd4bc</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075443349aa830</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075449a2403271</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a08369d9f6b09c0</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0754701539a56d</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075485ca2a3fef</t>
+  </si>
+  <si>
+    <t>Precision Heating &amp; Cooling</t>
+  </si>
+  <si>
+    <t>2026-09-06T01:37:52-07:00</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a075ddee6716e8a</t>
+  </si>
+  <si>
+    <t>Historical send discovered during Sep 12 audit; no reply found in connected Gmail search.</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07640ae5a69379</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a076456505c6304</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764664a2b1202</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a07646d6dbd3474</t>
+  </si>
+  <si>
+    <t>Gmail sent message 1a0764fa024df1f4</t>
+  </si>
+  <si>
     <t>Archived</t>
   </si>
   <si>
     <t>Leader Restoration</t>
   </si>
   <si>
+    <t>Rotated out of fresh queue 2026-09-12; no outreach found in connected Gmail checks.</t>
+  </si>
+  <si>
     <t>CostLess Heating &amp; Cooling</t>
   </si>
   <si>
@@ -866,15 +1089,6 @@
     <t>Los Gatos Roofing</t>
   </si>
   <si>
-    <t>Precision Heating &amp; Cooling</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>2026-09-06T01:37:52-07:00</t>
-  </si>
-  <si>
     <t>Roofs By Reveille, Inc</t>
   </si>
   <si>
@@ -887,13 +1101,10 @@
     <t>Any Hour Water and Fire</t>
   </si>
   <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
     <t>IRBIS Air Plumbing Electrical</t>
   </si>
   <si>
-    <t>2026-09-10</t>
+    <t>Use official web/phone route; no direct email re-verified 2026-09-09.</t>
   </si>
   <si>
     <t>California Water and Fire</t>
@@ -902,15 +1113,9 @@
     <t>Infinium Solar, Roofing and Electric</t>
   </si>
   <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
     <t>Lifetime Roofing &amp; Renovation, Inc.</t>
   </si>
   <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
     <t>ROOF EXPRESS</t>
   </si>
   <si>
@@ -938,19 +1143,25 @@
     <t>2026-09-11</t>
   </si>
   <si>
+    <t>Archived from active Top 10 on 2026-09-11; no outreach recorded.</t>
+  </si>
+  <si>
     <t>Top Tier Roofing</t>
   </si>
   <si>
     <t>Verified Date</t>
   </si>
   <si>
+    <t>Direct Contact</t>
+  </si>
+  <si>
     <t>Reverify Rule</t>
   </si>
   <si>
-    <t>Reverify time-sensitive offers, hours, financing, ETA, and contact details before outreach.</t>
-  </si>
-  <si>
-    <t>SAME-DAY CUSTOMER GROWTH PACK — LIVE DASHBOARD</t>
+    <t>Reverify time-sensitive offers, hours, financing, ETA, response-time claims, and contact details before outreach.</t>
+  </si>
+  <si>
+    <t>SAME-DAY CUSTOMER GROWTH PACK — LIVE PIPELINE</t>
   </si>
   <si>
     <t>Metric</t>
@@ -959,7 +1170,10 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Revenue Metric</t>
+    <t>Commercial Metric</t>
+  </si>
+  <si>
+    <t>Meaning</t>
   </si>
   <si>
     <t>Replied</t>
@@ -971,18 +1185,36 @@
     <t>Won/Paid</t>
   </si>
   <si>
-    <t>Quoted Pipeline</t>
+    <t>Nominal Offer Value</t>
+  </si>
+  <si>
+    <t>Potential at the standard package price; not booked revenue.</t>
+  </si>
+  <si>
+    <t>Actual Quoted $</t>
+  </si>
+  <si>
+    <t>Only real negotiated/quoted dollars.</t>
   </si>
   <si>
     <t>Paid Revenue</t>
   </si>
   <si>
+    <t>Only actual payments.</t>
+  </si>
+  <si>
     <t>Response Rate</t>
   </si>
   <si>
+    <t>Replies divided by records with a real first touch.</t>
+  </si>
+  <si>
     <t>Close Rate</t>
   </si>
   <si>
+    <t>Wins divided by records with a real first touch.</t>
+  </si>
+  <si>
     <t>Rule</t>
   </si>
   <si>
@@ -1007,10 +1239,16 @@
     <t>sales-engine/Same-Day-Customer-Growth-Pack-Live-CRM.xlsx</t>
   </si>
   <si>
+    <t>Fresh means fresh</t>
+  </si>
+  <si>
+    <t>Before a prospect enters New Lead Queue, verify it and check connected Gmail history for prior contact.</t>
+  </si>
+  <si>
     <t>Evidence</t>
   </si>
   <si>
-    <t>Every active lead requires a current source URL and dated evidence-based opportunity.</t>
+    <t>Every current lead requires a current source URL and dated evidence-based opportunity.</t>
   </si>
   <si>
     <t>Contacts</t>
@@ -1022,19 +1260,16 @@
     <t>Pipeline truth</t>
   </si>
   <si>
-    <t>Never mark contact, reply, payment, customer, revenue, or fulfillment unless it actually occurred.</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>Initial cold contact + max two cold follow-ups, then stop unless they reply.</t>
-  </si>
-  <si>
-    <t>Opt-out</t>
-  </si>
-  <si>
-    <t>Immediately stop and mark Do Not Contact.</t>
+    <t>Never mark contact, reply, quote, payment, customer, revenue, or fulfillment unless it actually occurred.</t>
+  </si>
+  <si>
+    <t>Offer value</t>
+  </si>
+  <si>
+    <t>The standard package price is potential value, not quoted pipeline or revenue.</t>
+  </si>
+  <si>
+    <t>Initial cold contact + max two respectful cold follow-ups; stop sooner on decline/opt-out and avoid duplicate account touches.</t>
   </si>
   <si>
     <t>Claims</t>
@@ -1046,16 +1281,16 @@
     <t>Workbook generation</t>
   </si>
   <si>
-    <t>GitHub Actions regenerates this XLSX from the live feed + pipeline history.</t>
+    <t>GitHub Actions regenerates this XLSX from the live feed + truth-preserving pipeline history.</t>
   </si>
   <si>
     <t>Refresh Date</t>
   </si>
   <si>
-    <t>Lead Feed Date</t>
-  </si>
-  <si>
-    <t>Active Leads</t>
+    <t>Fresh Leads</t>
+  </si>
+  <si>
+    <t>Observed Contact Records</t>
   </si>
   <si>
     <t>Archived Records</t>
@@ -1064,7 +1299,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Generated automatically from verified GitHub sources; pipeline history preserved separately.</t>
+    <t>Generated from the verified lead feed and preserved pipeline history. Unobserved outcomes remain zero/blank.</t>
   </si>
 </sst>
 </file>
@@ -1171,13 +1406,17 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1534,18 +1773,18 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
     <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" customWidth="1"/>
-    <col min="6" max="6" width="48.7109375" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
-    <col min="10" max="10" width="44.7109375" customWidth="1"/>
-    <col min="11" max="11" width="36.7109375" customWidth="1"/>
-    <col min="12" max="12" width="68.7109375" customWidth="1"/>
-    <col min="13" max="13" width="46.7109375" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" customWidth="1"/>
+    <col min="10" max="10" width="48.7109375" customWidth="1"/>
+    <col min="11" max="11" width="38.7109375" customWidth="1"/>
+    <col min="12" max="12" width="72.7109375" customWidth="1"/>
+    <col min="13" max="13" width="50.7109375" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" customWidth="1"/>
   </cols>
@@ -2559,7 +2798,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
     <col min="4" max="4" width="92.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2710,25 +2949,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="38.7109375" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="38.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="58.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="48.7109375" customWidth="1"/>
+    <col min="17" max="17" width="50.7109375" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>256</v>
       </c>
@@ -2780,8 +3023,11 @@
       <c r="Q1" s="1" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -2808,7 +3054,7 @@
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
@@ -2817,8 +3063,11 @@
       <c r="Q2" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -2845,7 +3094,7 @@
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
@@ -2854,8 +3103,11 @@
       <c r="Q3" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -2882,7 +3134,7 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
@@ -2891,8 +3143,11 @@
       <c r="Q4" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
@@ -2919,7 +3174,7 @@
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
@@ -2928,8 +3183,11 @@
       <c r="Q5" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -2956,7 +3214,7 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
@@ -2965,8 +3223,11 @@
       <c r="Q6" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
         <v>72</v>
       </c>
@@ -2993,7 +3254,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
@@ -3002,8 +3263,11 @@
       <c r="Q7" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
@@ -3030,7 +3294,7 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
@@ -3039,8 +3303,11 @@
       <c r="Q8" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -3067,7 +3334,7 @@
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
@@ -3076,8 +3343,11 @@
       <c r="Q9" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
         <v>105</v>
       </c>
@@ -3104,7 +3374,7 @@
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
@@ -3113,8 +3383,11 @@
       <c r="Q10" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
         <v>115</v>
       </c>
@@ -3141,7 +3414,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="s">
@@ -3150,8 +3423,11 @@
       <c r="Q11" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
         <v>124</v>
       </c>
@@ -3178,7 +3454,7 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
@@ -3187,8 +3463,11 @@
       <c r="Q12" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
         <v>134</v>
       </c>
@@ -3215,7 +3494,7 @@
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
@@ -3224,8 +3503,11 @@
       <c r="Q13" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
         <v>143</v>
       </c>
@@ -3252,7 +3534,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2" t="s">
@@ -3261,8 +3543,11 @@
       <c r="Q14" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
         <v>152</v>
       </c>
@@ -3289,7 +3574,7 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2" t="s">
@@ -3298,8 +3583,11 @@
       <c r="Q15" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
@@ -3326,7 +3614,7 @@
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
@@ -3335,8 +3623,11 @@
       <c r="Q16" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
         <v>171</v>
       </c>
@@ -3363,7 +3654,7 @@
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2" t="s">
@@ -3372,8 +3663,11 @@
       <c r="Q17" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
         <v>180</v>
       </c>
@@ -3400,7 +3694,7 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
@@ -3409,8 +3703,11 @@
       <c r="Q18" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
         <v>189</v>
       </c>
@@ -3437,7 +3734,7 @@
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
@@ -3446,8 +3743,11 @@
       <c r="Q19" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
         <v>198</v>
       </c>
@@ -3474,7 +3774,7 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
@@ -3483,8 +3783,11 @@
       <c r="Q20" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
         <v>207</v>
       </c>
@@ -3511,7 +3814,7 @@
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
@@ -3520,9 +3823,622 @@
       <c r="Q21" s="2" t="s">
         <v>215</v>
       </c>
+      <c r="R21" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="3">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q21"/>
+  <autoFilter ref="A1:R36"/>
   <conditionalFormatting sqref="J2:J501">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Won/Paid">
       <formula>NOT(ISERROR(SEARCH("Won/Paid",J2)))</formula>
@@ -3564,460 +4480,492 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="8" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="44.7109375" customWidth="1"/>
+    <col min="8" max="8" width="36.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="66.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="L1" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>336</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>285</v>
-      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>289</v>
+        <v>337</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>292</v>
-      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>343</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>285</v>
-      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>344</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>285</v>
-      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="2"/>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4026,17 +4974,528 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="64.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="62.7109375" customWidth="1"/>
     <col min="3" max="3" width="50.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="54.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4047,13 +5506,16 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>372</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>373</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -4067,10 +5529,13 @@
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -4084,10 +5549,13 @@
         <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -4101,10 +5569,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
@@ -4118,10 +5589,13 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>55</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -4135,10 +5609,13 @@
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>72</v>
       </c>
@@ -4152,10 +5629,13 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>77</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
@@ -4169,10 +5649,13 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -4186,10 +5669,13 @@
         <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>105</v>
       </c>
@@ -4203,10 +5689,13 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>109</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>115</v>
       </c>
@@ -4220,10 +5709,13 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>118</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>124</v>
       </c>
@@ -4237,10 +5729,13 @@
         <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>128</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>134</v>
       </c>
@@ -4254,10 +5749,13 @@
         <v>27</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>137</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>143</v>
       </c>
@@ -4271,10 +5769,13 @@
         <v>27</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>146</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>152</v>
       </c>
@@ -4288,10 +5789,13 @@
         <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>156</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
@@ -4305,10 +5809,13 @@
         <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>165</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>171</v>
       </c>
@@ -4322,10 +5829,13 @@
         <v>27</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>175</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>180</v>
       </c>
@@ -4339,10 +5849,13 @@
         <v>27</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>183</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>189</v>
       </c>
@@ -4356,10 +5869,13 @@
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>192</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>198</v>
       </c>
@@ -4373,10 +5889,13 @@
         <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>201</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>207</v>
       </c>
@@ -4390,7 +5909,10 @@
         <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>305</v>
+        <v>210</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -4420,43 +5942,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28" customHeight="1">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F1" s="5"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>308</v>
+        <v>378</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>378</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -4465,71 +5992,93 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>313</v>
+        <v>384</v>
       </c>
       <c r="E4" s="3">
-        <f>SUM(Pipeline!K:K)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <f>SUM(Pipeline!R:R)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Pipeline!J:J,"Contacted")</f>
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>314</v>
+        <v>386</v>
       </c>
       <c r="E5" s="3">
-        <f>SUM(Pipeline!L:L)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <f>SUM(Pipeline!K:K)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Pipeline!J:J,"Replied")</f>
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E6" s="6">
-        <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>388</v>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(Pipeline!L:L)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>311</v>
+        <v>382</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Pipeline!J:J,"Negotiating")</f>
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
+        <v>390</v>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <f>IFERROR(COUNTIF(Pipeline!J:J,"Replied")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>312</v>
+        <v>383</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Pipeline!J:J,"Won/Paid")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="D8" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E8" s="6">
+        <f>IFERROR(COUNTIF(Pipeline!J:J,"Won/Paid")/COUNTIF(Pipeline!D:D,"&lt;&gt;"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>267</v>
       </c>
@@ -4540,155 +6089,163 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="92.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="78.7109375" customWidth="1"/>
+    <col min="1" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="90.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>342</v>
+        <v>420</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
+      <c r="B2" s="2">
+        <v>20</v>
       </c>
       <c r="C2" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>344</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
